--- a/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_Evidence.xlsx
+++ b/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_Evidence.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="40">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -246,6 +246,19 @@
     </font>
     <font>
       <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -475,7 +488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -659,6 +672,13 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2052,6 +2072,7 @@
     <row r="22" ht="27.2" customHeight="1"/>
     <row r="23" ht="20.45" customHeight="1"/>
     <row r="24" ht="20.45" customHeight="1"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="71" t="inlineStr">
         <is>
@@ -2071,7 +2092,7 @@
       <c r="E27" s="74" t="n"/>
       <c r="F27" s="63" t="inlineStr">
         <is>
-          <t>Yellow cell: leave blank if the evidence folder sits next to this workbook; otherwise paste its full path (local, network or SharePoint).</t>
+          <t>Links are relative to this workbook: keep the folder BSI.IT.6.C7.3-Evidences next to this .xlsx (extract the whole zip first; do not open the workbook from inside the zip). If the evidence sits elsewhere, set File &gt; Info &gt; Properties &gt; Advanced Properties &gt; Summary &gt; Hyperlink base to the folder that contains it.</t>
         </is>
       </c>
     </row>
@@ -2081,18 +2102,21 @@
           <t>Links resolve to</t>
         </is>
       </c>
-      <c r="B28" s="75">
-        <f>EvidenceRoot</f>
-        <v/>
+      <c r="B28" s="75" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\ (in the same folder as this workbook)</t>
+        </is>
       </c>
       <c r="C28" s="73" t="n"/>
       <c r="D28" s="73" t="n"/>
       <c r="E28" s="74" t="n"/>
-      <c r="F28" s="76">
-        <f>HYPERLINK(EvidenceRoot,"Test: open the evidence folder")</f>
-        <v/>
-      </c>
-    </row>
+      <c r="F28" s="82" t="inlineStr">
+        <is>
+          <t>Test: open the evidence folder</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="71" t="inlineStr">
         <is>
@@ -2106,9 +2130,10 @@
           <t>Folder 01</t>
         </is>
       </c>
-      <c r="B31" s="79">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications","\","/"),"01_Management_Attestation_In-Scope_Applications"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications")</f>
-        <v/>
+      <c r="B31" s="79" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications</t>
+        </is>
       </c>
       <c r="C31" s="73" t="n"/>
       <c r="D31" s="73" t="n"/>
@@ -2125,9 +2150,10 @@
           <t>Folder 02</t>
         </is>
       </c>
-      <c r="B32" s="79">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email")</f>
-        <v/>
+      <c r="B32" s="79" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+        </is>
       </c>
       <c r="C32" s="73" t="n"/>
       <c r="D32" s="73" t="n"/>
@@ -2144,9 +2170,10 @@
           <t>Folder 03</t>
         </is>
       </c>
-      <c r="B33" s="79">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
-        <v/>
+      <c r="B33" s="79" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+        </is>
       </c>
       <c r="C33" s="73" t="n"/>
       <c r="D33" s="73" t="n"/>
@@ -2163,9 +2190,10 @@
           <t>Folder 04</t>
         </is>
       </c>
-      <c r="B34" s="79">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
-        <v/>
+      <c r="B34" s="79" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+        </is>
       </c>
       <c r="C34" s="73" t="n"/>
       <c r="D34" s="73" t="n"/>
@@ -2182,9 +2210,10 @@
           <t>Folder 05</t>
         </is>
       </c>
-      <c r="B35" s="79">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails")</f>
-        <v/>
+      <c r="B35" s="79" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails</t>
+        </is>
       </c>
       <c r="C35" s="73" t="n"/>
       <c r="D35" s="73" t="n"/>
@@ -2218,6 +2247,14 @@
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B28:E28"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" display="Test: open the evidence folder" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Aptos"&amp;1 &amp;K000000 Confidential#_x000d_</oddHeader>
@@ -4513,6 +4550,7 @@
       </c>
     </row>
     <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="21.95" customHeight="1">
       <c r="A4" s="46" t="inlineStr">
         <is>
@@ -4985,6 +5023,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="64" t="inlineStr">
         <is>
@@ -5006,6 +5045,7 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="64" t="inlineStr">
         <is>
@@ -5035,9 +5075,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="80">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails"),"Open evidence folder 05: DRS01, DRS02")</f>
-        <v/>
+      <c r="A22" s="80" t="inlineStr">
+        <is>
+          <t>Open evidence folder 05: DRS01, DRS02</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5047,6 +5088,9 @@
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A19:H19"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" display="Open evidence folder 05: DRS01, DRS02" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Aptos"&amp;1 &amp;K000000 Confidential#_x000d_</oddHeader>
@@ -5057,7 +5101,7 @@
     <firstFooter/>
   </headerFooter>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5445,25 +5489,30 @@
           <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero). IT and business DR scope confirmed by the DRS01 (IT Scope) and DRS02 (Business Scope) emails.</t>
         </is>
       </c>
-      <c r="T3" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications","\","/"),"01_Management_Attestation_In-Scope_Applications"),"Open folder 01: MA01")</f>
-        <v/>
-      </c>
-      <c r="U3" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"Open folder 02: BLA01")</f>
-        <v/>
-      </c>
-      <c r="V3" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"Open folder 03: DMA01, DMA02")</f>
-        <v/>
-      </c>
-      <c r="W3" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"Open folder 04: E01, E02, E03, E04, E05, E09, E16b")</f>
-        <v/>
-      </c>
-      <c r="X3" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails"),"Open folder 05: DRS01, DRS02")</f>
-        <v/>
+      <c r="T3" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 01: MA01</t>
+        </is>
+      </c>
+      <c r="U3" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 02: BLA01</t>
+        </is>
+      </c>
+      <c r="V3" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 03: DMA01, DMA02</t>
+        </is>
+      </c>
+      <c r="W3" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 04: E01, E02, E03, E04, E05, E09, E16b</t>
+        </is>
+      </c>
+      <c r="X3" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 05: DRS01, DRS02</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="60.6" customFormat="1" customHeight="1" s="8">
@@ -5584,25 +5633,30 @@
           <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero). IT and business DR scope confirmed by the DRS01 (IT Scope) and DRS02 (Business Scope) emails.</t>
         </is>
       </c>
-      <c r="T4" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications","\","/"),"01_Management_Attestation_In-Scope_Applications"),"Open folder 01: MA01")</f>
-        <v/>
-      </c>
-      <c r="U4" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"Open folder 02: BLA01")</f>
-        <v/>
-      </c>
-      <c r="V4" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"Open folder 03: DMA01, DMA02")</f>
-        <v/>
-      </c>
-      <c r="W4" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"Open folder 04: E01, E02, E03, E04, E05, E09, E16b")</f>
-        <v/>
-      </c>
-      <c r="X4" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails"),"Open folder 05: DRS01, DRS02")</f>
-        <v/>
+      <c r="T4" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 01: MA01</t>
+        </is>
+      </c>
+      <c r="U4" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 02: BLA01</t>
+        </is>
+      </c>
+      <c r="V4" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 03: DMA01, DMA02</t>
+        </is>
+      </c>
+      <c r="W4" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 04: E01, E02, E03, E04, E05, E09, E16b</t>
+        </is>
+      </c>
+      <c r="X4" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 05: DRS01, DRS02</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="60.6" customFormat="1" customHeight="1" s="8">
@@ -5723,25 +5777,30 @@
           <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero). IT and business DR scope confirmed by the DRS01 (IT Scope) and DRS02 (Business Scope) emails.</t>
         </is>
       </c>
-      <c r="T5" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications","\","/"),"01_Management_Attestation_In-Scope_Applications"),"Open folder 01: MA01")</f>
-        <v/>
-      </c>
-      <c r="U5" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"Open folder 02: BLA01")</f>
-        <v/>
-      </c>
-      <c r="V5" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"Open folder 03: DMA01, DMA02")</f>
-        <v/>
-      </c>
-      <c r="W5" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"Open folder 04: E01, E02, E03, E04, E05, E09, E16b")</f>
-        <v/>
-      </c>
-      <c r="X5" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails"),"Open folder 05: DRS01, DRS02")</f>
-        <v/>
+      <c r="T5" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 01: MA01</t>
+        </is>
+      </c>
+      <c r="U5" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 02: BLA01</t>
+        </is>
+      </c>
+      <c r="V5" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 03: DMA01, DMA02</t>
+        </is>
+      </c>
+      <c r="W5" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 04: E01, E02, E03, E04, E05, E09, E16b</t>
+        </is>
+      </c>
+      <c r="X5" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 05: DRS01, DRS02</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="60.6" customFormat="1" customHeight="1" s="8">
@@ -5884,25 +5943,30 @@
           <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Claudia Romero, Miguel Orozco, Maria del Cerro Hontanilla). IT and business DR scope confirmed by the DRS01 (IT Scope) and DRS02 (Business Scope) emails.</t>
         </is>
       </c>
-      <c r="T6" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications","\","/"),"01_Management_Attestation_In-Scope_Applications"),"Open folder 01: MA01")</f>
-        <v/>
-      </c>
-      <c r="U6" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"Open folder 02: BLA01, BLA02")</f>
-        <v/>
-      </c>
-      <c r="V6" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"Open folder 03: DMA01, DMA02, DMA05, DMA11")</f>
-        <v/>
-      </c>
-      <c r="W6" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"Open folder 04: E01, E02, E03, E04, E05, E09, E16b")</f>
-        <v/>
-      </c>
-      <c r="X6" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails"),"Open folder 05: DRS01, DRS02")</f>
-        <v/>
+      <c r="T6" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 01: MA01</t>
+        </is>
+      </c>
+      <c r="U6" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 02: BLA01, BLA02</t>
+        </is>
+      </c>
+      <c r="V6" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 03: DMA01, DMA02, DMA05, DMA11</t>
+        </is>
+      </c>
+      <c r="W6" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 04: E01, E02, E03, E04, E05, E09, E16b</t>
+        </is>
+      </c>
+      <c r="X6" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 05: DRS01, DRS02</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="60.6" customFormat="1" customHeight="1" s="8">
@@ -6022,25 +6086,30 @@
           <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Michelle Oropesa). IT and business DR scope confirmed by the DRS01 (IT Scope) and DRS02 (Business Scope) emails.</t>
         </is>
       </c>
-      <c r="T7" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications","\","/"),"01_Management_Attestation_In-Scope_Applications"),"Open folder 01: MA01")</f>
-        <v/>
-      </c>
-      <c r="U7" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"Open folder 02: BLA04")</f>
-        <v/>
-      </c>
-      <c r="V7" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"Open folder 03: DMA02, DMA04")</f>
-        <v/>
-      </c>
-      <c r="W7" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"Open folder 04: E01, E02, E03, E04, E05, E16b")</f>
-        <v/>
-      </c>
-      <c r="X7" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails"),"Open folder 05: DRS01, DRS02")</f>
-        <v/>
+      <c r="T7" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 01: MA01</t>
+        </is>
+      </c>
+      <c r="U7" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 02: BLA04</t>
+        </is>
+      </c>
+      <c r="V7" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 03: DMA02, DMA04</t>
+        </is>
+      </c>
+      <c r="W7" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 04: E01, E02, E03, E04, E05, E16b</t>
+        </is>
+      </c>
+      <c r="X7" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 05: DRS01, DRS02</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="60.6" customFormat="1" customHeight="1" s="8">
@@ -6163,25 +6232,30 @@
           <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Franklin Puentes). IT and business DR scope confirmed by the DRS01 (IT Scope) and DRS02 (Business Scope) emails.</t>
         </is>
       </c>
-      <c r="T8" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications","\","/"),"01_Management_Attestation_In-Scope_Applications"),"Open folder 01: MA01")</f>
-        <v/>
-      </c>
-      <c r="U8" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"Open folder 02: BLA03")</f>
-        <v/>
-      </c>
-      <c r="V8" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"Open folder 03: DMA02, DMA03")</f>
-        <v/>
-      </c>
-      <c r="W8" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"Open folder 04: E01, E02, E03, E04, E05, E07, E08, E16b")</f>
-        <v/>
-      </c>
-      <c r="X8" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails"),"Open folder 05: DRS01, DRS02")</f>
-        <v/>
+      <c r="T8" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 01: MA01</t>
+        </is>
+      </c>
+      <c r="U8" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 02: BLA03</t>
+        </is>
+      </c>
+      <c r="V8" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 03: DMA02, DMA03</t>
+        </is>
+      </c>
+      <c r="W8" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 04: E01, E02, E03, E04, E05, E07, E08, E16b</t>
+        </is>
+      </c>
+      <c r="X8" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 05: DRS01, DRS02</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="60.6" customFormat="1" customHeight="1" s="8">
@@ -6317,25 +6391,30 @@
           <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Franklin Puentes, Maria del Cerro Hontanilla). IT and business DR scope confirmed by the DRS01 (IT Scope) and DRS02 (Business Scope) emails.</t>
         </is>
       </c>
-      <c r="T9" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications","\","/"),"01_Management_Attestation_In-Scope_Applications"),"Open folder 01: MA01")</f>
-        <v/>
-      </c>
-      <c r="U9" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"Open folder 02: BLA02, BLA03")</f>
-        <v/>
-      </c>
-      <c r="V9" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"Open folder 03: DMA02, DMA03, DMA05")</f>
-        <v/>
-      </c>
-      <c r="W9" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"Open folder 04: E01, E02, E03, E04, E05, E07, E08, E16b")</f>
-        <v/>
-      </c>
-      <c r="X9" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails"),"Open folder 05: DRS01, DRS02")</f>
-        <v/>
+      <c r="T9" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 01: MA01</t>
+        </is>
+      </c>
+      <c r="U9" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 02: BLA02, BLA03</t>
+        </is>
+      </c>
+      <c r="V9" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 03: DMA02, DMA03, DMA05</t>
+        </is>
+      </c>
+      <c r="W9" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 04: E01, E02, E03, E04, E05, E07, E08, E16b</t>
+        </is>
+      </c>
+      <c r="X9" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 05: DRS01, DRS02</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="60.6" customFormat="1" customHeight="1" s="8">
@@ -6456,25 +6535,30 @@
           <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Sadis Alvarenga Hernandez). IT and business DR scope confirmed by the DRS01 (IT Scope) and DRS02 (Business Scope) emails.</t>
         </is>
       </c>
-      <c r="T10" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications","\","/"),"01_Management_Attestation_In-Scope_Applications"),"Open folder 01: MA01")</f>
-        <v/>
-      </c>
-      <c r="U10" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"Open folder 02: BLA05, BLA06")</f>
-        <v/>
-      </c>
-      <c r="V10" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"Open folder 03: DMA02")</f>
-        <v/>
-      </c>
-      <c r="W10" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"Open folder 04: E01, E02, E03, E04, E05, E10, E16b")</f>
-        <v/>
-      </c>
-      <c r="X10" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails"),"Open folder 05: DRS01, DRS02")</f>
-        <v/>
+      <c r="T10" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 01: MA01</t>
+        </is>
+      </c>
+      <c r="U10" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 02: BLA05, BLA06</t>
+        </is>
+      </c>
+      <c r="V10" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 03: DMA02</t>
+        </is>
+      </c>
+      <c r="W10" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 04: E01, E02, E03, E04, E05, E10, E16b</t>
+        </is>
+      </c>
+      <c r="X10" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 05: DRS01, DRS02</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="60.6" customFormat="1" customHeight="1" s="8">
@@ -6602,25 +6686,30 @@
           <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Michelle Oropesa). IT and business DR scope confirmed by the DRS01 (IT Scope) and DRS02 (Business Scope) emails.</t>
         </is>
       </c>
-      <c r="T11" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications","\","/"),"01_Management_Attestation_In-Scope_Applications"),"Open folder 01: MA01")</f>
-        <v/>
-      </c>
-      <c r="U11" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"Open folder 02: BLA03, BLA04")</f>
-        <v/>
-      </c>
-      <c r="V11" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"Open folder 03: DMA02, DMA04")</f>
-        <v/>
-      </c>
-      <c r="W11" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"Open folder 04: E01, E02, E03, E04, E05, E07, E08, E16b")</f>
-        <v/>
-      </c>
-      <c r="X11" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails"),"Open folder 05: DRS01, DRS02")</f>
-        <v/>
+      <c r="T11" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 01: MA01</t>
+        </is>
+      </c>
+      <c r="U11" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 02: BLA03, BLA04</t>
+        </is>
+      </c>
+      <c r="V11" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 03: DMA02, DMA04</t>
+        </is>
+      </c>
+      <c r="W11" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 04: E01, E02, E03, E04, E05, E07, E08, E16b</t>
+        </is>
+      </c>
+      <c r="X11" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 05: DRS01, DRS02</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="60.6" customFormat="1" customHeight="1" s="8">
@@ -6818,25 +6907,30 @@
           <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Ricardo Garcia, David Marquez, Claudia Romero, Miguel Orozco, Sadis Alvarenga Hernandez, Maria del Cerro Hontanilla, Michelle Oropesa, Franklin Puentes, Martha Sullivan, Liliana Vizhnay, Victoria Fernandez, Xavier Caisapanta, Clara De Castro). IT and business DR scope confirmed by the DRS01 (IT Scope) and DRS02 (Business Scope) emails.</t>
         </is>
       </c>
-      <c r="T12" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications","\","/"),"01_Management_Attestation_In-Scope_Applications"),"Open folder 01: MA01")</f>
-        <v/>
-      </c>
-      <c r="U12" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"Open folder 02: BLA01, BLA02, BLA03, BLA04, BLA05, BLA06")</f>
-        <v/>
-      </c>
-      <c r="V12" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"Open folder 03: DMA01, DMA02, DMA03, DMA04, DMA05, DMA06, DMA07, DMA08, DMA09, DMA10, DMA11, DMA12")</f>
-        <v/>
-      </c>
-      <c r="W12" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"Open folder 04: E01, E02, E03, E04, E05, E07, E08, E09, E10, E16b")</f>
-        <v/>
-      </c>
-      <c r="X12" s="81">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails"),"Open folder 05: DRS01, DRS02")</f>
-        <v/>
+      <c r="T12" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 01: MA01</t>
+        </is>
+      </c>
+      <c r="U12" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 02: BLA01, BLA02, BLA03, BLA04, BLA05, BLA06</t>
+        </is>
+      </c>
+      <c r="V12" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 03: DMA01, DMA02, DMA03, DMA04, DMA05, DMA06, DMA07, DMA08, DMA09, DMA10, DMA11, DMA12</t>
+        </is>
+      </c>
+      <c r="W12" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 04: E01, E02, E03, E04, E05, E07, E08, E09, E10, E16b</t>
+        </is>
+      </c>
+      <c r="X12" s="81" t="inlineStr">
+        <is>
+          <t>Open folder 05: DRS01, DRS02</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="60.6" customHeight="1">
@@ -6881,28 +6975,78 @@
     <hyperlink ref="S2" location="'Application Attribute Testing'!A113" tooltip="Go to conclusion table" display="Control Sample Assessment Result (Pass/Fail)"/>
     <hyperlink ref="A3" location="'Application Attribute Testing'!A115" tooltip="Go to sample 1822 conclusion" display="'Application Attribute Testing'!A115"/>
     <hyperlink ref="R3" location="'Application Attribute Testing'!A71" tooltip="Go to evidence file reviews" display="[01 Management Attestation / In-Scope Applications]_x000a_MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png_x000a_[02 Business Line Approval Results: Email]_x000a_BLA01: BSI.IT.6.C7.3-Evidences\02_Business"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T3" display="Open folder 01: MA01" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" display="Open folder 02: BLA01" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V3" display="Open folder 03: DMA01, DMA02" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" display="Open folder 04: E01, E02, E03, E04, E05, E09, E16b" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X3" display="Open folder 05: DRS01, DRS02" r:id="rId5"/>
     <hyperlink ref="A4" location="'Application Attribute Testing'!A116" tooltip="Go to sample 1867 conclusion" display="'Application Attribute Testing'!A116"/>
     <hyperlink ref="R4" location="'Application Attribute Testing'!A71" tooltip="Go to evidence file reviews" display="[01 Management Attestation / In-Scope Applications]_x000a_MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png_x000a_[02 Business Line Approval Results: Email]_x000a_BLA01: BSI.IT.6.C7.3-Evidences\02_Business"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" display="Open folder 01: MA01" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" display="Open folder 02: BLA01" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V4" display="Open folder 03: DMA01, DMA02" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" display="Open folder 04: E01, E02, E03, E04, E05, E09, E16b" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" display="Open folder 05: DRS01, DRS02" r:id="rId10"/>
     <hyperlink ref="A5" location="'Application Attribute Testing'!A117" tooltip="Go to sample 1868 conclusion" display="'Application Attribute Testing'!A117"/>
     <hyperlink ref="R5" location="'Application Attribute Testing'!A71" tooltip="Go to evidence file reviews" display="[01 Management Attestation / In-Scope Applications]_x000a_MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png_x000a_[02 Business Line Approval Results: Email]_x000a_BLA01: BSI.IT.6.C7.3-Evidences\02_Business"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T5" display="Open folder 01: MA01" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U5" display="Open folder 02: BLA01" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V5" display="Open folder 03: DMA01, DMA02" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" display="Open folder 04: E01, E02, E03, E04, E05, E09, E16b" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X5" display="Open folder 05: DRS01, DRS02" r:id="rId15"/>
     <hyperlink ref="A6" location="'Application Attribute Testing'!A118" tooltip="Go to sample 3299 conclusion" display="'Application Attribute Testing'!A118"/>
     <hyperlink ref="R6" location="'Application Attribute Testing'!A71" tooltip="Go to evidence file reviews" display="[01 Management Attestation / In-Scope Applications]_x000a_MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png_x000a_[02 Business Line Approval Results: Email]_x000a_BLA01: BSI.IT.6.C7.3-Evidences\02_Business"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T6" display="Open folder 01: MA01" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U6" display="Open folder 02: BLA01, BLA02" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V6" display="Open folder 03: DMA01, DMA02, DMA05, DMA11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" display="Open folder 04: E01, E02, E03, E04, E05, E09, E16b" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" display="Open folder 05: DRS01, DRS02" r:id="rId20"/>
     <hyperlink ref="A7" location="'Application Attribute Testing'!A119" tooltip="Go to sample 4052 conclusion" display="'Application Attribute Testing'!A119"/>
     <hyperlink ref="R7" location="'Application Attribute Testing'!A71" tooltip="Go to evidence file reviews" display="[01 Management Attestation / In-Scope Applications]_x000a_MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png_x000a_[02 Business Line Approval Results: Email]_x000a_BLA04: BSI.IT.6.C7.3-Evidences\02_Business"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T7" display="Open folder 01: MA01" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" display="Open folder 02: BLA04" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V7" display="Open folder 03: DMA02, DMA04" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" display="Open folder 04: E01, E02, E03, E04, E05, E16b" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X7" display="Open folder 05: DRS01, DRS02" r:id="rId25"/>
     <hyperlink ref="A8" location="'Application Attribute Testing'!A120" tooltip="Go to sample 3301 conclusion" display="'Application Attribute Testing'!A120"/>
     <hyperlink ref="R8" location="'Application Attribute Testing'!A71" tooltip="Go to evidence file reviews" display="[01 Management Attestation / In-Scope Applications]_x000a_MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png_x000a_[02 Business Line Approval Results: Email]_x000a_BLA03: BSI.IT.6.C7.3-Evidences\02_Business"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T8" display="Open folder 01: MA01" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" display="Open folder 02: BLA03" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V8" display="Open folder 03: DMA02, DMA03" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" display="Open folder 04: E01, E02, E03, E04, E05, E07, E08, E16b" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X8" display="Open folder 05: DRS01, DRS02" r:id="rId30"/>
     <hyperlink ref="A9" location="'Application Attribute Testing'!A121" tooltip="Go to sample 1903 conclusion" display="'Application Attribute Testing'!A121"/>
     <hyperlink ref="R9" location="'Application Attribute Testing'!A71" tooltip="Go to evidence file reviews" display="[01 Management Attestation / In-Scope Applications]_x000a_MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png_x000a_[02 Business Line Approval Results: Email]_x000a_BLA02: BSI.IT.6.C7.3-Evidences\02_Business"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T9" display="Open folder 01: MA01" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" display="Open folder 02: BLA02, BLA03" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V9" display="Open folder 03: DMA02, DMA03, DMA05" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" display="Open folder 04: E01, E02, E03, E04, E05, E07, E08, E16b" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X9" display="Open folder 05: DRS01, DRS02" r:id="rId35"/>
     <hyperlink ref="A10" location="'Application Attribute Testing'!A122" tooltip="Go to sample 1917 conclusion" display="'Application Attribute Testing'!A122"/>
     <hyperlink ref="R10" location="'Application Attribute Testing'!A71" tooltip="Go to evidence file reviews" display="[01 Management Attestation / In-Scope Applications]_x000a_MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png_x000a_[02 Business Line Approval Results: Email]_x000a_BLA05: BSI.IT.6.C7.3-Evidences\02_Business"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T10" display="Open folder 01: MA01" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" display="Open folder 02: BLA05, BLA06" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V10" display="Open folder 03: DMA02" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" display="Open folder 04: E01, E02, E03, E04, E05, E10, E16b" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X10" display="Open folder 05: DRS01, DRS02" r:id="rId40"/>
     <hyperlink ref="A11" location="'Application Attribute Testing'!A123" tooltip="Go to sample 1936 conclusion" display="'Application Attribute Testing'!A123"/>
     <hyperlink ref="R11" location="'Application Attribute Testing'!A71" tooltip="Go to evidence file reviews" display="[01 Management Attestation / In-Scope Applications]_x000a_MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png_x000a_[02 Business Line Approval Results: Email]_x000a_BLA03: BSI.IT.6.C7.3-Evidences\02_Business"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T11" display="Open folder 01: MA01" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" display="Open folder 02: BLA03, BLA04" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V11" display="Open folder 03: DMA02, DMA04" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" display="Open folder 04: E01, E02, E03, E04, E05, E07, E08, E16b" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X11" display="Open folder 05: DRS01, DRS02" r:id="rId45"/>
     <hyperlink ref="A12" location="'Application Attribute Testing'!A124" tooltip="Go to sample 1937 conclusion" display="'Application Attribute Testing'!A124"/>
     <hyperlink ref="R12" location="'Application Attribute Testing'!A71" tooltip="Go to evidence file reviews" display="[01 Management Attestation / In-Scope Applications]_x000a_MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png_x000a_[02 Business Line Approval Results: Email]_x000a_BLA01: BSI.IT.6.C7.3-Evidences\02_Business"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T12" display="Open folder 01: MA01" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" display="Open folder 02: BLA01, BLA02, BLA03, BLA04, BLA05, BLA06" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V12" display="Open folder 03: DMA01, DMA02, DMA03, DMA04, DMA05, DMA06, DMA07, DMA08, DMA09, DMA10, DMA11, DMA12" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" display="Open folder 04: E01, E02, E03, E04, E05, E07, E08, E09, E10, E16b" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X12" display="Open folder 05: DRS01, DRS02" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId51"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7026,9 +7170,10 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B5" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
-        <v/>
+      <c r="B5" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+        </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
@@ -7183,9 +7328,10 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B9" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
-        <v/>
+      <c r="B9" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+        </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
         <is>
@@ -7340,9 +7486,10 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B13" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
-        <v/>
+      <c r="B13" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+        </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
@@ -7492,9 +7639,10 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B17" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
-        <v/>
+      <c r="B17" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+        </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
@@ -7644,9 +7792,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B21" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B21" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C21" s="33" t="inlineStr">
         <is>
@@ -7795,9 +7944,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B25" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B25" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C25" s="33" t="inlineStr">
         <is>
@@ -7947,9 +8097,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B29" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B29" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C29" s="33" t="inlineStr">
         <is>
@@ -8104,9 +8255,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B33" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B33" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C33" s="33" t="inlineStr">
         <is>
@@ -8261,9 +8413,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B37" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B37" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C37" s="33" t="inlineStr">
         <is>
@@ -8410,9 +8563,10 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B41" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
-        <v/>
+      <c r="B41" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+        </is>
       </c>
       <c r="C41" s="33" t="inlineStr">
         <is>
@@ -8468,9 +8622,10 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B42" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
-        <v/>
+      <c r="B42" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C42" s="33" t="inlineStr">
         <is>
@@ -8515,9 +8670,10 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B43" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
-        <v/>
+      <c r="B43" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+        </is>
       </c>
       <c r="C43" s="33" t="inlineStr">
         <is>
@@ -8561,9 +8717,10 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B44" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
-        <v/>
+      <c r="B44" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C44" s="33" t="inlineStr">
         <is>
@@ -8606,9 +8763,10 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B45" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
-        <v/>
+      <c r="B45" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+        </is>
       </c>
       <c r="C45" s="33" t="inlineStr">
         <is>
@@ -8741,9 +8899,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B49" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B49" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C49" s="33" t="inlineStr">
         <is>
@@ -8889,9 +9048,10 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B53" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
-        <v/>
+      <c r="B53" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+        </is>
       </c>
       <c r="C53" s="33" t="inlineStr">
         <is>
@@ -9040,9 +9200,10 @@
           <t>E05</t>
         </is>
       </c>
-      <c r="B57" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg")</f>
-        <v/>
+      <c r="B57" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+        </is>
       </c>
       <c r="C57" s="33" t="inlineStr">
         <is>
@@ -9193,9 +9354,10 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B61" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
-        <v/>
+      <c r="B61" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+        </is>
       </c>
       <c r="C61" s="33" t="inlineStr">
         <is>
@@ -9252,9 +9414,10 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B62" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
-        <v/>
+      <c r="B62" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C62" s="33" t="inlineStr">
         <is>
@@ -9299,9 +9462,10 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B63" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
-        <v/>
+      <c r="B63" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+        </is>
       </c>
       <c r="C63" s="33" t="inlineStr">
         <is>
@@ -9345,9 +9509,10 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B64" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
-        <v/>
+      <c r="B64" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C64" s="33" t="inlineStr">
         <is>
@@ -9390,9 +9555,10 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B65" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
-        <v/>
+      <c r="B65" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+        </is>
       </c>
       <c r="C65" s="33" t="inlineStr">
         <is>
@@ -9525,9 +9691,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B69" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B69" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C69" s="33" t="inlineStr">
         <is>
@@ -9657,9 +9824,10 @@
           <t>BLA01</t>
         </is>
       </c>
-      <c r="B73" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
+      <c r="B73" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
+        </is>
       </c>
       <c r="C73" s="33" t="inlineStr">
         <is>
@@ -9698,9 +9866,10 @@
           <t>BLA02</t>
         </is>
       </c>
-      <c r="B74" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
+      <c r="B74" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
+        </is>
       </c>
       <c r="C74" s="33" t="inlineStr">
         <is>
@@ -9739,9 +9908,10 @@
           <t>BLA03</t>
         </is>
       </c>
-      <c r="B75" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
+      <c r="B75" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
+        </is>
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
@@ -9780,9 +9950,10 @@
           <t>BLA04</t>
         </is>
       </c>
-      <c r="B76" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx","\","/"),"02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx")</f>
-        <v/>
+      <c r="B76" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
+        </is>
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
@@ -9821,9 +9992,10 @@
           <t>BLA05</t>
         </is>
       </c>
-      <c r="B77" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
+      <c r="B77" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
+        </is>
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
@@ -9862,9 +10034,10 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B78" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
-        <v/>
+      <c r="B78" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+        </is>
       </c>
       <c r="C78" s="33" t="inlineStr">
         <is>
@@ -9972,9 +10145,10 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B82" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
-        <v/>
+      <c r="B82" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C82" s="33" t="inlineStr">
         <is>
@@ -10008,9 +10182,10 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B83" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
-        <v/>
+      <c r="B83" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+        </is>
       </c>
       <c r="C83" s="33" t="inlineStr">
         <is>
@@ -10044,9 +10219,10 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B84" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
-        <v/>
+      <c r="B84" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C84" s="33" t="inlineStr">
         <is>
@@ -10080,9 +10256,10 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B85" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
-        <v/>
+      <c r="B85" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+        </is>
       </c>
       <c r="C85" s="33" t="inlineStr">
         <is>
@@ -10116,9 +10293,10 @@
           <t>DMA05</t>
         </is>
       </c>
-      <c r="B86" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg")</f>
-        <v/>
+      <c r="B86" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+        </is>
       </c>
       <c r="C86" s="33" t="inlineStr">
         <is>
@@ -10152,9 +10330,10 @@
           <t>DMA06</t>
         </is>
       </c>
-      <c r="B87" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg")</f>
-        <v/>
+      <c r="B87" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C87" s="33" t="inlineStr">
         <is>
@@ -10188,9 +10367,10 @@
           <t>DMA07</t>
         </is>
       </c>
-      <c r="B88" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg")</f>
-        <v/>
+      <c r="B88" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C88" s="33" t="inlineStr">
         <is>
@@ -10224,9 +10404,10 @@
           <t>DMA08</t>
         </is>
       </c>
-      <c r="B89" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg")</f>
-        <v/>
+      <c r="B89" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C89" s="33" t="inlineStr">
         <is>
@@ -10260,9 +10441,10 @@
           <t>DMA09</t>
         </is>
       </c>
-      <c r="B90" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg")</f>
-        <v/>
+      <c r="B90" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C90" s="33" t="inlineStr">
         <is>
@@ -10296,9 +10478,10 @@
           <t>DMA10</t>
         </is>
       </c>
-      <c r="B91" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml")</f>
-        <v/>
+      <c r="B91" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+        </is>
       </c>
       <c r="C91" s="33" t="inlineStr">
         <is>
@@ -10332,9 +10515,10 @@
           <t>DMA11</t>
         </is>
       </c>
-      <c r="B92" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml")</f>
-        <v/>
+      <c r="B92" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+        </is>
       </c>
       <c r="C92" s="33" t="inlineStr">
         <is>
@@ -10368,9 +10552,10 @@
           <t>DMA12</t>
         </is>
       </c>
-      <c r="B93" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml")</f>
-        <v/>
+      <c r="B93" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+        </is>
       </c>
       <c r="C93" s="33" t="inlineStr">
         <is>
@@ -10404,9 +10589,10 @@
           <t>DMA13</t>
         </is>
       </c>
-      <c r="B94" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml")</f>
-        <v/>
+      <c r="B94" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
+        </is>
       </c>
       <c r="C94" s="33" t="inlineStr">
         <is>
@@ -10499,9 +10685,10 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B98" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
-        <v/>
+      <c r="B98" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+        </is>
       </c>
       <c r="C98" s="33" t="inlineStr">
         <is>
@@ -10535,9 +10722,10 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B99" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
-        <v/>
+      <c r="B99" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+        </is>
       </c>
       <c r="C99" s="33" t="inlineStr">
         <is>
@@ -10571,9 +10759,10 @@
           <t>E02</t>
         </is>
       </c>
-      <c r="B100" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg")</f>
-        <v/>
+      <c r="B100" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+        </is>
       </c>
       <c r="C100" s="33" t="inlineStr">
         <is>
@@ -10607,9 +10796,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B101" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B101" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C101" s="33" t="inlineStr">
         <is>
@@ -10643,9 +10833,10 @@
           <t>E04</t>
         </is>
       </c>
-      <c r="B102" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg")</f>
-        <v/>
+      <c r="B102" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+        </is>
       </c>
       <c r="C102" s="33" t="inlineStr">
         <is>
@@ -10679,9 +10870,10 @@
           <t>E05</t>
         </is>
       </c>
-      <c r="B103" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg")</f>
-        <v/>
+      <c r="B103" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+        </is>
       </c>
       <c r="C103" s="33" t="inlineStr">
         <is>
@@ -10715,9 +10907,10 @@
           <t>E07</t>
         </is>
       </c>
-      <c r="B104" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg")</f>
-        <v/>
+      <c r="B104" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+        </is>
       </c>
       <c r="C104" s="33" t="inlineStr">
         <is>
@@ -10751,9 +10944,10 @@
           <t>E08</t>
         </is>
       </c>
-      <c r="B105" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg")</f>
-        <v/>
+      <c r="B105" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+        </is>
       </c>
       <c r="C105" s="33" t="inlineStr">
         <is>
@@ -10787,9 +10981,10 @@
           <t>E09</t>
         </is>
       </c>
-      <c r="B106" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg")</f>
-        <v/>
+      <c r="B106" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+        </is>
       </c>
       <c r="C106" s="33" t="inlineStr">
         <is>
@@ -10823,9 +11018,10 @@
           <t>E10</t>
         </is>
       </c>
-      <c r="B107" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg")</f>
-        <v/>
+      <c r="B107" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+        </is>
       </c>
       <c r="C107" s="33" t="inlineStr">
         <is>
@@ -10859,9 +11055,10 @@
           <t>E13</t>
         </is>
       </c>
-      <c r="B108" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg")</f>
-        <v/>
+      <c r="B108" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
+        </is>
       </c>
       <c r="C108" s="33" t="inlineStr">
         <is>
@@ -10895,9 +11092,10 @@
           <t>E16b</t>
         </is>
       </c>
-      <c r="B109" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx")</f>
-        <v/>
+      <c r="B109" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+        </is>
       </c>
       <c r="C109" s="33" t="inlineStr">
         <is>
@@ -11672,42 +11870,96 @@
   <hyperlinks>
     <hyperlink ref="A3" location="'Application Attribute Testing-1'!B2" tooltip="Back to column B on Application Attribute Testing-1" display="1. Application Name (column B): review of evidence files and results"/>
     <hyperlink ref="A5" location="'Application Attribute Testing'!A98" tooltip="Go to MA01 evidence review" display="MA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png" r:id="rId1"/>
     <hyperlink ref="A7" location="'Application Attribute Testing-1'!C2" tooltip="Back to column C on Application Attribute Testing-1" display="2. Applications in Scope Identified (column C): review of evidence files and results"/>
     <hyperlink ref="A9" location="'Application Attribute Testing'!A98" tooltip="Go to MA01 evidence review" display="MA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png" r:id="rId2"/>
     <hyperlink ref="A11" location="'Application Attribute Testing-1'!D2" tooltip="Back to column D on Application Attribute Testing-1" display="3. IT DR exercise name (column D): review of evidence files and results"/>
     <hyperlink ref="A13" location="'Application Attribute Testing'!A99" tooltip="Go to E01 evidence review" display="E01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId3"/>
     <hyperlink ref="A15" location="'Application Attribute Testing-1'!E2" tooltip="Back to column E on Application Attribute Testing-1" display="4. IT DR exercise name, was the exercise annually executed? (column E): review of evidence files and results"/>
     <hyperlink ref="A17" location="'Application Attribute Testing'!A99" tooltip="Go to E01 evidence review" display="E01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId4"/>
     <hyperlink ref="A19" location="'Application Attribute Testing-1'!F2" tooltip="Back to column F on Application Attribute Testing-1" display="5. Business Tester (column F): review of evidence files and results"/>
     <hyperlink ref="A21" location="'Application Attribute Testing'!A101" tooltip="Go to E03 evidence review" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId5"/>
     <hyperlink ref="A23" location="'Application Attribute Testing-1'!G2" tooltip="Back to column G on Application Attribute Testing-1" display="6. Business Data validation (column G): review of evidence files and results"/>
     <hyperlink ref="A25" location="'Application Attribute Testing'!A101" tooltip="Go to E03 evidence review" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId6"/>
     <hyperlink ref="A27" location="'Application Attribute Testing-1'!H2" tooltip="Back to column H on Application Attribute Testing-1" display="7. Business line manager name (column H): review of evidence files and results"/>
     <hyperlink ref="A29" location="'Application Attribute Testing'!A101" tooltip="Go to E03 evidence review" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId7"/>
     <hyperlink ref="A31" location="'Application Attribute Testing-1'!I2" tooltip="Back to column I on Application Attribute Testing-1" display="8. Business line manager approval dates (column I): review of evidence files and results"/>
     <hyperlink ref="A33" location="'Application Attribute Testing'!A101" tooltip="Go to E03 evidence review" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId8"/>
     <hyperlink ref="A35" location="'Application Attribute Testing-1'!J2" tooltip="Back to column J on Application Attribute Testing-1" display="9. DIV Test procedures listed within the Test results document (column J): review of evidence files and results"/>
     <hyperlink ref="A37" location="'Application Attribute Testing'!A101" tooltip="Go to E03 evidence review" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId9"/>
     <hyperlink ref="A39" location="'Application Attribute Testing-1'!K2" tooltip="Back to column K on Application Attribute Testing-1" display="10. Emails showing Business line manager approval of DIV testing results (column K): review of evidence files and results"/>
     <hyperlink ref="A41" location="'Application Attribute Testing'!A78" tooltip="Go to BLA06 evidence review" display="BLA06"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId10"/>
     <hyperlink ref="A42" location="'Application Attribute Testing'!A82" tooltip="Go to DMA01 evidence review" display="DMA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId11"/>
     <hyperlink ref="A43" location="'Application Attribute Testing'!A83" tooltip="Go to DMA02 evidence review" display="DMA02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId12"/>
     <hyperlink ref="A44" location="'Application Attribute Testing'!A84" tooltip="Go to DMA03 evidence review" display="DMA03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId13"/>
     <hyperlink ref="A45" location="'Application Attribute Testing'!A85" tooltip="Go to DMA04 evidence review" display="DMA04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId14"/>
     <hyperlink ref="A47" location="'Application Attribute Testing-1'!L2" tooltip="Back to column L on Application Attribute Testing-1" display="11. All evidence of Data Integrity DR test in BCIC (column L): review of evidence files and results"/>
     <hyperlink ref="A49" location="'Application Attribute Testing'!A101" tooltip="Go to E03 evidence review" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId15"/>
     <hyperlink ref="A51" location="'Application Attribute Testing-1'!M2" tooltip="Back to column M on Application Attribute Testing-1" display="12. Annual Testing Executed (column M): review of evidence files and results"/>
     <hyperlink ref="A53" location="'Application Attribute Testing'!A99" tooltip="Go to E01 evidence review" display="E01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId16"/>
     <hyperlink ref="A55" location="'Application Attribute Testing-1'!N2" tooltip="Back to column N on Application Attribute Testing-1" display="13. Data Integrity Validation Performed by IT DR Team (column N): review of evidence files and results"/>
     <hyperlink ref="A57" location="'Application Attribute Testing'!A103" tooltip="Go to E05 evidence review" display="E05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg" r:id="rId17"/>
     <hyperlink ref="A59" location="'Application Attribute Testing-1'!O2" tooltip="Back to column O on Application Attribute Testing-1" display="14. Business Line Approval of Results (column O): review of evidence files and results"/>
     <hyperlink ref="A61" location="'Application Attribute Testing'!A78" tooltip="Go to BLA06 evidence review" display="BLA06"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId18"/>
     <hyperlink ref="A62" location="'Application Attribute Testing'!A82" tooltip="Go to DMA01 evidence review" display="DMA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId19"/>
     <hyperlink ref="A63" location="'Application Attribute Testing'!A83" tooltip="Go to DMA02 evidence review" display="DMA02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId20"/>
     <hyperlink ref="A64" location="'Application Attribute Testing'!A84" tooltip="Go to DMA03 evidence review" display="DMA03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId21"/>
     <hyperlink ref="A65" location="'Application Attribute Testing'!A85" tooltip="Go to DMA04 evidence review" display="DMA04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId22"/>
     <hyperlink ref="A67" location="'Application Attribute Testing-1'!P2" tooltip="Back to column P on Application Attribute Testing-1" display="15. Results Documented in BCMS (column P): review of evidence files and results"/>
     <hyperlink ref="A69" location="'Application Attribute Testing'!A101" tooltip="Go to E03 evidence review" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx" r:id="rId54"/>
     <hyperlink ref="A115" location="'Application Attribute Testing-1'!A3" tooltip="Back to sample 1822 on Application Attribute Testing-1" display="1822"/>
     <hyperlink ref="B115" location="'Application Attribute Testing-1'!A3" tooltip="Back to sample 1822 on Application Attribute Testing-1" display="ACH Express"/>
     <hyperlink ref="A116" location="'Application Attribute Testing-1'!A4" tooltip="Back to sample 1867 on Application Attribute Testing-1" display="1867"/>
@@ -12011,9 +12263,10 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B5" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
-        <v/>
+      <c r="B5" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+        </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
@@ -12314,9 +12567,10 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B9" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
-        <v/>
+      <c r="B9" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+        </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
         <is>
@@ -12419,9 +12673,10 @@
           <t>DRS01</t>
         </is>
       </c>
-      <c r="B10" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B10" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C10" s="33" t="inlineStr">
         <is>
@@ -12471,9 +12726,10 @@
           <t>DRS02</t>
         </is>
       </c>
-      <c r="B11" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B11" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C11" s="33" t="inlineStr">
         <is>
@@ -12730,9 +12986,10 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B15" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
-        <v/>
+      <c r="B15" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+        </is>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
@@ -12827,9 +13084,10 @@
           <t>DRS01</t>
         </is>
       </c>
-      <c r="B16" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B16" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
@@ -12879,9 +13137,10 @@
           <t>DRS02</t>
         </is>
       </c>
-      <c r="B17" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B17" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
@@ -13129,9 +13388,10 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B21" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
-        <v/>
+      <c r="B21" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+        </is>
       </c>
       <c r="C21" s="33" t="inlineStr">
         <is>
@@ -13227,9 +13487,10 @@
           <t>DRS01</t>
         </is>
       </c>
-      <c r="B22" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B22" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
@@ -13279,9 +13540,10 @@
           <t>DRS02</t>
         </is>
       </c>
-      <c r="B23" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B23" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C23" s="33" t="inlineStr">
         <is>
@@ -13529,9 +13791,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B27" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B27" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C27" s="33" t="inlineStr">
         <is>
@@ -13823,9 +14086,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B31" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B31" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C31" s="33" t="inlineStr">
         <is>
@@ -14117,9 +14381,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B35" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B35" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C35" s="33" t="inlineStr">
         <is>
@@ -14213,9 +14478,10 @@
           <t>DRS02</t>
         </is>
       </c>
-      <c r="B36" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B36" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C36" s="33" t="inlineStr">
         <is>
@@ -14473,9 +14739,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B40" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B40" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C40" s="33" t="inlineStr">
         <is>
@@ -14767,9 +15034,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B44" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B44" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C44" s="33" t="inlineStr">
         <is>
@@ -15061,9 +15329,10 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B48" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
-        <v/>
+      <c r="B48" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+        </is>
       </c>
       <c r="C48" s="33" t="inlineStr">
         <is>
@@ -15149,9 +15418,10 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B49" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
-        <v/>
+      <c r="B49" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C49" s="33" t="inlineStr">
         <is>
@@ -15240,9 +15510,10 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B50" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
-        <v/>
+      <c r="B50" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+        </is>
       </c>
       <c r="C50" s="33" t="inlineStr">
         <is>
@@ -15330,9 +15601,10 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B51" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
-        <v/>
+      <c r="B51" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C51" s="33" t="inlineStr">
         <is>
@@ -15419,9 +15691,10 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B52" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
-        <v/>
+      <c r="B52" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+        </is>
       </c>
       <c r="C52" s="33" t="inlineStr">
         <is>
@@ -15706,9 +15979,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B56" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B56" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C56" s="33" t="inlineStr">
         <is>
@@ -16000,9 +16274,10 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B60" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
-        <v/>
+      <c r="B60" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+        </is>
       </c>
       <c r="C60" s="33" t="inlineStr">
         <is>
@@ -16098,9 +16373,10 @@
           <t>DRS01</t>
         </is>
       </c>
-      <c r="B61" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B61" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C61" s="33" t="inlineStr">
         <is>
@@ -16150,9 +16426,10 @@
           <t>DRS02</t>
         </is>
       </c>
-      <c r="B62" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B62" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C62" s="33" t="inlineStr">
         <is>
@@ -16400,9 +16677,10 @@
           <t>E05</t>
         </is>
       </c>
-      <c r="B66" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg")</f>
-        <v/>
+      <c r="B66" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+        </is>
       </c>
       <c r="C66" s="33" t="inlineStr">
         <is>
@@ -16496,9 +16774,10 @@
           <t>DRS01</t>
         </is>
       </c>
-      <c r="B67" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B67" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C67" s="33" t="inlineStr">
         <is>
@@ -16548,9 +16827,10 @@
           <t>DRS02</t>
         </is>
       </c>
-      <c r="B68" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B68" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C68" s="33" t="inlineStr">
         <is>
@@ -16798,9 +17078,10 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B72" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
-        <v/>
+      <c r="B72" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+        </is>
       </c>
       <c r="C72" s="33" t="inlineStr">
         <is>
@@ -16886,9 +17167,10 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B73" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
-        <v/>
+      <c r="B73" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C73" s="33" t="inlineStr">
         <is>
@@ -16977,9 +17259,10 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B74" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
-        <v/>
+      <c r="B74" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+        </is>
       </c>
       <c r="C74" s="33" t="inlineStr">
         <is>
@@ -17067,9 +17350,10 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B75" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
-        <v/>
+      <c r="B75" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
@@ -17156,9 +17440,10 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B76" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
-        <v/>
+      <c r="B76" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+        </is>
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
@@ -17245,9 +17530,10 @@
           <t>DRS02</t>
         </is>
       </c>
-      <c r="B77" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B77" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
@@ -17495,9 +17781,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B81" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B81" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C81" s="33" t="inlineStr">
         <is>
@@ -17789,9 +18076,10 @@
           <t>BLA01</t>
         </is>
       </c>
-      <c r="B85" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
+      <c r="B85" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
+        </is>
       </c>
       <c r="C85" s="33" t="inlineStr">
         <is>
@@ -17874,9 +18162,10 @@
           <t>BLA02</t>
         </is>
       </c>
-      <c r="B86" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
+      <c r="B86" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
+        </is>
       </c>
       <c r="C86" s="33" t="inlineStr">
         <is>
@@ -17959,9 +18248,10 @@
           <t>BLA03</t>
         </is>
       </c>
-      <c r="B87" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
+      <c r="B87" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
+        </is>
       </c>
       <c r="C87" s="33" t="inlineStr">
         <is>
@@ -18044,9 +18334,10 @@
           <t>BLA04</t>
         </is>
       </c>
-      <c r="B88" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx","\","/"),"02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx")</f>
-        <v/>
+      <c r="B88" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
+        </is>
       </c>
       <c r="C88" s="33" t="inlineStr">
         <is>
@@ -18129,9 +18420,10 @@
           <t>BLA05</t>
         </is>
       </c>
-      <c r="B89" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
+      <c r="B89" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
+        </is>
       </c>
       <c r="C89" s="33" t="inlineStr">
         <is>
@@ -18214,9 +18506,10 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B90" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
-        <v/>
+      <c r="B90" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+        </is>
       </c>
       <c r="C90" s="33" t="inlineStr">
         <is>
@@ -18497,9 +18790,10 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B94" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
-        <v/>
+      <c r="B94" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C94" s="33" t="inlineStr">
         <is>
@@ -18582,9 +18876,10 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B95" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
-        <v/>
+      <c r="B95" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+        </is>
       </c>
       <c r="C95" s="33" t="inlineStr">
         <is>
@@ -18667,9 +18962,10 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B96" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
-        <v/>
+      <c r="B96" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C96" s="33" t="inlineStr">
         <is>
@@ -18752,9 +19048,10 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B97" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
-        <v/>
+      <c r="B97" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+        </is>
       </c>
       <c r="C97" s="33" t="inlineStr">
         <is>
@@ -18837,9 +19134,10 @@
           <t>DMA05</t>
         </is>
       </c>
-      <c r="B98" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg")</f>
-        <v/>
+      <c r="B98" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+        </is>
       </c>
       <c r="C98" s="33" t="inlineStr">
         <is>
@@ -18922,9 +19220,10 @@
           <t>DMA06</t>
         </is>
       </c>
-      <c r="B99" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg")</f>
-        <v/>
+      <c r="B99" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C99" s="33" t="inlineStr">
         <is>
@@ -19007,9 +19306,10 @@
           <t>DMA07</t>
         </is>
       </c>
-      <c r="B100" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg")</f>
-        <v/>
+      <c r="B100" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C100" s="33" t="inlineStr">
         <is>
@@ -19092,9 +19392,10 @@
           <t>DMA08</t>
         </is>
       </c>
-      <c r="B101" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg")</f>
-        <v/>
+      <c r="B101" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C101" s="33" t="inlineStr">
         <is>
@@ -19177,9 +19478,10 @@
           <t>DMA09</t>
         </is>
       </c>
-      <c r="B102" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg")</f>
-        <v/>
+      <c r="B102" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C102" s="33" t="inlineStr">
         <is>
@@ -19262,9 +19564,10 @@
           <t>DMA10</t>
         </is>
       </c>
-      <c r="B103" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml")</f>
-        <v/>
+      <c r="B103" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+        </is>
       </c>
       <c r="C103" s="33" t="inlineStr">
         <is>
@@ -19347,9 +19650,10 @@
           <t>DMA11</t>
         </is>
       </c>
-      <c r="B104" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml")</f>
-        <v/>
+      <c r="B104" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+        </is>
       </c>
       <c r="C104" s="33" t="inlineStr">
         <is>
@@ -19432,9 +19736,10 @@
           <t>DMA12</t>
         </is>
       </c>
-      <c r="B105" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml")</f>
-        <v/>
+      <c r="B105" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+        </is>
       </c>
       <c r="C105" s="33" t="inlineStr">
         <is>
@@ -19517,9 +19822,10 @@
           <t>DMA13</t>
         </is>
       </c>
-      <c r="B106" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml")</f>
-        <v/>
+      <c r="B106" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
+        </is>
       </c>
       <c r="C106" s="33" t="inlineStr">
         <is>
@@ -19800,9 +20106,10 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B110" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
-        <v/>
+      <c r="B110" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+        </is>
       </c>
       <c r="C110" s="33" t="inlineStr">
         <is>
@@ -19885,9 +20192,10 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B111" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
-        <v/>
+      <c r="B111" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+        </is>
       </c>
       <c r="C111" s="33" t="inlineStr">
         <is>
@@ -19970,9 +20278,10 @@
           <t>E02</t>
         </is>
       </c>
-      <c r="B112" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg")</f>
-        <v/>
+      <c r="B112" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+        </is>
       </c>
       <c r="C112" s="33" t="inlineStr">
         <is>
@@ -20055,9 +20364,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B113" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B113" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C113" s="33" t="inlineStr">
         <is>
@@ -20140,9 +20450,10 @@
           <t>E04</t>
         </is>
       </c>
-      <c r="B114" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg")</f>
-        <v/>
+      <c r="B114" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+        </is>
       </c>
       <c r="C114" s="33" t="inlineStr">
         <is>
@@ -20225,9 +20536,10 @@
           <t>E05</t>
         </is>
       </c>
-      <c r="B115" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg")</f>
-        <v/>
+      <c r="B115" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+        </is>
       </c>
       <c r="C115" s="33" t="inlineStr">
         <is>
@@ -20310,9 +20622,10 @@
           <t>E07</t>
         </is>
       </c>
-      <c r="B116" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg")</f>
-        <v/>
+      <c r="B116" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+        </is>
       </c>
       <c r="C116" s="33" t="inlineStr">
         <is>
@@ -20395,9 +20708,10 @@
           <t>E08</t>
         </is>
       </c>
-      <c r="B117" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg")</f>
-        <v/>
+      <c r="B117" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+        </is>
       </c>
       <c r="C117" s="33" t="inlineStr">
         <is>
@@ -20480,9 +20794,10 @@
           <t>E09</t>
         </is>
       </c>
-      <c r="B118" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg")</f>
-        <v/>
+      <c r="B118" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+        </is>
       </c>
       <c r="C118" s="33" t="inlineStr">
         <is>
@@ -20565,9 +20880,10 @@
           <t>E10</t>
         </is>
       </c>
-      <c r="B119" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg")</f>
-        <v/>
+      <c r="B119" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+        </is>
       </c>
       <c r="C119" s="33" t="inlineStr">
         <is>
@@ -20650,9 +20966,10 @@
           <t>E13</t>
         </is>
       </c>
-      <c r="B120" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg")</f>
-        <v/>
+      <c r="B120" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
+        </is>
       </c>
       <c r="C120" s="33" t="inlineStr">
         <is>
@@ -20735,9 +21052,10 @@
           <t>E16b</t>
         </is>
       </c>
-      <c r="B121" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx")</f>
-        <v/>
+      <c r="B121" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+        </is>
       </c>
       <c r="C121" s="33" t="inlineStr">
         <is>
@@ -20877,9 +21195,10 @@
           <t>DRS01</t>
         </is>
       </c>
-      <c r="B125" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B125" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C125" s="33" t="inlineStr">
         <is>
@@ -20918,9 +21237,10 @@
           <t>DRS02</t>
         </is>
       </c>
-      <c r="B126" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B126" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C126" s="33" t="inlineStr">
         <is>
@@ -20978,56 +21298,124 @@
   <hyperlinks>
     <hyperlink ref="A3" location="'Application Attribute Testing-1'!B2" tooltip="Back to column B on Application Attribute Testing-1" display="1. Application Name (column B): review of evidence files and results"/>
     <hyperlink ref="A5" location="'Testing Attributes Testing -2'!A110" tooltip="Go to MA01 evidence review" display="MA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png" r:id="rId1"/>
     <hyperlink ref="A7" location="'Application Attribute Testing-1'!C2" tooltip="Back to column C on Application Attribute Testing-1" display="2. Applications in Scope Identified (column C): review of evidence files and results"/>
     <hyperlink ref="A9" location="'Testing Attributes Testing -2'!A110" tooltip="Go to MA01 evidence review" display="MA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png" r:id="rId2"/>
     <hyperlink ref="A10" location="'Testing Attributes Testing -2'!A125" display="DRS01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId3"/>
     <hyperlink ref="A11" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId4"/>
     <hyperlink ref="A13" location="'Application Attribute Testing-1'!D2" tooltip="Back to column D on Application Attribute Testing-1" display="3. IT DR exercise name (column D): review of evidence files and results"/>
     <hyperlink ref="A15" location="'Testing Attributes Testing -2'!A111" tooltip="Go to E01 evidence review" display="E01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId5"/>
     <hyperlink ref="A16" location="'Testing Attributes Testing -2'!A125" display="DRS01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId6"/>
     <hyperlink ref="A17" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId7"/>
     <hyperlink ref="A19" location="'Application Attribute Testing-1'!E2" tooltip="Back to column E on Application Attribute Testing-1" display="4. IT DR exercise name, was the exercise annually executed? (column E): review of evidence files and results"/>
     <hyperlink ref="A21" location="'Testing Attributes Testing -2'!A111" tooltip="Go to E01 evidence review" display="E01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId8"/>
     <hyperlink ref="A22" location="'Testing Attributes Testing -2'!A125" display="DRS01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId9"/>
     <hyperlink ref="A23" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId10"/>
     <hyperlink ref="A25" location="'Application Attribute Testing-1'!F2" tooltip="Back to column F on Application Attribute Testing-1" display="5. Business Tester (column F): review of evidence files and results"/>
     <hyperlink ref="A27" location="'Testing Attributes Testing -2'!A113" tooltip="Go to E03 evidence review" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId11"/>
     <hyperlink ref="A29" location="'Application Attribute Testing-1'!G2" tooltip="Back to column G on Application Attribute Testing-1" display="6. Business Data validation (column G): review of evidence files and results"/>
     <hyperlink ref="A31" location="'Testing Attributes Testing -2'!A113" tooltip="Go to E03 evidence review" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId12"/>
     <hyperlink ref="A33" location="'Application Attribute Testing-1'!H2" tooltip="Back to column H on Application Attribute Testing-1" display="7. Business line manager name (column H): review of evidence files and results"/>
     <hyperlink ref="A35" location="'Testing Attributes Testing -2'!A113" tooltip="Go to E03 evidence review" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId13"/>
     <hyperlink ref="A36" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId14"/>
     <hyperlink ref="A38" location="'Application Attribute Testing-1'!I2" tooltip="Back to column I on Application Attribute Testing-1" display="8. Business line manager approval dates (column I): review of evidence files and results"/>
     <hyperlink ref="A40" location="'Testing Attributes Testing -2'!A113" tooltip="Go to E03 evidence review" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId15"/>
     <hyperlink ref="A42" location="'Application Attribute Testing-1'!J2" tooltip="Back to column J on Application Attribute Testing-1" display="9. DIV Test procedures listed within the Test results document (column J): review of evidence files and results"/>
     <hyperlink ref="A44" location="'Testing Attributes Testing -2'!A113" tooltip="Go to E03 evidence review" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId16"/>
     <hyperlink ref="A46" location="'Application Attribute Testing-1'!K2" tooltip="Back to column K on Application Attribute Testing-1" display="10. Emails showing Business line manager approval of DIV testing results (column K): review of evidence files and results"/>
     <hyperlink ref="A48" location="'Testing Attributes Testing -2'!A90" tooltip="Go to BLA06 evidence review" display="BLA06"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId17"/>
     <hyperlink ref="A49" location="'Testing Attributes Testing -2'!A94" tooltip="Go to DMA01 evidence review" display="DMA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId18"/>
     <hyperlink ref="A50" location="'Testing Attributes Testing -2'!A95" tooltip="Go to DMA02 evidence review" display="DMA02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId19"/>
     <hyperlink ref="A51" location="'Testing Attributes Testing -2'!A96" tooltip="Go to DMA03 evidence review" display="DMA03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId20"/>
     <hyperlink ref="A52" location="'Testing Attributes Testing -2'!A97" tooltip="Go to DMA04 evidence review" display="DMA04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId21"/>
     <hyperlink ref="A54" location="'Application Attribute Testing-1'!L2" tooltip="Back to column L on Application Attribute Testing-1" display="11. All evidence of Data Integrity DR test in BCIC (column L): review of evidence files and results"/>
     <hyperlink ref="A56" location="'Testing Attributes Testing -2'!A113" tooltip="Go to E03 evidence review" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId22"/>
     <hyperlink ref="A58" location="'Application Attribute Testing-1'!M2" tooltip="Back to column M on Application Attribute Testing-1" display="12. Annual Testing Executed (column M): review of evidence files and results"/>
     <hyperlink ref="A60" location="'Testing Attributes Testing -2'!A111" tooltip="Go to E01 evidence review" display="E01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId23"/>
     <hyperlink ref="A61" location="'Testing Attributes Testing -2'!A125" display="DRS01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId24"/>
     <hyperlink ref="A62" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId25"/>
     <hyperlink ref="A64" location="'Application Attribute Testing-1'!N2" tooltip="Back to column N on Application Attribute Testing-1" display="13. Data Integrity Validation Performed by IT DR Team (column N): review of evidence files and results"/>
     <hyperlink ref="A66" location="'Testing Attributes Testing -2'!A115" tooltip="Go to E05 evidence review" display="E05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg" r:id="rId26"/>
     <hyperlink ref="A67" location="'Testing Attributes Testing -2'!A125" display="DRS01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId27"/>
     <hyperlink ref="A68" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId28"/>
     <hyperlink ref="A70" location="'Application Attribute Testing-1'!O2" tooltip="Back to column O on Application Attribute Testing-1" display="14. Business Line Approval of Results (column O): review of evidence files and results"/>
     <hyperlink ref="A72" location="'Testing Attributes Testing -2'!A90" tooltip="Go to BLA06 evidence review" display="BLA06"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId29"/>
     <hyperlink ref="A73" location="'Testing Attributes Testing -2'!A94" tooltip="Go to DMA01 evidence review" display="DMA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId30"/>
     <hyperlink ref="A74" location="'Testing Attributes Testing -2'!A95" tooltip="Go to DMA02 evidence review" display="DMA02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId31"/>
     <hyperlink ref="A75" location="'Testing Attributes Testing -2'!A96" tooltip="Go to DMA03 evidence review" display="DMA03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId32"/>
     <hyperlink ref="A76" location="'Testing Attributes Testing -2'!A97" tooltip="Go to DMA04 evidence review" display="DMA04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId33"/>
     <hyperlink ref="A77" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId34"/>
     <hyperlink ref="A79" location="'Application Attribute Testing-1'!P2" tooltip="Back to column P on Application Attribute Testing-1" display="15. Results Documented in BCMS (column P): review of evidence files and results"/>
     <hyperlink ref="A81" location="'Testing Attributes Testing -2'!A113" tooltip="Go to E03 evidence review" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx" r:id="rId66"/>
     <hyperlink ref="A125" location="'Application Attribute Testing-1'!R3" display="DRS01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId67"/>
     <hyperlink ref="A126" location="'Application Attribute Testing-1'!R3" display="DRS02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -22473,9 +22861,10 @@
           <t>BLA01</t>
         </is>
       </c>
-      <c r="B3" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
+      <c r="B3" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
+        </is>
       </c>
       <c r="C3" s="33" t="inlineStr">
         <is>
@@ -22564,9 +22953,10 @@
           <t>BLA02</t>
         </is>
       </c>
-      <c r="B4" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
+      <c r="B4" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
+        </is>
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
@@ -22655,9 +23045,10 @@
           <t>BLA03</t>
         </is>
       </c>
-      <c r="B5" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
+      <c r="B5" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
+        </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
@@ -22746,9 +23137,10 @@
           <t>BLA04</t>
         </is>
       </c>
-      <c r="B6" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx","\","/"),"02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx")</f>
-        <v/>
+      <c r="B6" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
+        </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
@@ -22837,9 +23229,10 @@
           <t>BLA05</t>
         </is>
       </c>
-      <c r="B7" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
+      <c r="B7" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
+        </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
@@ -22928,9 +23321,10 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B8" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
-        <v/>
+      <c r="B8" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+        </is>
       </c>
       <c r="C8" s="33" t="inlineStr">
         <is>
@@ -23016,9 +23410,10 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B9" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
-        <v/>
+      <c r="B9" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
         <is>
@@ -23104,9 +23499,10 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B10" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
-        <v/>
+      <c r="B10" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+        </is>
       </c>
       <c r="C10" s="33" t="inlineStr">
         <is>
@@ -23197,9 +23593,10 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B11" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
-        <v/>
+      <c r="B11" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C11" s="33" t="inlineStr">
         <is>
@@ -23285,9 +23682,10 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B12" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
-        <v/>
+      <c r="B12" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+        </is>
       </c>
       <c r="C12" s="33" t="inlineStr">
         <is>
@@ -23373,9 +23771,10 @@
           <t>DMA05</t>
         </is>
       </c>
-      <c r="B13" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg")</f>
-        <v/>
+      <c r="B13" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+        </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
@@ -23461,9 +23860,10 @@
           <t>DMA06</t>
         </is>
       </c>
-      <c r="B14" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg")</f>
-        <v/>
+      <c r="B14" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C14" s="33" t="inlineStr">
         <is>
@@ -23549,9 +23949,10 @@
           <t>DMA07</t>
         </is>
       </c>
-      <c r="B15" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg")</f>
-        <v/>
+      <c r="B15" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
@@ -23637,9 +24038,10 @@
           <t>DMA08</t>
         </is>
       </c>
-      <c r="B16" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg")</f>
-        <v/>
+      <c r="B16" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
@@ -23725,9 +24127,10 @@
           <t>DMA09</t>
         </is>
       </c>
-      <c r="B17" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg")</f>
-        <v/>
+      <c r="B17" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+        </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
@@ -23813,9 +24216,10 @@
           <t>DMA10</t>
         </is>
       </c>
-      <c r="B18" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml")</f>
-        <v/>
+      <c r="B18" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+        </is>
       </c>
       <c r="C18" s="33" t="inlineStr">
         <is>
@@ -23901,9 +24305,10 @@
           <t>DMA11</t>
         </is>
       </c>
-      <c r="B19" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml")</f>
-        <v/>
+      <c r="B19" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+        </is>
       </c>
       <c r="C19" s="33" t="inlineStr">
         <is>
@@ -23989,9 +24394,10 @@
           <t>DMA12</t>
         </is>
       </c>
-      <c r="B20" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml")</f>
-        <v/>
+      <c r="B20" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+        </is>
       </c>
       <c r="C20" s="33" t="inlineStr">
         <is>
@@ -24077,9 +24483,10 @@
           <t>DMA13</t>
         </is>
       </c>
-      <c r="B21" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml")</f>
-        <v/>
+      <c r="B21" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
+        </is>
       </c>
       <c r="C21" s="33" t="inlineStr">
         <is>
@@ -24158,9 +24565,10 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B22" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
-        <v/>
+      <c r="B22" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+        </is>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
@@ -24245,9 +24653,10 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B23" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
-        <v/>
+      <c r="B23" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+        </is>
       </c>
       <c r="C23" s="33" t="inlineStr">
         <is>
@@ -24335,9 +24744,10 @@
           <t>E02</t>
         </is>
       </c>
-      <c r="B24" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg")</f>
-        <v/>
+      <c r="B24" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+        </is>
       </c>
       <c r="C24" s="33" t="inlineStr">
         <is>
@@ -24422,9 +24832,10 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B25" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
+      <c r="B25" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
       </c>
       <c r="C25" s="33" t="inlineStr">
         <is>
@@ -24518,9 +24929,10 @@
           <t>E04</t>
         </is>
       </c>
-      <c r="B26" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg")</f>
-        <v/>
+      <c r="B26" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+        </is>
       </c>
       <c r="C26" s="33" t="inlineStr">
         <is>
@@ -24608,9 +25020,10 @@
           <t>E05</t>
         </is>
       </c>
-      <c r="B27" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg")</f>
-        <v/>
+      <c r="B27" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+        </is>
       </c>
       <c r="C27" s="33" t="inlineStr">
         <is>
@@ -24694,9 +25107,10 @@
           <t>E07</t>
         </is>
       </c>
-      <c r="B28" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg")</f>
-        <v/>
+      <c r="B28" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+        </is>
       </c>
       <c r="C28" s="33" t="inlineStr">
         <is>
@@ -24779,9 +25193,10 @@
           <t>E08</t>
         </is>
       </c>
-      <c r="B29" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg")</f>
-        <v/>
+      <c r="B29" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+        </is>
       </c>
       <c r="C29" s="33" t="inlineStr">
         <is>
@@ -24865,9 +25280,10 @@
           <t>E09</t>
         </is>
       </c>
-      <c r="B30" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg")</f>
-        <v/>
+      <c r="B30" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+        </is>
       </c>
       <c r="C30" s="33" t="inlineStr">
         <is>
@@ -24956,9 +25372,10 @@
           <t>E10</t>
         </is>
       </c>
-      <c r="B31" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg")</f>
-        <v/>
+      <c r="B31" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+        </is>
       </c>
       <c r="C31" s="33" t="inlineStr">
         <is>
@@ -25041,9 +25458,10 @@
           <t>E13</t>
         </is>
       </c>
-      <c r="B32" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg")</f>
-        <v/>
+      <c r="B32" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
+        </is>
       </c>
       <c r="C32" s="33" t="inlineStr">
         <is>
@@ -25122,9 +25540,10 @@
           <t>E16b</t>
         </is>
       </c>
-      <c r="B33" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx")</f>
-        <v/>
+      <c r="B33" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+        </is>
       </c>
       <c r="C33" s="33" t="inlineStr">
         <is>
@@ -25212,9 +25631,10 @@
           <t>DRS01</t>
         </is>
       </c>
-      <c r="B34" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B34" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C34" s="33" t="inlineStr">
         <is>
@@ -25258,9 +25678,10 @@
           <t>DRS02</t>
         </is>
       </c>
-      <c r="B35" s="24">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml")</f>
-        <v/>
+      <c r="B35" s="83" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+        </is>
       </c>
       <c r="C35" s="33" t="inlineStr">
         <is>
@@ -25306,38 +25727,71 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A3" location="'Application Attribute Testing'!A73" display="BLA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf" r:id="rId1"/>
     <hyperlink ref="A4" location="'Application Attribute Testing'!A74" display="BLA02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf" r:id="rId2"/>
     <hyperlink ref="A5" location="'Application Attribute Testing'!A75" display="BLA03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf" r:id="rId3"/>
     <hyperlink ref="A6" location="'Application Attribute Testing'!A76" display="BLA04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx" r:id="rId4"/>
     <hyperlink ref="A7" location="'Application Attribute Testing'!A77" display="BLA05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf" r:id="rId5"/>
     <hyperlink ref="A8" location="'Application Attribute Testing'!A78" display="BLA06"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId6"/>
     <hyperlink ref="A9" location="'Application Attribute Testing'!A82" display="DMA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId7"/>
     <hyperlink ref="A10" location="'Application Attribute Testing'!A83" display="DMA02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId8"/>
     <hyperlink ref="A11" location="'Application Attribute Testing'!A84" display="DMA03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId9"/>
     <hyperlink ref="A12" location="'Application Attribute Testing'!A85" display="DMA04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId10"/>
     <hyperlink ref="A13" location="'Application Attribute Testing'!A86" display="DMA05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg" r:id="rId11"/>
     <hyperlink ref="A14" location="'Application Attribute Testing'!A87" display="DMA06"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg" r:id="rId12"/>
     <hyperlink ref="A15" location="'Application Attribute Testing'!A88" display="DMA07"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg" r:id="rId13"/>
     <hyperlink ref="A16" location="'Application Attribute Testing'!A89" display="DMA08"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg" r:id="rId14"/>
     <hyperlink ref="A17" location="'Application Attribute Testing'!A90" display="DMA09"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg" r:id="rId15"/>
     <hyperlink ref="A18" location="'Application Attribute Testing'!A91" display="DMA10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml" r:id="rId16"/>
     <hyperlink ref="A19" location="'Application Attribute Testing'!A92" display="DMA11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml" r:id="rId17"/>
     <hyperlink ref="A20" location="'Application Attribute Testing'!A93" display="DMA12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml" r:id="rId18"/>
     <hyperlink ref="A21" location="'Application Attribute Testing'!A94" display="DMA13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml" r:id="rId19"/>
     <hyperlink ref="A22" location="'Application Attribute Testing'!A98" display="MA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png" r:id="rId20"/>
     <hyperlink ref="A23" location="'Application Attribute Testing'!A99" display="E01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId21"/>
     <hyperlink ref="A24" location="'Application Attribute Testing'!A100" display="E02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg" r:id="rId22"/>
     <hyperlink ref="A25" location="'Application Attribute Testing'!A101" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId23"/>
     <hyperlink ref="A26" location="'Application Attribute Testing'!A102" display="E04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg" r:id="rId24"/>
     <hyperlink ref="A27" location="'Application Attribute Testing'!A103" display="E05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg" r:id="rId25"/>
     <hyperlink ref="A28" location="'Application Attribute Testing'!A104" display="E07"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg" r:id="rId26"/>
     <hyperlink ref="A29" location="'Application Attribute Testing'!A105" display="E08"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg" r:id="rId27"/>
     <hyperlink ref="A30" location="'Application Attribute Testing'!A106" display="E09"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg" r:id="rId28"/>
     <hyperlink ref="A31" location="'Application Attribute Testing'!A107" display="E10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg" r:id="rId29"/>
     <hyperlink ref="A32" location="'Application Attribute Testing'!A108" display="E13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg" r:id="rId30"/>
     <hyperlink ref="A33" location="'Application Attribute Testing'!A109" display="E16b"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx" r:id="rId31"/>
     <hyperlink ref="A34" location="'Testing Attributes Testing -2'!A125" display="DRS01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId32"/>
     <hyperlink ref="A35" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -25405,6 +25859,7 @@
       <c r="P2" s="70" t="n"/>
       <c r="Q2" s="70" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="51" t="inlineStr">
         <is>
@@ -27199,6 +27654,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="15.6" customHeight="1">
       <c r="A16" s="53" t="inlineStr">
         <is>
@@ -27400,13 +27856,15 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B3" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"MA01_BSI In-Scope Applications-2026.png")</f>
-        <v/>
-      </c>
-      <c r="C3" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications","\","/"),"01_Management_Attestation_In-Scope_Applications"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications")</f>
-        <v/>
+      <c r="B3" s="84" t="inlineStr">
+        <is>
+          <t>MA01_BSI In-Scope Applications-2026.png</t>
+        </is>
+      </c>
+      <c r="C3" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications</t>
+        </is>
       </c>
       <c r="D3" s="57" t="inlineStr">
         <is>
@@ -27452,13 +27910,15 @@
           <t>BLA01</t>
         </is>
       </c>
-      <c r="B4" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf"),"BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
-      </c>
-      <c r="C4" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email")</f>
-        <v/>
+      <c r="B4" s="84" t="inlineStr">
+        <is>
+          <t>BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
+        </is>
+      </c>
+      <c r="C4" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+        </is>
       </c>
       <c r="D4" s="57" t="inlineStr">
         <is>
@@ -27504,13 +27964,15 @@
           <t>BLA02</t>
         </is>
       </c>
-      <c r="B5" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf"),"BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
-      </c>
-      <c r="C5" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email")</f>
-        <v/>
+      <c r="B5" s="84" t="inlineStr">
+        <is>
+          <t>BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
+        </is>
+      </c>
+      <c r="C5" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+        </is>
       </c>
       <c r="D5" s="57" t="inlineStr">
         <is>
@@ -27556,13 +28018,15 @@
           <t>BLA03</t>
         </is>
       </c>
-      <c r="B6" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf"),"BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
-      </c>
-      <c r="C6" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email")</f>
-        <v/>
+      <c r="B6" s="84" t="inlineStr">
+        <is>
+          <t>BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
+        </is>
+      </c>
+      <c r="C6" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+        </is>
       </c>
       <c r="D6" s="57" t="inlineStr">
         <is>
@@ -27608,13 +28072,15 @@
           <t>BLA04</t>
         </is>
       </c>
-      <c r="B7" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx","\","/"),"02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx"),"BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx")</f>
-        <v/>
-      </c>
-      <c r="C7" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email")</f>
-        <v/>
+      <c r="B7" s="84" t="inlineStr">
+        <is>
+          <t>BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
+        </is>
+      </c>
+      <c r="C7" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+        </is>
       </c>
       <c r="D7" s="57" t="inlineStr">
         <is>
@@ -27660,13 +28126,15 @@
           <t>BLA05</t>
         </is>
       </c>
-      <c r="B8" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf"),"BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
-      </c>
-      <c r="C8" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email")</f>
-        <v/>
+      <c r="B8" s="84" t="inlineStr">
+        <is>
+          <t>BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
+        </is>
+      </c>
+      <c r="C8" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+        </is>
       </c>
       <c r="D8" s="57" t="inlineStr">
         <is>
@@ -27712,13 +28180,15 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B9" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C9" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email")</f>
-        <v/>
+      <c r="B9" s="84" t="inlineStr">
+        <is>
+          <t>BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+        </is>
+      </c>
+      <c r="C9" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+        </is>
       </c>
       <c r="D9" s="57" t="inlineStr">
         <is>
@@ -27764,13 +28234,15 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B10" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C10" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
-        <v/>
+      <c r="B10" s="84" t="inlineStr">
+        <is>
+          <t>DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+        </is>
+      </c>
+      <c r="C10" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+        </is>
       </c>
       <c r="D10" s="57" t="inlineStr">
         <is>
@@ -27816,13 +28288,15 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B11" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C11" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
-        <v/>
+      <c r="B11" s="84" t="inlineStr">
+        <is>
+          <t>DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+        </is>
+      </c>
+      <c r="C11" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+        </is>
       </c>
       <c r="D11" s="57" t="inlineStr">
         <is>
@@ -27868,13 +28342,15 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B12" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C12" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
-        <v/>
+      <c r="B12" s="84" t="inlineStr">
+        <is>
+          <t>DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+        </is>
+      </c>
+      <c r="C12" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+        </is>
       </c>
       <c r="D12" s="57" t="inlineStr">
         <is>
@@ -27920,13 +28396,15 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B13" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C13" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
-        <v/>
+      <c r="B13" s="84" t="inlineStr">
+        <is>
+          <t>DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+        </is>
+      </c>
+      <c r="C13" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+        </is>
       </c>
       <c r="D13" s="57" t="inlineStr">
         <is>
@@ -27972,13 +28450,15 @@
           <t>DMA05</t>
         </is>
       </c>
-      <c r="B14" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg"),"DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C14" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
-        <v/>
+      <c r="B14" s="84" t="inlineStr">
+        <is>
+          <t>DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+        </is>
+      </c>
+      <c r="C14" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+        </is>
       </c>
       <c r="D14" s="57" t="inlineStr">
         <is>
@@ -28024,13 +28504,15 @@
           <t>DMA06</t>
         </is>
       </c>
-      <c r="B15" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg"),"DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C15" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
-        <v/>
+      <c r="B15" s="84" t="inlineStr">
+        <is>
+          <t>DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+        </is>
+      </c>
+      <c r="C15" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+        </is>
       </c>
       <c r="D15" s="57" t="inlineStr">
         <is>
@@ -28076,13 +28558,15 @@
           <t>DMA07</t>
         </is>
       </c>
-      <c r="B16" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg"),"DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C16" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
-        <v/>
+      <c r="B16" s="84" t="inlineStr">
+        <is>
+          <t>DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+        </is>
+      </c>
+      <c r="C16" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+        </is>
       </c>
       <c r="D16" s="57" t="inlineStr">
         <is>
@@ -28128,13 +28612,15 @@
           <t>DMA08</t>
         </is>
       </c>
-      <c r="B17" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg"),"DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C17" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
-        <v/>
+      <c r="B17" s="84" t="inlineStr">
+        <is>
+          <t>DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
+        </is>
+      </c>
+      <c r="C17" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+        </is>
       </c>
       <c r="D17" s="57" t="inlineStr">
         <is>
@@ -28180,13 +28666,15 @@
           <t>DMA09</t>
         </is>
       </c>
-      <c r="B18" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg"),"DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C18" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
-        <v/>
+      <c r="B18" s="84" t="inlineStr">
+        <is>
+          <t>DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+        </is>
+      </c>
+      <c r="C18" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+        </is>
       </c>
       <c r="D18" s="57" t="inlineStr">
         <is>
@@ -28232,13 +28720,15 @@
           <t>DMA10</t>
         </is>
       </c>
-      <c r="B19" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml"),"DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml")</f>
-        <v/>
-      </c>
-      <c r="C19" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
-        <v/>
+      <c r="B19" s="84" t="inlineStr">
+        <is>
+          <t>DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+        </is>
+      </c>
+      <c r="C19" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+        </is>
       </c>
       <c r="D19" s="57" t="inlineStr">
         <is>
@@ -28284,13 +28774,15 @@
           <t>DMA11</t>
         </is>
       </c>
-      <c r="B20" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml"),"DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml")</f>
-        <v/>
-      </c>
-      <c r="C20" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
-        <v/>
+      <c r="B20" s="84" t="inlineStr">
+        <is>
+          <t>DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+        </is>
+      </c>
+      <c r="C20" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+        </is>
       </c>
       <c r="D20" s="57" t="inlineStr">
         <is>
@@ -28336,13 +28828,15 @@
           <t>DMA12</t>
         </is>
       </c>
-      <c r="B21" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml"),"DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml")</f>
-        <v/>
-      </c>
-      <c r="C21" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
-        <v/>
+      <c r="B21" s="84" t="inlineStr">
+        <is>
+          <t>DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+        </is>
+      </c>
+      <c r="C21" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+        </is>
       </c>
       <c r="D21" s="57" t="inlineStr">
         <is>
@@ -28388,13 +28882,15 @@
           <t>DMA13</t>
         </is>
       </c>
-      <c r="B22" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml"),"DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml")</f>
-        <v/>
-      </c>
-      <c r="C22" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
-        <v/>
+      <c r="B22" s="84" t="inlineStr">
+        <is>
+          <t>DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
+        </is>
+      </c>
+      <c r="C22" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+        </is>
       </c>
       <c r="D22" s="57" t="inlineStr">
         <is>
@@ -28436,13 +28932,15 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B23" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
-        <v/>
-      </c>
-      <c r="C23" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
-        <v/>
+      <c r="B23" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+        </is>
+      </c>
+      <c r="C23" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+        </is>
       </c>
       <c r="D23" s="57" t="inlineStr">
         <is>
@@ -28488,13 +28986,15 @@
           <t>E02</t>
         </is>
       </c>
-      <c r="B24" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg"),"BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg")</f>
-        <v/>
-      </c>
-      <c r="C24" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
-        <v/>
+      <c r="B24" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+        </is>
+      </c>
+      <c r="C24" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+        </is>
       </c>
       <c r="D24" s="57" t="inlineStr">
         <is>
@@ -28540,13 +29040,15 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B25" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
-      </c>
-      <c r="C25" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
-        <v/>
+      <c r="B25" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+        </is>
+      </c>
+      <c r="C25" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+        </is>
       </c>
       <c r="D25" s="57" t="inlineStr">
         <is>
@@ -28592,13 +29094,15 @@
           <t>E04</t>
         </is>
       </c>
-      <c r="B26" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg"),"BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg")</f>
-        <v/>
-      </c>
-      <c r="C26" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
-        <v/>
+      <c r="B26" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+        </is>
+      </c>
+      <c r="C26" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+        </is>
       </c>
       <c r="D26" s="57" t="inlineStr">
         <is>
@@ -28644,13 +29148,15 @@
           <t>E05</t>
         </is>
       </c>
-      <c r="B27" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg"),"BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg")</f>
-        <v/>
-      </c>
-      <c r="C27" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
-        <v/>
+      <c r="B27" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+        </is>
+      </c>
+      <c r="C27" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+        </is>
       </c>
       <c r="D27" s="57" t="inlineStr">
         <is>
@@ -28696,13 +29202,15 @@
           <t>E07</t>
         </is>
       </c>
-      <c r="B28" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg"),"BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg")</f>
-        <v/>
-      </c>
-      <c r="C28" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
-        <v/>
+      <c r="B28" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+        </is>
+      </c>
+      <c r="C28" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+        </is>
       </c>
       <c r="D28" s="57" t="inlineStr">
         <is>
@@ -28748,13 +29256,15 @@
           <t>E08</t>
         </is>
       </c>
-      <c r="B29" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg"),"BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg")</f>
-        <v/>
-      </c>
-      <c r="C29" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
-        <v/>
+      <c r="B29" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+        </is>
+      </c>
+      <c r="C29" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+        </is>
       </c>
       <c r="D29" s="57" t="inlineStr">
         <is>
@@ -28800,13 +29310,15 @@
           <t>E09</t>
         </is>
       </c>
-      <c r="B30" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg"),"BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg")</f>
-        <v/>
-      </c>
-      <c r="C30" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
-        <v/>
+      <c r="B30" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+        </is>
+      </c>
+      <c r="C30" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+        </is>
       </c>
       <c r="D30" s="57" t="inlineStr">
         <is>
@@ -28852,13 +29364,15 @@
           <t>E10</t>
         </is>
       </c>
-      <c r="B31" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg"),"BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg")</f>
-        <v/>
-      </c>
-      <c r="C31" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
-        <v/>
+      <c r="B31" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+        </is>
+      </c>
+      <c r="C31" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+        </is>
       </c>
       <c r="D31" s="57" t="inlineStr">
         <is>
@@ -28904,13 +29418,15 @@
           <t>E13</t>
         </is>
       </c>
-      <c r="B32" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg"),"BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg")</f>
-        <v/>
-      </c>
-      <c r="C32" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
-        <v/>
+      <c r="B32" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
+        </is>
+      </c>
+      <c r="C32" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+        </is>
       </c>
       <c r="D32" s="57" t="inlineStr">
         <is>
@@ -28952,13 +29468,15 @@
           <t>E16b</t>
         </is>
       </c>
-      <c r="B33" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx"),"BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx")</f>
-        <v/>
-      </c>
-      <c r="C33" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
-        <v/>
+      <c r="B33" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+        </is>
+      </c>
+      <c r="C33" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+        </is>
       </c>
       <c r="D33" s="57" t="inlineStr">
         <is>
@@ -29004,13 +29522,15 @@
           <t>DRS01</t>
         </is>
       </c>
-      <c r="B34" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml")</f>
-        <v/>
-      </c>
-      <c r="C34" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails")</f>
-        <v/>
+      <c r="B34" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+        </is>
+      </c>
+      <c r="C34" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails</t>
+        </is>
       </c>
       <c r="D34" s="57" t="inlineStr">
         <is>
@@ -29059,13 +29579,15 @@
           <t>DRS02</t>
         </is>
       </c>
-      <c r="B35" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml")</f>
-        <v/>
-      </c>
-      <c r="C35" s="56">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("05_Annual_DR_Exercise_IT_and_Business_Scope_Emails","\","/"),"05_Annual_DR_Exercise_IT_and_Business_Scope_Emails"),"BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails")</f>
-        <v/>
+      <c r="B35" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+        </is>
+      </c>
+      <c r="C35" s="84" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails</t>
+        </is>
       </c>
       <c r="D35" s="57" t="inlineStr">
         <is>
@@ -30814,38 +31336,104 @@
   <autoFilter ref="A2:K35"/>
   <hyperlinks>
     <hyperlink ref="A3" location="'Application Attribute Testing'!A98" display="MA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" display="MA01_BSI In-Scope Applications-2026.png" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications" r:id="rId2"/>
     <hyperlink ref="A4" location="'Application Attribute Testing'!A73" display="BLA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" display="BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email" r:id="rId4"/>
     <hyperlink ref="A5" location="'Application Attribute Testing'!A74" display="BLA02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email" r:id="rId6"/>
     <hyperlink ref="A6" location="'Application Attribute Testing'!A75" display="BLA03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" display="BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email" r:id="rId8"/>
     <hyperlink ref="A7" location="'Application Attribute Testing'!A76" display="BLA04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" display="BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email" r:id="rId10"/>
     <hyperlink ref="A8" location="'Application Attribute Testing'!A77" display="BLA05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" display="BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email" r:id="rId12"/>
     <hyperlink ref="A9" location="'Application Attribute Testing'!A78" display="BLA06"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" display="BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email" r:id="rId14"/>
     <hyperlink ref="A10" location="'Application Attribute Testing'!A82" display="DMA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" display="DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId16"/>
     <hyperlink ref="A11" location="'Application Attribute Testing'!A83" display="DMA02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" display="DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId18"/>
     <hyperlink ref="A12" location="'Application Attribute Testing'!A84" display="DMA03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" display="DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId20"/>
     <hyperlink ref="A13" location="'Application Attribute Testing'!A85" display="DMA04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" display="DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId22"/>
     <hyperlink ref="A14" location="'Application Attribute Testing'!A86" display="DMA05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" display="DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId24"/>
     <hyperlink ref="A15" location="'Application Attribute Testing'!A87" display="DMA06"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" display="DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId26"/>
     <hyperlink ref="A16" location="'Application Attribute Testing'!A88" display="DMA07"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" display="DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId28"/>
     <hyperlink ref="A17" location="'Application Attribute Testing'!A89" display="DMA08"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId30"/>
     <hyperlink ref="A18" location="'Application Attribute Testing'!A90" display="DMA09"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" display="DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId32"/>
     <hyperlink ref="A19" location="'Application Attribute Testing'!A91" display="DMA10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" display="DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId34"/>
     <hyperlink ref="A20" location="'Application Attribute Testing'!A92" display="DMA11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" display="DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId36"/>
     <hyperlink ref="A21" location="'Application Attribute Testing'!A93" display="DMA12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId38"/>
     <hyperlink ref="A22" location="'Application Attribute Testing'!A94" display="DMA13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" display="DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId40"/>
     <hyperlink ref="A23" location="'Application Attribute Testing'!A99" display="E01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" display="BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId42"/>
     <hyperlink ref="A24" location="'Application Attribute Testing'!A100" display="E02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" display="BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId44"/>
     <hyperlink ref="A25" location="'Application Attribute Testing'!A101" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" display="BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId46"/>
     <hyperlink ref="A26" location="'Application Attribute Testing'!A102" display="E04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" display="BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId48"/>
     <hyperlink ref="A27" location="'Application Attribute Testing'!A103" display="E05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" display="BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId50"/>
     <hyperlink ref="A28" location="'Application Attribute Testing'!A104" display="E07"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" display="BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId52"/>
     <hyperlink ref="A29" location="'Application Attribute Testing'!A105" display="E08"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" display="BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId54"/>
     <hyperlink ref="A30" location="'Application Attribute Testing'!A106" display="E09"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" display="BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId56"/>
     <hyperlink ref="A31" location="'Application Attribute Testing'!A107" display="E10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" display="BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId58"/>
     <hyperlink ref="A32" location="'Application Attribute Testing'!A108" display="E13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" display="BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId60"/>
     <hyperlink ref="A33" location="'Application Attribute Testing'!A109" display="E16b"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" display="BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId62"/>
     <hyperlink ref="A34" location="'Testing Attributes Testing -2'!A125" display="DRS01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails" r:id="rId64"/>
     <hyperlink ref="A35" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_Evidence.xlsx
+++ b/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_Evidence.xlsx
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B9" s="38" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png; E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png; E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="C9" s="38" t="n"/>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B10" s="38" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls; E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls; E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx</t>
         </is>
       </c>
       <c r="C10" s="38" t="n"/>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B11" s="38" t="inlineStr">
         <is>
-          <t>DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml; DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml; DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C11" s="38" t="n"/>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F14" s="38" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png; E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx; E02; DRS01 / DRS02 (BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails): IT Scope and Business Scope DR exercise emails</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png; E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx; E02; DRS01 / DRS02 (BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails): IT Scope and Business Scope DR exercise emails</t>
         </is>
       </c>
       <c r="G14" s="42" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="F15" s="38" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls; E16b; BLA01 to BLA05 (BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email)</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls; E16b; BLA01 to BLA05 (BSI.IT.6.C7.3-Evidences\02_BL_Results)</t>
         </is>
       </c>
       <c r="G15" s="42" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="F16" s="38" t="inlineStr">
         <is>
-          <t>BLA01 to BLA06 (BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email); DMA01 to DMA12 (BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals); E09; E03 approval fields; DRS02 Business Scope email (application scope sent to the business line managers)</t>
+          <t>BLA01 to BLA06 (BSI.IT.6.C7.3-Evidences\02_BL_Results); DMA01 to DMA12 (BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals); E09; E03 approval fields; DRS02 Business Scope email (application scope sent to the business line managers)</t>
         </is>
       </c>
       <c r="G16" s="42" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="F17" s="38" t="inlineStr">
         <is>
-          <t>E04, E02, MA01 (BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence / 01_Management_Attestation_In-Scope_Applications); E03 / E16b source data</t>
+          <t>E04, E02, MA01 (BSI.IT.6.C7.3-Evidences\04_DIV_Testing / 01_InScope_Apps); E03 / E16b source data</t>
         </is>
       </c>
       <c r="G17" s="43" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="F18" s="38" t="inlineStr">
         <is>
-          <t>E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>E03 – BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="G18" s="44" t="n"/>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="B31" s="79" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_InScope_Apps</t>
         </is>
       </c>
       <c r="C31" s="73" t="n"/>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B32" s="79" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results</t>
         </is>
       </c>
       <c r="C32" s="73" t="n"/>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B33" s="79" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals</t>
         </is>
       </c>
       <c r="C33" s="73" t="n"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B34" s="79" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing</t>
         </is>
       </c>
       <c r="C34" s="73" t="n"/>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="B35" s="79" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails</t>
         </is>
       </c>
       <c r="C35" s="73" t="n"/>
@@ -2249,11 +2249,11 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" display="Test: open the evidence folder" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" display="BSI.IT.6.C7.3-Evidences\01_InScope_Apps" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" display="BSI.IT.6.C7.3-Evidences\02_BL_Results" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -5056,21 +5056,21 @@
     <row r="19">
       <c r="A19" s="66" t="inlineStr">
         <is>
-          <t>Application scope = the 10 applications selected in BCiC 'Applications In Scope for DR Test BSI' with 2025 Backup/Restore DIV Scope = True, MA01 (BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png).</t>
+          <t>Application scope = the 10 applications selected in BCiC 'Applications In Scope for DR Test BSI' with 2025 Backup/Restore DIV Scope = True, MA01 (BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="66" t="inlineStr">
         <is>
-          <t>DR Exercise Dates were confirmed from E01 (BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx); DIV records per application from E03 (BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls).</t>
+          <t>DR Exercise Dates were confirmed from E01 (BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx); DIV records per application from E03 (BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="66" t="inlineStr">
         <is>
-          <t>IT and business DR scope for the 11/15/2025 exercise confirmed by the Annual DR Exercise emails from Elizabeth Noda: DRS01 IT Scope (BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml) and DRS02 Business Scope (BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml). All 10 applications appear in DRS02; T24 is also in the DRS01 IT Scope.</t>
+          <t>IT and business DR scope for the 11/15/2025 exercise confirmed by the Annual DR Exercise emails from Elizabeth Noda: DRS01 IT Scope (BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml) and DRS02 Business Scope (BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml). All 10 applications appear in DRS02; T24 is also in the DRS01 IT Scope.</t>
         </is>
       </c>
     </row>
@@ -5465,23 +5465,23 @@
       <c r="R3" s="36" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf
 [03 DIV Manager Attestation Email Approvals]
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="S3" s="15" t="inlineStr">
@@ -5609,23 +5609,23 @@
       <c r="R4" s="36" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf
 [03 DIV Manager Attestation Email Approvals]
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="S4" s="15" t="inlineStr">
@@ -5753,23 +5753,23 @@
       <c r="R5" s="36" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf
 [03 DIV Manager Attestation Email Approvals]
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="S5" s="15" t="inlineStr">
@@ -5916,26 +5916,26 @@
       <c r="R6" s="36" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf
 [03 DIV Manager Attestation Email Approvals]
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DMA11: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg
+DMA11: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="S6" s="15" t="inlineStr">
@@ -6063,22 +6063,22 @@
       <c r="R7" s="36" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx
 [03 DIV Manager Attestation Email Approvals]
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="S7" s="15" t="inlineStr">
@@ -6207,24 +6207,24 @@
       <c r="R8" s="36" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf
 [03 DIV Manager Attestation Email Approvals]
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E07: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="S8" s="15" t="inlineStr">
@@ -6364,26 +6364,26 @@
       <c r="R9" s="36" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf
 [03 DIV Manager Attestation Email Approvals]
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E07: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="S9" s="15" t="inlineStr">
@@ -6511,23 +6511,23 @@
       <c r="R10" s="36" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf
-BLA06: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf
+BLA06: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg
 [03 DIV Manager Attestation Email Approvals]
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E10: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E10: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="S10" s="15" t="inlineStr">
@@ -6660,25 +6660,25 @@
       <c r="R11" s="36" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx
 [03 DIV Manager Attestation Email Approvals]
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E07: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="S11" s="15" t="inlineStr">
@@ -6865,41 +6865,41 @@
       <c r="R12" s="36" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf
-BLA06: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf
+BLA06: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg
 [03 DIV Manager Attestation Email Approvals]
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DMA06: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-DMA07: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-DMA08: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
-DMA09: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg
-DMA10: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
-DMA11: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-DMA12: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg
+DMA06: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg
+DMA07: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg
+DMA08: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA08_FinancialRisk_Caisapanta_2026-08-18.msg
+DMA09: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg
+DMA10: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA10_DigitalWealth_Fernandez_2026-08-21.eml
+DMA11: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml
+DMA12: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA12_ClientServicing_Vizhnay_2026-09-09.eml
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E10: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E07: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+E10: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="S12" s="15" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="B5" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png</t>
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="B9" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="B13" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="B17" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="B21" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C21" s="33" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="B25" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C25" s="33" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="B29" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C29" s="33" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="B33" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C33" s="33" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="B37" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C37" s="33" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="B41" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="C41" s="33" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="B42" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C42" s="33" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="B43" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="C43" s="33" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="B44" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C44" s="33" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="B45" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="C45" s="33" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="B49" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C49" s="33" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="B53" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="C53" s="33" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="B57" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg</t>
         </is>
       </c>
       <c r="C57" s="33" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="B61" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="C61" s="33" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="B62" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C62" s="33" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="B63" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="C63" s="33" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="B64" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C64" s="33" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="B65" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="C65" s="33" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="B69" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C69" s="33" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="B73" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C73" s="33" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="B74" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C74" s="33" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="B75" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C75" s="33" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="B76" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx</t>
         </is>
       </c>
       <c r="C76" s="33" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="B77" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C77" s="33" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="B78" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="C78" s="33" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="B82" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C82" s="33" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="B83" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="C83" s="33" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="B84" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C84" s="33" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="B85" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="C85" s="33" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="B86" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg</t>
         </is>
       </c>
       <c r="C86" s="33" t="inlineStr">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="B87" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C87" s="33" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="B88" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C88" s="33" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="B89" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA08_FinancialRisk_Caisapanta_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C89" s="33" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="B90" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C90" s="33" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="B91" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA10_DigitalWealth_Fernandez_2026-08-21.eml</t>
         </is>
       </c>
       <c r="C91" s="33" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="B92" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml</t>
         </is>
       </c>
       <c r="C92" s="33" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="B93" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA12_ClientServicing_Vizhnay_2026-09-09.eml</t>
         </is>
       </c>
       <c r="C93" s="33" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="B94" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA13_CiscoCallMgr_Noda_2026-09-09_OutOfScope.eml</t>
         </is>
       </c>
       <c r="C94" s="33" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="B98" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png</t>
         </is>
       </c>
       <c r="C98" s="33" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="B99" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="C99" s="33" t="inlineStr">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="B100" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg</t>
         </is>
       </c>
       <c r="C100" s="33" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="B101" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C101" s="33" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="B102" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg</t>
         </is>
       </c>
       <c r="C102" s="33" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="B103" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg</t>
         </is>
       </c>
       <c r="C103" s="33" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="B104" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg</t>
         </is>
       </c>
       <c r="C104" s="33" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="B105" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg</t>
         </is>
       </c>
       <c r="C105" s="33" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="B106" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg</t>
         </is>
       </c>
       <c r="C106" s="33" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="B107" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg</t>
         </is>
       </c>
       <c r="C107" s="33" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="B108" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E13_T24_Env_Refresh_2024-11-13.msg</t>
         </is>
       </c>
       <c r="C108" s="33" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="B109" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx</t>
         </is>
       </c>
       <c r="C109" s="33" t="inlineStr">
@@ -11870,96 +11870,96 @@
   <hyperlinks>
     <hyperlink ref="A3" location="'Application Attribute Testing-1'!B2" tooltip="Back to column B on Application Attribute Testing-1" display="1. Application Name (column B): review of evidence files and results"/>
     <hyperlink ref="A5" location="'Application Attribute Testing'!A98" tooltip="Go to MA01 evidence review" display="MA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png" r:id="rId1"/>
     <hyperlink ref="A7" location="'Application Attribute Testing-1'!C2" tooltip="Back to column C on Application Attribute Testing-1" display="2. Applications in Scope Identified (column C): review of evidence files and results"/>
     <hyperlink ref="A9" location="'Application Attribute Testing'!A98" tooltip="Go to MA01 evidence review" display="MA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" display="BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png" r:id="rId2"/>
     <hyperlink ref="A11" location="'Application Attribute Testing-1'!D2" tooltip="Back to column D on Application Attribute Testing-1" display="3. IT DR exercise name (column D): review of evidence files and results"/>
     <hyperlink ref="A13" location="'Application Attribute Testing'!A99" tooltip="Go to E01 evidence review" display="E01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx" r:id="rId3"/>
     <hyperlink ref="A15" location="'Application Attribute Testing-1'!E2" tooltip="Back to column E on Application Attribute Testing-1" display="4. IT DR exercise name, was the exercise annually executed? (column E): review of evidence files and results"/>
     <hyperlink ref="A17" location="'Application Attribute Testing'!A99" tooltip="Go to E01 evidence review" display="E01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx" r:id="rId4"/>
     <hyperlink ref="A19" location="'Application Attribute Testing-1'!F2" tooltip="Back to column F on Application Attribute Testing-1" display="5. Business Tester (column F): review of evidence files and results"/>
     <hyperlink ref="A21" location="'Application Attribute Testing'!A101" tooltip="Go to E03 evidence review" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId5"/>
     <hyperlink ref="A23" location="'Application Attribute Testing-1'!G2" tooltip="Back to column G on Application Attribute Testing-1" display="6. Business Data validation (column G): review of evidence files and results"/>
     <hyperlink ref="A25" location="'Application Attribute Testing'!A101" tooltip="Go to E03 evidence review" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId6"/>
     <hyperlink ref="A27" location="'Application Attribute Testing-1'!H2" tooltip="Back to column H on Application Attribute Testing-1" display="7. Business line manager name (column H): review of evidence files and results"/>
     <hyperlink ref="A29" location="'Application Attribute Testing'!A101" tooltip="Go to E03 evidence review" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId7"/>
     <hyperlink ref="A31" location="'Application Attribute Testing-1'!I2" tooltip="Back to column I on Application Attribute Testing-1" display="8. Business line manager approval dates (column I): review of evidence files and results"/>
     <hyperlink ref="A33" location="'Application Attribute Testing'!A101" tooltip="Go to E03 evidence review" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId8"/>
     <hyperlink ref="A35" location="'Application Attribute Testing-1'!J2" tooltip="Back to column J on Application Attribute Testing-1" display="9. DIV Test procedures listed within the Test results document (column J): review of evidence files and results"/>
     <hyperlink ref="A37" location="'Application Attribute Testing'!A101" tooltip="Go to E03 evidence review" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId9"/>
     <hyperlink ref="A39" location="'Application Attribute Testing-1'!K2" tooltip="Back to column K on Application Attribute Testing-1" display="10. Emails showing Business line manager approval of DIV testing results (column K): review of evidence files and results"/>
     <hyperlink ref="A41" location="'Application Attribute Testing'!A78" tooltip="Go to BLA06 evidence review" display="BLA06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg" r:id="rId10"/>
     <hyperlink ref="A42" location="'Application Attribute Testing'!A82" tooltip="Go to DMA01 evidence review" display="DMA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg" r:id="rId11"/>
     <hyperlink ref="A43" location="'Application Attribute Testing'!A83" tooltip="Go to DMA02 evidence review" display="DMA02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg" r:id="rId12"/>
     <hyperlink ref="A44" location="'Application Attribute Testing'!A84" tooltip="Go to DMA03 evidence review" display="DMA03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg" r:id="rId13"/>
     <hyperlink ref="A45" location="'Application Attribute Testing'!A85" tooltip="Go to DMA04 evidence review" display="DMA04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg" r:id="rId14"/>
     <hyperlink ref="A47" location="'Application Attribute Testing-1'!L2" tooltip="Back to column L on Application Attribute Testing-1" display="11. All evidence of Data Integrity DR test in BCIC (column L): review of evidence files and results"/>
     <hyperlink ref="A49" location="'Application Attribute Testing'!A101" tooltip="Go to E03 evidence review" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId15"/>
     <hyperlink ref="A51" location="'Application Attribute Testing-1'!M2" tooltip="Back to column M on Application Attribute Testing-1" display="12. Annual Testing Executed (column M): review of evidence files and results"/>
     <hyperlink ref="A53" location="'Application Attribute Testing'!A99" tooltip="Go to E01 evidence review" display="E01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx" r:id="rId16"/>
     <hyperlink ref="A55" location="'Application Attribute Testing-1'!N2" tooltip="Back to column N on Application Attribute Testing-1" display="13. Data Integrity Validation Performed by IT DR Team (column N): review of evidence files and results"/>
     <hyperlink ref="A57" location="'Application Attribute Testing'!A103" tooltip="Go to E05 evidence review" display="E05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg" r:id="rId17"/>
     <hyperlink ref="A59" location="'Application Attribute Testing-1'!O2" tooltip="Back to column O on Application Attribute Testing-1" display="14. Business Line Approval of Results (column O): review of evidence files and results"/>
     <hyperlink ref="A61" location="'Application Attribute Testing'!A78" tooltip="Go to BLA06 evidence review" display="BLA06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg" r:id="rId18"/>
     <hyperlink ref="A62" location="'Application Attribute Testing'!A82" tooltip="Go to DMA01 evidence review" display="DMA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg" r:id="rId19"/>
     <hyperlink ref="A63" location="'Application Attribute Testing'!A83" tooltip="Go to DMA02 evidence review" display="DMA02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg" r:id="rId20"/>
     <hyperlink ref="A64" location="'Application Attribute Testing'!A84" tooltip="Go to DMA03 evidence review" display="DMA03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg" r:id="rId21"/>
     <hyperlink ref="A65" location="'Application Attribute Testing'!A85" tooltip="Go to DMA04 evidence review" display="DMA04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg" r:id="rId22"/>
     <hyperlink ref="A67" location="'Application Attribute Testing-1'!P2" tooltip="Back to column P on Application Attribute Testing-1" display="15. Results Documented in BCMS (column P): review of evidence files and results"/>
     <hyperlink ref="A69" location="'Application Attribute Testing'!A101" tooltip="Go to E03 evidence review" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA08_FinancialRisk_Caisapanta_2026-08-18.msg" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA10_DigitalWealth_Fernandez_2026-08-21.eml" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA12_ClientServicing_Vizhnay_2026-09-09.eml" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA13_CiscoCallMgr_Noda_2026-09-09_OutOfScope.eml" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" display="BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E13_T24_Env_Refresh_2024-11-13.msg" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx" r:id="rId54"/>
     <hyperlink ref="A115" location="'Application Attribute Testing-1'!A3" tooltip="Back to sample 1822 on Application Attribute Testing-1" display="1822"/>
     <hyperlink ref="B115" location="'Application Attribute Testing-1'!A3" tooltip="Back to sample 1822 on Application Attribute Testing-1" display="ACH Express"/>
     <hyperlink ref="A116" location="'Application Attribute Testing-1'!A4" tooltip="Back to sample 1867 on Application Attribute Testing-1" display="1867"/>
@@ -12265,12 +12265,12 @@
       </c>
       <c r="B5" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png</t>
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png</t>
         </is>
       </c>
       <c r="D5" s="33" t="inlineStr">
@@ -12569,12 +12569,12 @@
       </c>
       <c r="B9" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png</t>
         </is>
       </c>
       <c r="D9" s="33" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="B10" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C10" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D10" s="33" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="B11" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C11" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D11" s="33" t="inlineStr">
@@ -12988,12 +12988,12 @@
       </c>
       <c r="B15" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="D15" s="33" t="inlineStr">
@@ -13086,12 +13086,12 @@
       </c>
       <c r="B16" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D16" s="33" t="inlineStr">
@@ -13139,12 +13139,12 @@
       </c>
       <c r="B17" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D17" s="33" t="inlineStr">
@@ -13390,12 +13390,12 @@
       </c>
       <c r="B21" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="C21" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="D21" s="33" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="B22" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D22" s="33" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="B23" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C23" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D23" s="33" t="inlineStr">
@@ -13793,12 +13793,12 @@
       </c>
       <c r="B27" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C27" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="D27" s="33" t="inlineStr">
@@ -14088,12 +14088,12 @@
       </c>
       <c r="B31" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C31" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="D31" s="33" t="inlineStr">
@@ -14383,12 +14383,12 @@
       </c>
       <c r="B35" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C35" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="D35" s="33" t="inlineStr">
@@ -14480,12 +14480,12 @@
       </c>
       <c r="B36" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C36" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D36" s="33" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="B40" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C40" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="D40" s="33" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="B44" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C44" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="D44" s="33" t="inlineStr">
@@ -15331,12 +15331,12 @@
       </c>
       <c r="B48" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="C48" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="D48" s="33" t="inlineStr">
@@ -15420,12 +15420,12 @@
       </c>
       <c r="B49" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C49" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D49" s="33" t="inlineStr">
@@ -15512,12 +15512,12 @@
       </c>
       <c r="B50" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="C50" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="D50" s="33" t="inlineStr">
@@ -15603,12 +15603,12 @@
       </c>
       <c r="B51" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C51" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D51" s="33" t="inlineStr">
@@ -15693,12 +15693,12 @@
       </c>
       <c r="B52" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="C52" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="D52" s="33" t="inlineStr">
@@ -15981,12 +15981,12 @@
       </c>
       <c r="B56" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C56" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="D56" s="33" t="inlineStr">
@@ -16276,12 +16276,12 @@
       </c>
       <c r="B60" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="C60" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="D60" s="33" t="inlineStr">
@@ -16375,12 +16375,12 @@
       </c>
       <c r="B61" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C61" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D61" s="33" t="inlineStr">
@@ -16428,12 +16428,12 @@
       </c>
       <c r="B62" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C62" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D62" s="33" t="inlineStr">
@@ -16679,12 +16679,12 @@
       </c>
       <c r="B66" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg</t>
         </is>
       </c>
       <c r="C66" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg</t>
         </is>
       </c>
       <c r="D66" s="33" t="inlineStr">
@@ -16776,12 +16776,12 @@
       </c>
       <c r="B67" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C67" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D67" s="33" t="inlineStr">
@@ -16829,12 +16829,12 @@
       </c>
       <c r="B68" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C68" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D68" s="33" t="inlineStr">
@@ -17080,12 +17080,12 @@
       </c>
       <c r="B72" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="C72" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="D72" s="33" t="inlineStr">
@@ -17169,12 +17169,12 @@
       </c>
       <c r="B73" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C73" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D73" s="33" t="inlineStr">
@@ -17261,12 +17261,12 @@
       </c>
       <c r="B74" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="C74" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="D74" s="33" t="inlineStr">
@@ -17352,12 +17352,12 @@
       </c>
       <c r="B75" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D75" s="33" t="inlineStr">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="B76" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="D76" s="33" t="inlineStr">
@@ -17532,12 +17532,12 @@
       </c>
       <c r="B77" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D77" s="33" t="inlineStr">
@@ -17783,12 +17783,12 @@
       </c>
       <c r="B81" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C81" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="D81" s="33" t="inlineStr">
@@ -18078,12 +18078,12 @@
       </c>
       <c r="B85" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C85" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="D85" s="33" t="inlineStr">
@@ -18164,12 +18164,12 @@
       </c>
       <c r="B86" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C86" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="D86" s="33" t="inlineStr">
@@ -18250,12 +18250,12 @@
       </c>
       <c r="B87" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C87" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="D87" s="33" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="B88" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx</t>
         </is>
       </c>
       <c r="C88" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx</t>
         </is>
       </c>
       <c r="D88" s="33" t="inlineStr">
@@ -18422,12 +18422,12 @@
       </c>
       <c r="B89" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C89" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="D89" s="33" t="inlineStr">
@@ -18508,12 +18508,12 @@
       </c>
       <c r="B90" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="C90" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="D90" s="33" t="inlineStr">
@@ -18792,12 +18792,12 @@
       </c>
       <c r="B94" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C94" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D94" s="33" t="inlineStr">
@@ -18878,12 +18878,12 @@
       </c>
       <c r="B95" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="C95" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="D95" s="33" t="inlineStr">
@@ -18964,12 +18964,12 @@
       </c>
       <c r="B96" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C96" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D96" s="33" t="inlineStr">
@@ -19050,12 +19050,12 @@
       </c>
       <c r="B97" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="C97" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="D97" s="33" t="inlineStr">
@@ -19136,12 +19136,12 @@
       </c>
       <c r="B98" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg</t>
         </is>
       </c>
       <c r="C98" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg</t>
         </is>
       </c>
       <c r="D98" s="33" t="inlineStr">
@@ -19222,12 +19222,12 @@
       </c>
       <c r="B99" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C99" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D99" s="33" t="inlineStr">
@@ -19308,12 +19308,12 @@
       </c>
       <c r="B100" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C100" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D100" s="33" t="inlineStr">
@@ -19394,12 +19394,12 @@
       </c>
       <c r="B101" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA08_FinancialRisk_Caisapanta_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C101" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA08_FinancialRisk_Caisapanta_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D101" s="33" t="inlineStr">
@@ -19480,12 +19480,12 @@
       </c>
       <c r="B102" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C102" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D102" s="33" t="inlineStr">
@@ -19566,12 +19566,12 @@
       </c>
       <c r="B103" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA10_DigitalWealth_Fernandez_2026-08-21.eml</t>
         </is>
       </c>
       <c r="C103" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA10_DigitalWealth_Fernandez_2026-08-21.eml</t>
         </is>
       </c>
       <c r="D103" s="33" t="inlineStr">
@@ -19652,12 +19652,12 @@
       </c>
       <c r="B104" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml</t>
         </is>
       </c>
       <c r="C104" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml</t>
         </is>
       </c>
       <c r="D104" s="33" t="inlineStr">
@@ -19738,12 +19738,12 @@
       </c>
       <c r="B105" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA12_ClientServicing_Vizhnay_2026-09-09.eml</t>
         </is>
       </c>
       <c r="C105" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA12_ClientServicing_Vizhnay_2026-09-09.eml</t>
         </is>
       </c>
       <c r="D105" s="33" t="inlineStr">
@@ -19824,12 +19824,12 @@
       </c>
       <c r="B106" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA13_CiscoCallMgr_Noda_2026-09-09_OutOfScope.eml</t>
         </is>
       </c>
       <c r="C106" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA13_CiscoCallMgr_Noda_2026-09-09_OutOfScope.eml</t>
         </is>
       </c>
       <c r="D106" s="33" t="inlineStr">
@@ -20108,12 +20108,12 @@
       </c>
       <c r="B110" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png</t>
         </is>
       </c>
       <c r="C110" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png</t>
         </is>
       </c>
       <c r="D110" s="33" t="inlineStr">
@@ -20194,12 +20194,12 @@
       </c>
       <c r="B111" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="C111" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="D111" s="33" t="inlineStr">
@@ -20280,12 +20280,12 @@
       </c>
       <c r="B112" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg</t>
         </is>
       </c>
       <c r="C112" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg</t>
         </is>
       </c>
       <c r="D112" s="33" t="inlineStr">
@@ -20366,12 +20366,12 @@
       </c>
       <c r="B113" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C113" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="D113" s="33" t="inlineStr">
@@ -20452,12 +20452,12 @@
       </c>
       <c r="B114" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg</t>
         </is>
       </c>
       <c r="C114" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg</t>
         </is>
       </c>
       <c r="D114" s="33" t="inlineStr">
@@ -20538,12 +20538,12 @@
       </c>
       <c r="B115" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg</t>
         </is>
       </c>
       <c r="C115" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg</t>
         </is>
       </c>
       <c r="D115" s="33" t="inlineStr">
@@ -20624,12 +20624,12 @@
       </c>
       <c r="B116" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg</t>
         </is>
       </c>
       <c r="C116" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg</t>
         </is>
       </c>
       <c r="D116" s="33" t="inlineStr">
@@ -20710,12 +20710,12 @@
       </c>
       <c r="B117" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg</t>
         </is>
       </c>
       <c r="C117" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg</t>
         </is>
       </c>
       <c r="D117" s="33" t="inlineStr">
@@ -20796,12 +20796,12 @@
       </c>
       <c r="B118" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg</t>
         </is>
       </c>
       <c r="C118" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg</t>
         </is>
       </c>
       <c r="D118" s="33" t="inlineStr">
@@ -20882,12 +20882,12 @@
       </c>
       <c r="B119" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg</t>
         </is>
       </c>
       <c r="C119" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg</t>
         </is>
       </c>
       <c r="D119" s="33" t="inlineStr">
@@ -20968,12 +20968,12 @@
       </c>
       <c r="B120" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E13_T24_Env_Refresh_2024-11-13.msg</t>
         </is>
       </c>
       <c r="C120" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E13_T24_Env_Refresh_2024-11-13.msg</t>
         </is>
       </c>
       <c r="D120" s="33" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="B121" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx</t>
         </is>
       </c>
       <c r="C121" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx</t>
         </is>
       </c>
       <c r="D121" s="33" t="inlineStr">
@@ -21197,12 +21197,12 @@
       </c>
       <c r="B125" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C125" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D125" s="33" t="inlineStr">
@@ -21239,12 +21239,12 @@
       </c>
       <c r="B126" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C126" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D126" s="33" t="inlineStr">
@@ -21298,124 +21298,124 @@
   <hyperlinks>
     <hyperlink ref="A3" location="'Application Attribute Testing-1'!B2" tooltip="Back to column B on Application Attribute Testing-1" display="1. Application Name (column B): review of evidence files and results"/>
     <hyperlink ref="A5" location="'Testing Attributes Testing -2'!A110" tooltip="Go to MA01 evidence review" display="MA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png" r:id="rId1"/>
     <hyperlink ref="A7" location="'Application Attribute Testing-1'!C2" tooltip="Back to column C on Application Attribute Testing-1" display="2. Applications in Scope Identified (column C): review of evidence files and results"/>
     <hyperlink ref="A9" location="'Testing Attributes Testing -2'!A110" tooltip="Go to MA01 evidence review" display="MA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" display="BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png" r:id="rId2"/>
     <hyperlink ref="A10" location="'Testing Attributes Testing -2'!A125" display="DRS01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml" r:id="rId3"/>
     <hyperlink ref="A11" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml" r:id="rId4"/>
     <hyperlink ref="A13" location="'Application Attribute Testing-1'!D2" tooltip="Back to column D on Application Attribute Testing-1" display="3. IT DR exercise name (column D): review of evidence files and results"/>
     <hyperlink ref="A15" location="'Testing Attributes Testing -2'!A111" tooltip="Go to E01 evidence review" display="E01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx" r:id="rId5"/>
     <hyperlink ref="A16" location="'Testing Attributes Testing -2'!A125" display="DRS01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml" r:id="rId6"/>
     <hyperlink ref="A17" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml" r:id="rId7"/>
     <hyperlink ref="A19" location="'Application Attribute Testing-1'!E2" tooltip="Back to column E on Application Attribute Testing-1" display="4. IT DR exercise name, was the exercise annually executed? (column E): review of evidence files and results"/>
     <hyperlink ref="A21" location="'Testing Attributes Testing -2'!A111" tooltip="Go to E01 evidence review" display="E01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx" r:id="rId8"/>
     <hyperlink ref="A22" location="'Testing Attributes Testing -2'!A125" display="DRS01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml" r:id="rId9"/>
     <hyperlink ref="A23" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml" r:id="rId10"/>
     <hyperlink ref="A25" location="'Application Attribute Testing-1'!F2" tooltip="Back to column F on Application Attribute Testing-1" display="5. Business Tester (column F): review of evidence files and results"/>
     <hyperlink ref="A27" location="'Testing Attributes Testing -2'!A113" tooltip="Go to E03 evidence review" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId11"/>
     <hyperlink ref="A29" location="'Application Attribute Testing-1'!G2" tooltip="Back to column G on Application Attribute Testing-1" display="6. Business Data validation (column G): review of evidence files and results"/>
     <hyperlink ref="A31" location="'Testing Attributes Testing -2'!A113" tooltip="Go to E03 evidence review" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId12"/>
     <hyperlink ref="A33" location="'Application Attribute Testing-1'!H2" tooltip="Back to column H on Application Attribute Testing-1" display="7. Business line manager name (column H): review of evidence files and results"/>
     <hyperlink ref="A35" location="'Testing Attributes Testing -2'!A113" tooltip="Go to E03 evidence review" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId13"/>
     <hyperlink ref="A36" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml" r:id="rId14"/>
     <hyperlink ref="A38" location="'Application Attribute Testing-1'!I2" tooltip="Back to column I on Application Attribute Testing-1" display="8. Business line manager approval dates (column I): review of evidence files and results"/>
     <hyperlink ref="A40" location="'Testing Attributes Testing -2'!A113" tooltip="Go to E03 evidence review" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId15"/>
     <hyperlink ref="A42" location="'Application Attribute Testing-1'!J2" tooltip="Back to column J on Application Attribute Testing-1" display="9. DIV Test procedures listed within the Test results document (column J): review of evidence files and results"/>
     <hyperlink ref="A44" location="'Testing Attributes Testing -2'!A113" tooltip="Go to E03 evidence review" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId16"/>
     <hyperlink ref="A46" location="'Application Attribute Testing-1'!K2" tooltip="Back to column K on Application Attribute Testing-1" display="10. Emails showing Business line manager approval of DIV testing results (column K): review of evidence files and results"/>
     <hyperlink ref="A48" location="'Testing Attributes Testing -2'!A90" tooltip="Go to BLA06 evidence review" display="BLA06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg" r:id="rId17"/>
     <hyperlink ref="A49" location="'Testing Attributes Testing -2'!A94" tooltip="Go to DMA01 evidence review" display="DMA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg" r:id="rId18"/>
     <hyperlink ref="A50" location="'Testing Attributes Testing -2'!A95" tooltip="Go to DMA02 evidence review" display="DMA02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg" r:id="rId19"/>
     <hyperlink ref="A51" location="'Testing Attributes Testing -2'!A96" tooltip="Go to DMA03 evidence review" display="DMA03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg" r:id="rId20"/>
     <hyperlink ref="A52" location="'Testing Attributes Testing -2'!A97" tooltip="Go to DMA04 evidence review" display="DMA04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg" r:id="rId21"/>
     <hyperlink ref="A54" location="'Application Attribute Testing-1'!L2" tooltip="Back to column L on Application Attribute Testing-1" display="11. All evidence of Data Integrity DR test in BCIC (column L): review of evidence files and results"/>
     <hyperlink ref="A56" location="'Testing Attributes Testing -2'!A113" tooltip="Go to E03 evidence review" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId22"/>
     <hyperlink ref="A58" location="'Application Attribute Testing-1'!M2" tooltip="Back to column M on Application Attribute Testing-1" display="12. Annual Testing Executed (column M): review of evidence files and results"/>
     <hyperlink ref="A60" location="'Testing Attributes Testing -2'!A111" tooltip="Go to E01 evidence review" display="E01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx" r:id="rId23"/>
     <hyperlink ref="A61" location="'Testing Attributes Testing -2'!A125" display="DRS01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml" r:id="rId24"/>
     <hyperlink ref="A62" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml" r:id="rId25"/>
     <hyperlink ref="A64" location="'Application Attribute Testing-1'!N2" tooltip="Back to column N on Application Attribute Testing-1" display="13. Data Integrity Validation Performed by IT DR Team (column N): review of evidence files and results"/>
     <hyperlink ref="A66" location="'Testing Attributes Testing -2'!A115" tooltip="Go to E05 evidence review" display="E05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg" r:id="rId26"/>
     <hyperlink ref="A67" location="'Testing Attributes Testing -2'!A125" display="DRS01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml" r:id="rId27"/>
     <hyperlink ref="A68" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml" r:id="rId28"/>
     <hyperlink ref="A70" location="'Application Attribute Testing-1'!O2" tooltip="Back to column O on Application Attribute Testing-1" display="14. Business Line Approval of Results (column O): review of evidence files and results"/>
     <hyperlink ref="A72" location="'Testing Attributes Testing -2'!A90" tooltip="Go to BLA06 evidence review" display="BLA06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg" r:id="rId29"/>
     <hyperlink ref="A73" location="'Testing Attributes Testing -2'!A94" tooltip="Go to DMA01 evidence review" display="DMA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg" r:id="rId30"/>
     <hyperlink ref="A74" location="'Testing Attributes Testing -2'!A95" tooltip="Go to DMA02 evidence review" display="DMA02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg" r:id="rId31"/>
     <hyperlink ref="A75" location="'Testing Attributes Testing -2'!A96" tooltip="Go to DMA03 evidence review" display="DMA03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg" r:id="rId32"/>
     <hyperlink ref="A76" location="'Testing Attributes Testing -2'!A97" tooltip="Go to DMA04 evidence review" display="DMA04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg" r:id="rId33"/>
     <hyperlink ref="A77" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml" r:id="rId34"/>
     <hyperlink ref="A79" location="'Application Attribute Testing-1'!P2" tooltip="Back to column P on Application Attribute Testing-1" display="15. Results Documented in BCMS (column P): review of evidence files and results"/>
     <hyperlink ref="A81" location="'Testing Attributes Testing -2'!A113" tooltip="Go to E03 evidence review" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA08_FinancialRisk_Caisapanta_2026-08-18.msg" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA10_DigitalWealth_Fernandez_2026-08-21.eml" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA12_ClientServicing_Vizhnay_2026-09-09.eml" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA13_CiscoCallMgr_Noda_2026-09-09_OutOfScope.eml" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" display="BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E13_T24_Env_Refresh_2024-11-13.msg" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx" r:id="rId66"/>
     <hyperlink ref="A125" location="'Application Attribute Testing-1'!R3" display="DRS01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml" r:id="rId67"/>
     <hyperlink ref="A126" location="'Application Attribute Testing-1'!R3" display="DRS02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -22863,12 +22863,12 @@
       </c>
       <c r="B3" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C3" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="D3" s="33" t="inlineStr">
@@ -22955,12 +22955,12 @@
       </c>
       <c r="B4" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="D4" s="33" t="inlineStr">
@@ -23047,12 +23047,12 @@
       </c>
       <c r="B5" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="D5" s="33" t="inlineStr">
@@ -23139,12 +23139,12 @@
       </c>
       <c r="B6" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx</t>
         </is>
       </c>
       <c r="D6" s="33" t="inlineStr">
@@ -23231,12 +23231,12 @@
       </c>
       <c r="B7" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="D7" s="33" t="inlineStr">
@@ -23323,12 +23323,12 @@
       </c>
       <c r="B8" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="C8" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="D8" s="33" t="inlineStr">
@@ -23412,12 +23412,12 @@
       </c>
       <c r="B9" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D9" s="33" t="inlineStr">
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B10" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="C10" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="D10" s="33" t="inlineStr">
@@ -23595,12 +23595,12 @@
       </c>
       <c r="B11" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C11" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D11" s="33" t="inlineStr">
@@ -23684,12 +23684,12 @@
       </c>
       <c r="B12" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="C12" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="D12" s="33" t="inlineStr">
@@ -23773,12 +23773,12 @@
       </c>
       <c r="B13" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg</t>
         </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg</t>
         </is>
       </c>
       <c r="D13" s="33" t="inlineStr">
@@ -23862,12 +23862,12 @@
       </c>
       <c r="B14" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C14" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D14" s="33" t="inlineStr">
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B15" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D15" s="33" t="inlineStr">
@@ -24040,12 +24040,12 @@
       </c>
       <c r="B16" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA08_FinancialRisk_Caisapanta_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA08_FinancialRisk_Caisapanta_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D16" s="33" t="inlineStr">
@@ -24129,12 +24129,12 @@
       </c>
       <c r="B17" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg</t>
         </is>
       </c>
       <c r="D17" s="33" t="inlineStr">
@@ -24218,12 +24218,12 @@
       </c>
       <c r="B18" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA10_DigitalWealth_Fernandez_2026-08-21.eml</t>
         </is>
       </c>
       <c r="C18" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA10_DigitalWealth_Fernandez_2026-08-21.eml</t>
         </is>
       </c>
       <c r="D18" s="33" t="inlineStr">
@@ -24307,12 +24307,12 @@
       </c>
       <c r="B19" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml</t>
         </is>
       </c>
       <c r="C19" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml</t>
         </is>
       </c>
       <c r="D19" s="33" t="inlineStr">
@@ -24396,12 +24396,12 @@
       </c>
       <c r="B20" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA12_ClientServicing_Vizhnay_2026-09-09.eml</t>
         </is>
       </c>
       <c r="C20" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA12_ClientServicing_Vizhnay_2026-09-09.eml</t>
         </is>
       </c>
       <c r="D20" s="33" t="inlineStr">
@@ -24485,12 +24485,12 @@
       </c>
       <c r="B21" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA13_CiscoCallMgr_Noda_2026-09-09_OutOfScope.eml</t>
         </is>
       </c>
       <c r="C21" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA13_CiscoCallMgr_Noda_2026-09-09_OutOfScope.eml</t>
         </is>
       </c>
       <c r="D21" s="33" t="inlineStr">
@@ -24567,12 +24567,12 @@
       </c>
       <c r="B22" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png</t>
         </is>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png</t>
         </is>
       </c>
       <c r="D22" s="33" t="inlineStr">
@@ -24655,12 +24655,12 @@
       </c>
       <c r="B23" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="C23" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="D23" s="33" t="inlineStr">
@@ -24746,12 +24746,12 @@
       </c>
       <c r="B24" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg</t>
         </is>
       </c>
       <c r="C24" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg</t>
         </is>
       </c>
       <c r="D24" s="33" t="inlineStr">
@@ -24834,12 +24834,12 @@
       </c>
       <c r="B25" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C25" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="D25" s="33" t="inlineStr">
@@ -24931,12 +24931,12 @@
       </c>
       <c r="B26" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg</t>
         </is>
       </c>
       <c r="C26" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg</t>
         </is>
       </c>
       <c r="D26" s="33" t="inlineStr">
@@ -25022,12 +25022,12 @@
       </c>
       <c r="B27" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg</t>
         </is>
       </c>
       <c r="C27" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg</t>
         </is>
       </c>
       <c r="D27" s="33" t="inlineStr">
@@ -25109,12 +25109,12 @@
       </c>
       <c r="B28" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg</t>
         </is>
       </c>
       <c r="C28" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg</t>
         </is>
       </c>
       <c r="D28" s="33" t="inlineStr">
@@ -25195,12 +25195,12 @@
       </c>
       <c r="B29" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg</t>
         </is>
       </c>
       <c r="C29" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg</t>
         </is>
       </c>
       <c r="D29" s="33" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="B30" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg</t>
         </is>
       </c>
       <c r="C30" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg</t>
         </is>
       </c>
       <c r="D30" s="33" t="inlineStr">
@@ -25374,12 +25374,12 @@
       </c>
       <c r="B31" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg</t>
         </is>
       </c>
       <c r="C31" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg</t>
         </is>
       </c>
       <c r="D31" s="33" t="inlineStr">
@@ -25460,12 +25460,12 @@
       </c>
       <c r="B32" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E13_T24_Env_Refresh_2024-11-13.msg</t>
         </is>
       </c>
       <c r="C32" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E13_T24_Env_Refresh_2024-11-13.msg</t>
         </is>
       </c>
       <c r="D32" s="33" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="B33" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx</t>
         </is>
       </c>
       <c r="C33" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx</t>
         </is>
       </c>
       <c r="D33" s="33" t="inlineStr">
@@ -25633,12 +25633,12 @@
       </c>
       <c r="B34" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C34" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D34" s="33" t="inlineStr">
@@ -25680,12 +25680,12 @@
       </c>
       <c r="B35" s="83" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C35" s="33" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="D35" s="33" t="inlineStr">
@@ -25727,71 +25727,71 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A3" location="'Application Attribute Testing'!A73" display="BLA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf" r:id="rId1"/>
     <hyperlink ref="A4" location="'Application Attribute Testing'!A74" display="BLA02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf" r:id="rId2"/>
     <hyperlink ref="A5" location="'Application Attribute Testing'!A75" display="BLA03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf" r:id="rId3"/>
     <hyperlink ref="A6" location="'Application Attribute Testing'!A76" display="BLA04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx" r:id="rId4"/>
     <hyperlink ref="A7" location="'Application Attribute Testing'!A77" display="BLA05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf" r:id="rId5"/>
     <hyperlink ref="A8" location="'Application Attribute Testing'!A78" display="BLA06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" display="BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg" r:id="rId6"/>
     <hyperlink ref="A9" location="'Application Attribute Testing'!A82" display="DMA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg" r:id="rId7"/>
     <hyperlink ref="A10" location="'Application Attribute Testing'!A83" display="DMA02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg" r:id="rId8"/>
     <hyperlink ref="A11" location="'Application Attribute Testing'!A84" display="DMA03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg" r:id="rId9"/>
     <hyperlink ref="A12" location="'Application Attribute Testing'!A85" display="DMA04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg" r:id="rId10"/>
     <hyperlink ref="A13" location="'Application Attribute Testing'!A86" display="DMA05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg" r:id="rId11"/>
     <hyperlink ref="A14" location="'Application Attribute Testing'!A87" display="DMA06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg" r:id="rId12"/>
     <hyperlink ref="A15" location="'Application Attribute Testing'!A88" display="DMA07"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg" r:id="rId13"/>
     <hyperlink ref="A16" location="'Application Attribute Testing'!A89" display="DMA08"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA08_FinancialRisk_Caisapanta_2026-08-18.msg" r:id="rId14"/>
     <hyperlink ref="A17" location="'Application Attribute Testing'!A90" display="DMA09"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg" r:id="rId15"/>
     <hyperlink ref="A18" location="'Application Attribute Testing'!A91" display="DMA10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA10_DigitalWealth_Fernandez_2026-08-21.eml" r:id="rId16"/>
     <hyperlink ref="A19" location="'Application Attribute Testing'!A92" display="DMA11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml" r:id="rId17"/>
     <hyperlink ref="A20" location="'Application Attribute Testing'!A93" display="DMA12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA12_ClientServicing_Vizhnay_2026-09-09.eml" r:id="rId18"/>
     <hyperlink ref="A21" location="'Application Attribute Testing'!A94" display="DMA13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA13_CiscoCallMgr_Noda_2026-09-09_OutOfScope.eml" r:id="rId19"/>
     <hyperlink ref="A22" location="'Application Attribute Testing'!A98" display="MA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" display="BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png" r:id="rId20"/>
     <hyperlink ref="A23" location="'Application Attribute Testing'!A99" display="E01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx" r:id="rId21"/>
     <hyperlink ref="A24" location="'Application Attribute Testing'!A100" display="E02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg" r:id="rId22"/>
     <hyperlink ref="A25" location="'Application Attribute Testing'!A101" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls" r:id="rId23"/>
     <hyperlink ref="A26" location="'Application Attribute Testing'!A102" display="E04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg" r:id="rId24"/>
     <hyperlink ref="A27" location="'Application Attribute Testing'!A103" display="E05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg" r:id="rId25"/>
     <hyperlink ref="A28" location="'Application Attribute Testing'!A104" display="E07"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg" r:id="rId26"/>
     <hyperlink ref="A29" location="'Application Attribute Testing'!A105" display="E08"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg" r:id="rId27"/>
     <hyperlink ref="A30" location="'Application Attribute Testing'!A106" display="E09"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg" r:id="rId28"/>
     <hyperlink ref="A31" location="'Application Attribute Testing'!A107" display="E10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg" r:id="rId29"/>
     <hyperlink ref="A32" location="'Application Attribute Testing'!A108" display="E13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E13_T24_Env_Refresh_2024-11-13.msg" r:id="rId30"/>
     <hyperlink ref="A33" location="'Application Attribute Testing'!A109" display="E16b"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx" r:id="rId31"/>
     <hyperlink ref="A34" location="'Testing Attributes Testing -2'!A125" display="DRS01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml" r:id="rId32"/>
     <hyperlink ref="A35" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -25839,7 +25839,7 @@
     <row r="2">
       <c r="A2" s="70" t="inlineStr">
         <is>
-          <t>Every file named below is stored in repository BSI.IT.6.C7.3-Evidences: 01_Management_Attestation_In-Scope_Applications (MA), 02_Business_Line_Approval_Results_Email (BLA), 03_DIV_Manager_Attestation_Email_Approvals (DMA), 04_Data_Integrity_and_Email_Testing_Evidence (E). Row numbers refer to the Excel row in the source export. 05_Annual_DR_Exercise_IT_and_Business_Scope_Emails (DRS).</t>
+          <t>Every file named below is stored in repository BSI.IT.6.C7.3-Evidences: 01_InScope_Apps (MA), 02_BL_Results (BLA), 03_Mgr_Approvals (DMA), 04_DIV_Testing (E). Row numbers refer to the Excel row in the source export. 05_DR_Scope_Emails (DRS).</t>
         </is>
       </c>
       <c r="B2" s="70" t="n"/>
@@ -25953,148 +25953,148 @@
       </c>
       <c r="B5" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 3, Exercise Date 12/11/25, 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 48, Business Data Validation Date 11/15/2025
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, script header DATE: 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 3, Exercise Date 12/11/25, 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 47, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 48, Business Data Validation Date 11/15/2025
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, script header DATE: 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
         </is>
       </c>
       <c r="C5" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 1822 selected; 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 3, Application ID 1822
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC view 'Applications In Scope for DR Test BSI'
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 48
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 1822 selected; 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 3, Application ID 1822
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC view 'Applications In Scope for DR Test BSI'
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 47
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 48
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, BCiC report screen (record on a later page of the 66-item report)</t>
         </is>
       </c>
       <c r="D5" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, 'Business Tester(s)' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 48
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, PRINT NAME OF OPERATOR: Raimy Ayala
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, Client Back Office test evidence submitted by Mariorly Morales / Ilumel Rodriguez / Rolando Bonilla</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 47, 'Business Tester(s)' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 48
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, PRINT NAME OF OPERATOR: Raimy Ayala
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg, Client Back Office test evidence submitted by Mariorly Morales / Ilumel Rodriguez / Rolando Bonilla</t>
         </is>
       </c>
       <c r="E5" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 48 to 11/15/2025; Format, Headers and Content validated
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 47, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 48 to 11/15/2025; Format, Headers and Content validated
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots</t>
         </is>
       </c>
       <c r="F5" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, 'Department Manager' column
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Claudia Romero (Client Back Office)</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 47, 'Department Manager' column
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Claudia Romero (Client Back Office)</t>
         </is>
       </c>
       <c r="G5" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, 'Department Manager Approval Date' and 'Attestation Date' columns
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 47, 'Department Manager Approval Date' and 'Attestation Date' columns
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="H5" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, 'Data Integrity Validation Procedures' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 48, 'Data Integrity Validation Procedures' column
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 47, 'Data Integrity Validation Procedures' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 48, 'Data Integrity Validation Procedures' column
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
         </is>
       </c>
       <c r="I5" s="52" t="inlineStr">
         <is>
-          <t>E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="J5" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, BCiC DIV export (tester, dates, manager, validation results, attestation)
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 48, BCiC DIV export 2025-26 reviewed with the attestation
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 3
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC DR-scope view
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, App ID 1822 selected in BCiC in-scope view</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 47, BCiC DIV export (tester, dates, manager, validation results, attestation)
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 48, BCiC DIV export 2025-26 reviewed with the attestation
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, BCiC report screen (record on a later page of the 66-item report)
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 3
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC DR-scope view
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, App ID 1822 selected in BCiC in-scope view</t>
         </is>
       </c>
       <c r="K5" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 3, Exercise Date 12/11/2025 / 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, dated 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 3, Exercise Date 12/11/2025 / 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 47, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, dated 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
         </is>
       </c>
       <c r="L5" s="52" t="inlineStr">
         <is>
-          <t>E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, Format, Headers and Content validated
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
+          <t>E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, IT DR test script completed by the business-line tester
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg, IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 47, Format, Headers and Content validated
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
         </is>
       </c>
       <c r="M5" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 1822 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 3 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, view 'Applications In Scope for DR Test BSI'
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, BIA results &amp; applications list review
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, scope table: application to Client Back Office to Claudia Romero
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, ACH Express listed under 'Applications To Test' for Client Back Office (Claudia Romero)
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 1822 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 3 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, view 'Applications In Scope for DR Test BSI'
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, BIA results &amp; applications list review
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg, scope table: application to Client Back Office to Claudia Romero
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, ACH Express listed under 'Applications To Test' for Client Back Office (Claudia Romero)
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
         </is>
       </c>
       <c r="N5" s="52" t="inlineStr">
         <is>
-          <t>BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, business line DIV results document, 11/15/2025, Client Back Office (operator Raimy Ayala)
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, Department Manager / Approval Date / Attestation fields
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Claudia Romero); scope confirmation only</t>
+          <t>BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, business line DIV results document, 11/15/2025, Client Back Office (operator Raimy Ayala)
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 47, Department Manager / Approval Date / Attestation fields
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Claudia Romero); scope confirmation only</t>
         </is>
       </c>
       <c r="O5" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 48
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 47
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 48
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, BCiC report screen (record on a later page of the 66-item report)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P5" s="52" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf
 [03 DIV Manager Attestation Email Approvals]
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="Q5" s="52" t="inlineStr">
@@ -26109,152 +26109,152 @@
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 19, Exercise Date 12/11/25, 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 9, Business Data Validation Date 11/15/2025
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, script header DATE: 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 19, Exercise Date 12/11/25, 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 9, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 9, Business Data Validation Date 11/15/2025
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, script header DATE: 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
         </is>
       </c>
       <c r="C6" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 1867 selected; 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 19, Application ID 1867
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC view 'Applications In Scope for DR Test BSI'
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 9
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 1867 selected; 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 19, Application ID 1867
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC view 'Applications In Scope for DR Test BSI'
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 9
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 9
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen</t>
         </is>
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, 'Business Tester(s)' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 9
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Tester(s) column
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, PRINT NAME OF OPERATOR: Raimy Ayala
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, Client Back Office test evidence submitted by Mariorly Morales / Ilumel Rodriguez / Rolando Bonilla</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 9, 'Business Tester(s)' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 9
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Business Tester(s) column
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, PRINT NAME OF OPERATOR: Raimy Ayala
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg, Client Back Office test evidence submitted by Mariorly Morales / Ilumel Rodriguez / Rolando Bonilla</t>
         </is>
       </c>
       <c r="E6" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 9 to 11/15/2025; Format, Headers and Content validated
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and validation result columns
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 9, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 9 to 11/15/2025; Format, Headers and Content validated
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Business Data Validation Date and validation result columns
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots</t>
         </is>
       </c>
       <c r="F6" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, 'Department Manager' column
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Department Manager column
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Claudia Romero (Client Back Office)</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 9, 'Department Manager' column
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Department Manager column
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Claudia Romero (Client Back Office)</t>
         </is>
       </c>
       <c r="G6" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, 'Department Manager Approval Date' and 'Attestation Date' columns
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Department Manager Approval Date column
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 9, 'Department Manager Approval Date' and 'Attestation Date' columns
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Department Manager Approval Date column
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="H6" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, 'Data Integrity Validation Procedures' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 9, 'Data Integrity Validation Procedures' column
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 9, 'Data Integrity Validation Procedures' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 9, 'Data Integrity Validation Procedures' column
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
         </is>
       </c>
       <c r="I6" s="52" t="inlineStr">
         <is>
-          <t>E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="J6" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, BCiC DIV export (tester, dates, manager, validation results, attestation)
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 9, BCiC DIV export 2025-26 reviewed with the attestation
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 19
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC DR-scope view
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, App ID 1867 selected in BCiC in-scope view</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 9, BCiC DIV export (tester, dates, manager, validation results, attestation)
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 9, BCiC DIV export 2025-26 reviewed with the attestation
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 19
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC DR-scope view
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, App ID 1867 selected in BCiC in-scope view</t>
         </is>
       </c>
       <c r="K6" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 19, Exercise Date 12/11/2025 / 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, dated 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 19, Exercise Date 12/11/2025 / 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 9, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, dated 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
         </is>
       </c>
       <c r="L6" s="52" t="inlineStr">
         <is>
-          <t>E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, Format, Headers and Content validated
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
+          <t>E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, IT DR test script completed by the business-line tester
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg, IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 9, Format, Headers and Content validated
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
         </is>
       </c>
       <c r="M6" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 1867 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 19 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, view 'Applications In Scope for DR Test BSI'
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, BIA results &amp; applications list review
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, scope table: application to Client Back Office to Claudia Romero
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, FedExport - BSI listed under 'Applications To Test' for Client Back Office (Claudia Romero)
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 1867 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 19 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, view 'Applications In Scope for DR Test BSI'
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, BIA results &amp; applications list review
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg, scope table: application to Client Back Office to Claudia Romero
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, FedExport - BSI listed under 'Applications To Test' for Client Back Office (Claudia Romero)
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
         </is>
       </c>
       <c r="N6" s="52" t="inlineStr">
         <is>
-          <t>BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, business line DIV results document, 11/15/2025, Client Back Office (operator Raimy Ayala)
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, Department Manager / Approval Date / Attestation fields
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Claudia Romero); scope confirmation only</t>
+          <t>BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, business line DIV results document, 11/15/2025, Client Back Office (operator Raimy Ayala)
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 9, Department Manager / Approval Date / Attestation fields
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Claudia Romero); scope confirmation only</t>
         </is>
       </c>
       <c r="O6" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 9
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 9
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 9
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P6" s="52" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf
 [03 DIV Manager Attestation Email Approvals]
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="Q6" s="52" t="inlineStr">
@@ -26269,152 +26269,152 @@
       </c>
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 20, Exercise Date 12/11/25, 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 10, Business Data Validation Date 11/15/2025
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, script header DATE: 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 20, Exercise Date 12/11/25, 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 10, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 10, Business Data Validation Date 11/15/2025
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, script header DATE: 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
         </is>
       </c>
       <c r="C7" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 1868 selected; 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 20, Application ID 1868
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC view 'Applications In Scope for DR Test BSI'
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 10
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 1868 selected; 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 20, Application ID 1868
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC view 'Applications In Scope for DR Test BSI'
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 10
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 10
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen</t>
         </is>
       </c>
       <c r="D7" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, 'Business Tester(s)' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 10
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Tester(s) column
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, PRINT NAME OF OPERATOR: Raimy Ayala
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, Client Back Office test evidence submitted by Mariorly Morales / Ilumel Rodriguez / Rolando Bonilla</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 10, 'Business Tester(s)' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 10
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Business Tester(s) column
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, PRINT NAME OF OPERATOR: Raimy Ayala
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg, Client Back Office test evidence submitted by Mariorly Morales / Ilumel Rodriguez / Rolando Bonilla</t>
         </is>
       </c>
       <c r="E7" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 10 to 11/15/2025; Format, Headers and Content validated
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and validation result columns
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 10, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 10 to 11/15/2025; Format, Headers and Content validated
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Business Data Validation Date and validation result columns
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots</t>
         </is>
       </c>
       <c r="F7" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, 'Department Manager' column
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Department Manager column
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Claudia Romero (Client Back Office)</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 10, 'Department Manager' column
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Department Manager column
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Claudia Romero (Client Back Office)</t>
         </is>
       </c>
       <c r="G7" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, 'Department Manager Approval Date' and 'Attestation Date' columns
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Department Manager Approval Date column
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 10, 'Department Manager Approval Date' and 'Attestation Date' columns
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Department Manager Approval Date column
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="H7" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, 'Data Integrity Validation Procedures' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 10, 'Data Integrity Validation Procedures' column
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 10, 'Data Integrity Validation Procedures' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 10, 'Data Integrity Validation Procedures' column
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
         </is>
       </c>
       <c r="I7" s="52" t="inlineStr">
         <is>
-          <t>E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="J7" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, BCiC DIV export (tester, dates, manager, validation results, attestation)
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 10, BCiC DIV export 2025-26 reviewed with the attestation
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 20
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC DR-scope view
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, App ID 1868 selected in BCiC in-scope view</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 10, BCiC DIV export (tester, dates, manager, validation results, attestation)
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 10, BCiC DIV export 2025-26 reviewed with the attestation
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 20
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC DR-scope view
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, App ID 1868 selected in BCiC in-scope view</t>
         </is>
       </c>
       <c r="K7" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 20, Exercise Date 12/11/2025 / 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, dated 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 20, Exercise Date 12/11/2025 / 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 10, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, dated 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
         </is>
       </c>
       <c r="L7" s="52" t="inlineStr">
         <is>
-          <t>E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, Format, Headers and Content validated
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
+          <t>E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, IT DR test script completed by the business-line tester
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg, IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 10, Format, Headers and Content validated
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
         </is>
       </c>
       <c r="M7" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 1868 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 20 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, view 'Applications In Scope for DR Test BSI'
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, BIA results &amp; applications list review
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, scope table: application to Client Back Office to Claudia Romero
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, FedImport - BSI listed under 'Applications To Test' for Client Back Office (Claudia Romero)
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 1868 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 20 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, view 'Applications In Scope for DR Test BSI'
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, BIA results &amp; applications list review
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg, scope table: application to Client Back Office to Claudia Romero
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, FedImport - BSI listed under 'Applications To Test' for Client Back Office (Claudia Romero)
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
         </is>
       </c>
       <c r="N7" s="52" t="inlineStr">
         <is>
-          <t>BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, business line DIV results document, 11/15/2025, Client Back Office (operator Raimy Ayala)
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, Department Manager / Approval Date / Attestation fields
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Claudia Romero); scope confirmation only</t>
+          <t>BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, business line DIV results document, 11/15/2025, Client Back Office (operator Raimy Ayala)
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 10, Department Manager / Approval Date / Attestation fields
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Claudia Romero); scope confirmation only</t>
         </is>
       </c>
       <c r="O7" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 10
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 10
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 10
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P7" s="52" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf
 [03 DIV Manager Attestation Email Approvals]
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="Q7" s="52" t="inlineStr">
@@ -26429,174 +26429,174 @@
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 24, Exercise Date 11/15/25, 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 5, 11, 13, 52, 54, 58, Business Data Validation Date 11/15/2025
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, script header DATE: 11/15/2025
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, script header DATE: 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 24, Exercise Date 11/15/25, 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 5, 11, 13, 51, 53, 57, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 5, 11, 13, 52, 54, 58, Business Data Validation Date 11/15/2025
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, script header DATE: 11/15/2025
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, script header DATE: 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
         </is>
       </c>
       <c r="C8" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 3299 selected; 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 24, Application ID 3299
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC view 'Applications In Scope for DR Test BSI'
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 5, 11, 13, 52, 54, 58
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 3299 selected; 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 24, Application ID 3299
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC view 'Applications In Scope for DR Test BSI'
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 5, 11, 13, 51, 53, 57
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 5, 11, 13, 52, 54, 58
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen</t>
         </is>
       </c>
       <c r="D8" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, 'Business Tester(s)' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 5, 11, 13, 52, 54, 58
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Tester(s) column
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, PRINT NAME OF OPERATOR: Raimy Ayala
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, PRINT NAME OF OPERATOR: David Marquez
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, Client Back Office test evidence submitted by Mariorly Morales / Ilumel Rodriguez / Rolando Bonilla</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 5, 11, 13, 51, 53, 57, 'Business Tester(s)' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 5, 11, 13, 52, 54, 58
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Business Tester(s) column
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, PRINT NAME OF OPERATOR: Raimy Ayala
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, PRINT NAME OF OPERATOR: David Marquez
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg, Client Back Office test evidence submitted by Mariorly Morales / Ilumel Rodriguez / Rolando Bonilla</t>
         </is>
       </c>
       <c r="E8" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 5, 11, 13, 52, 54, 58 to 11/15/2025; Format, Headers and Content validated
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and validation result columns
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, p.1 DIV procedure &amp; in-scope apps; pp.2-14 production-day 11/14 versus test-day 11/15 screenshots</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 5, 11, 13, 51, 53, 57, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 5, 11, 13, 52, 54, 58 to 11/15/2025; Format, Headers and Content validated
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Business Data Validation Date and validation result columns
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, p.1 DIV procedure &amp; in-scope apps; pp.2-14 production-day 11/14 versus test-day 11/15 screenshots</t>
         </is>
       </c>
       <c r="F8" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, 'Department Manager' column
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Department Manager column
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA11: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Claudia Romero; Miguel Orozco; Jaime Verastegui (BSA/AML/OFAC); Gabriela Hernandez Gonzalez (FATCA); Marcel Garcia (Governance and Static Data)</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 5, 11, 13, 51, 53, 57, 'Department Manager' column
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Department Manager column
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA11: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Claudia Romero; Miguel Orozco; Jaime Verastegui (BSA/AML/OFAC); Gabriela Hernandez Gonzalez (FATCA); Marcel Garcia (Governance and Static Data)</t>
         </is>
       </c>
       <c r="G8" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, 'Department Manager Approval Date' and 'Attestation Date' columns
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Department Manager Approval Date column
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA11: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 5, 11, 13, 51, 53, 57, 'Department Manager Approval Date' and 'Attestation Date' columns
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Department Manager Approval Date column
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA11: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg</t>
         </is>
       </c>
       <c r="H8" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, 'Data Integrity Validation Procedures' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 5, 11, 13, 52, 54, 58, 'Data Integrity Validation Procedures' column
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 5, 11, 13, 51, 53, 57, 'Data Integrity Validation Procedures' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 5, 11, 13, 52, 54, 58, 'Data Integrity Validation Procedures' column
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
         </is>
       </c>
       <c r="I8" s="52" t="inlineStr">
         <is>
-          <t>DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA11: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA11: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg</t>
         </is>
       </c>
       <c r="J8" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, BCiC DIV export (tester, dates, manager, validation results, attestation)
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 5, 11, 13, 52, 54, 58, BCiC DIV export 2025-26 reviewed with the attestation
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 24
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC DR-scope view
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, App ID 3299 selected in BCiC in-scope view</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 5, 11, 13, 51, 53, 57, BCiC DIV export (tester, dates, manager, validation results, attestation)
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 5, 11, 13, 52, 54, 58, BCiC DIV export 2025-26 reviewed with the attestation
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 24
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC DR-scope view
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, App ID 3299 selected in BCiC in-scope view</t>
         </is>
       </c>
       <c r="K8" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 24, Exercise Date 11/15/2025 / 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, dated 11/15/2025
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, dated 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 24, Exercise Date 11/15/2025 / 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 5, 11, 13, 51, 53, 57, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, dated 11/15/2025
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, dated 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
         </is>
       </c>
       <c r="L8" s="52" t="inlineStr">
         <is>
-          <t>E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, Format, Headers and Content validated
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
+          <t>E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, IT DR test script completed by the business-line tester
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, IT DR test script completed by the business-line tester
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg, IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 5, 11, 13, 51, 53, 57, Format, Headers and Content validated
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
         </is>
       </c>
       <c r="M8" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 3299 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 24 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, view 'Applications In Scope for DR Test BSI'
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, BIA results &amp; applications list review
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, scope table: application to Client Back Office to Claudia Romero
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, Imaging101 listed under 'Applications To Test' for Client Back Office (Claudia Romero); Commercial Middle office (Miguel Orozco); BSA/AML/OFAC (Jaime Verastegui); FATCA (Gabriela Hernandez Gonzalez); Governance and Static Data (Marcel Garcia)
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 3299 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 24 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, view 'Applications In Scope for DR Test BSI'
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, BIA results &amp; applications list review
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg, scope table: application to Client Back Office to Claudia Romero
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, Imaging101 listed under 'Applications To Test' for Client Back Office (Claudia Romero); Commercial Middle office (Miguel Orozco); BSA/AML/OFAC (Jaime Verastegui); FATCA (Gabriela Hernandez Gonzalez); Governance and Static Data (Marcel Garcia)
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
         </is>
       </c>
       <c r="N8" s="52" t="inlineStr">
         <is>
-          <t>BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, business line DIV results document, 11/15/2025, Client Back Office (operator Raimy Ayala)
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, business line DIV results document, 11/15/2025, BSA/AML/OFAC Compliance (operator David Marquez)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA11: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, Department Manager / Approval Date / Attestation fields
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Claudia Romero, Miguel Orozco, Maria Teresa Del Cerro); scope confirmation only</t>
+          <t>BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, business line DIV results document, 11/15/2025, Client Back Office (operator Raimy Ayala)
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, business line DIV results document, 11/15/2025, BSA/AML/OFAC Compliance (operator David Marquez)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA11: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 5, 11, 13, 51, 53, 57, Department Manager / Approval Date / Attestation fields
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Claudia Romero, Miguel Orozco, Maria Teresa Del Cerro); scope confirmation only</t>
         </is>
       </c>
       <c r="O8" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 5, 11, 13, 52, 54, 58
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 5, 11, 13, 51, 53, 57
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 5, 11, 13, 52, 54, 58
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P8" s="52" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf
 [03 DIV Manager Attestation Email Approvals]
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DMA11: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg
+DMA11: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="Q8" s="52" t="inlineStr">
@@ -26611,140 +26611,140 @@
       </c>
       <c r="B9" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 25, Exercise Date 11/15/25, 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 62, Business Data Validation Date 11/15/2025
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, script header DATE: 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 25, Exercise Date 11/15/25, 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 61, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 62, Business Data Validation Date 11/15/2025
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, script header DATE: 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
         </is>
       </c>
       <c r="C9" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 4052 selected; 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 25, Application ID 4052
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC view 'Applications In Scope for DR Test BSI'
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 62
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 4052 selected; 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 25, Application ID 4052
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC view 'Applications In Scope for DR Test BSI'
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 61
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 62
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, BCiC report screen (record on a later page of the 66-item report)</t>
         </is>
       </c>
       <c r="D9" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, 'Business Tester(s)' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 62
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, PRINT NAME OF OPERATOR: Michelle Oropesa</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 61, 'Business Tester(s)' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 62
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, PRINT NAME OF OPERATOR: Michelle Oropesa</t>
         </is>
       </c>
       <c r="E9" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 62 to 11/15/2025; Format, Headers and Content validated
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, DIV table (Format / Headers / Content = Yes; MT300 &amp; FX S reports matched 11/14 versus 11/15)</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 61, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 62 to 11/15/2025; Format, Headers and Content validated
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, DIV table (Format / Headers / Content = Yes; MT300 &amp; FX S reports matched 11/14 versus 11/15)</t>
         </is>
       </c>
       <c r="F9" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, 'Department Manager' column
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Michelle Oropesa (Investment Operations)</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 61, 'Department Manager' column
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Michelle Oropesa (Investment Operations)</t>
         </is>
       </c>
       <c r="G9" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, 'Department Manager Approval Date' and 'Attestation Date' columns
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 61, 'Department Manager Approval Date' and 'Attestation Date' columns
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="H9" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, 'Data Integrity Validation Procedures' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 62, 'Data Integrity Validation Procedures' column
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 61, 'Data Integrity Validation Procedures' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 62, 'Data Integrity Validation Procedures' column
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
         </is>
       </c>
       <c r="I9" s="52" t="inlineStr">
         <is>
-          <t>• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>• DMA04 – BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="J9" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, BCiC DIV export (tester, dates, manager, validation results, attestation)
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 62, BCiC DIV export 2025-26 reviewed with the attestation
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 25
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC DR-scope view
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, App ID 4052 selected in BCiC in-scope view</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 61, BCiC DIV export (tester, dates, manager, validation results, attestation)
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 62, BCiC DIV export 2025-26 reviewed with the attestation
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, BCiC report screen (record on a later page of the 66-item report)
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 25
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC DR-scope view
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, App ID 4052 selected in BCiC in-scope view</t>
         </is>
       </c>
       <c r="K9" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 25, Exercise Date 11/15/2025 / 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, dated 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 25, Exercise Date 11/15/2025 / 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 61, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, dated 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
         </is>
       </c>
       <c r="L9" s="52" t="inlineStr">
         <is>
-          <t>E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, IT DR test script completed by the business-line tester
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, Format, Headers and Content validated
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
+          <t>E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, IT DR test script completed by the business-line tester
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 61, Format, Headers and Content validated
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
         </is>
       </c>
       <c r="M9" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 4052 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 25 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, view 'Applications In Scope for DR Test BSI'
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, BIA results &amp; applications list review
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, Interface Monitor listed under 'Applications To Test' for Investment Operations (Michelle Oropesa), listed as 'Swift Interface'
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 4052 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 25 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, view 'Applications In Scope for DR Test BSI'
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, BIA results &amp; applications list review
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, Interface Monitor listed under 'Applications To Test' for Investment Operations (Michelle Oropesa), listed as 'Swift Interface'
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
         </is>
       </c>
       <c r="N9" s="52" t="inlineStr">
         <is>
-          <t>BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, business line DIV results document, 11/15/2025, Investment Operations (operator Michelle Oropesa)
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, Department Manager / Approval Date / Attestation fields
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Michelle Oropesa); scope confirmation only</t>
+          <t>BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, business line DIV results document, 11/15/2025, Investment Operations (operator Michelle Oropesa)
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 61, Department Manager / Approval Date / Attestation fields
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Michelle Oropesa); scope confirmation only</t>
         </is>
       </c>
       <c r="O9" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 62
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 61
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 62
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, BCiC report screen (record on a later page of the 66-item report)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P9" s="52" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx
 [03 DIV Manager Attestation Email Approvals]
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="Q9" s="52" t="inlineStr">
@@ -26759,145 +26759,145 @@
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 31, Exercise Date 11/15/25, 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 25, 29, Business Data Validation Date 11/15/2025
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, script header DATE: 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 31, Exercise Date 11/15/25, 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 25, 29, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 25, 29, Business Data Validation Date 11/15/2025
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, script header DATE: 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
         </is>
       </c>
       <c r="C10" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 3301 selected; 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 31, Application ID 3301
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC view 'Applications In Scope for DR Test BSI'
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 25, 29
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 3301 selected; 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 31, Application ID 3301
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC view 'Applications In Scope for DR Test BSI'
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 25, 29
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 25, 29
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, BCiC report screen (record on a later page of the 66-item report)</t>
         </is>
       </c>
       <c r="D10" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, 'Business Tester(s)' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 25, 29
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, PRINT NAME OF OPERATOR: Frank Puentes / Gustavo Bucaro</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 25, 29, 'Business Tester(s)' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 25, 29
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, PRINT NAME OF OPERATOR: Frank Puentes / Gustavo Bucaro</t>
         </is>
       </c>
       <c r="E10" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 25, 29 to 11/15/2025; Format, Headers and Content validated
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, pp.1-2 DIV section (Format / Headers / Content = yes; 11/14 Fed &amp; SWIFT data reconciled)
-E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg, pre-DR source reports 11/14/2025 (Payment Monitor, OFAC, SWIFT Interface Monitor)
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg, DR test-day 11/15/2025 comparison reports</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 25, 29, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 25, 29 to 11/15/2025; Format, Headers and Content validated
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, pp.1-2 DIV section (Format / Headers / Content = yes; 11/14 Fed &amp; SWIFT data reconciled)
+E07: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg, pre-DR source reports 11/14/2025 (Payment Monitor, OFAC, SWIFT Interface Monitor)
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg, DR test-day 11/15/2025 comparison reports</t>
         </is>
       </c>
       <c r="F10" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, 'Department Manager' column
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Franklin Puentes (Payments &amp; Cash Management)</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 25, 29, 'Department Manager' column
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Franklin Puentes (Payments &amp; Cash Management)</t>
         </is>
       </c>
       <c r="G10" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, 'Department Manager Approval Date' and 'Attestation Date' columns
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 25, 29, 'Department Manager Approval Date' and 'Attestation Date' columns
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="H10" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, 'Data Integrity Validation Procedures' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 25, 29, 'Data Integrity Validation Procedures' column
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 25, 29, 'Data Integrity Validation Procedures' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 25, 29, 'Data Integrity Validation Procedures' column
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
         </is>
       </c>
       <c r="I10" s="52" t="inlineStr">
         <is>
-          <t>• DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>• DMA03 – BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="J10" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, BCiC DIV export (tester, dates, manager, validation results, attestation)
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 25, 29, BCiC DIV export 2025-26 reviewed with the attestation
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 31
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC DR-scope view
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, App ID 3301 selected in BCiC in-scope view</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 25, 29, BCiC DIV export (tester, dates, manager, validation results, attestation)
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 25, 29, BCiC DIV export 2025-26 reviewed with the attestation
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, BCiC report screen (record on a later page of the 66-item report)
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 31
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC DR-scope view
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, App ID 3301 selected in BCiC in-scope view</t>
         </is>
       </c>
       <c r="K10" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 31, Exercise Date 11/15/2025 / 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, dated 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 31, Exercise Date 11/15/2025 / 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 25, 29, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, dated 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
         </is>
       </c>
       <c r="L10" s="52" t="inlineStr">
         <is>
-          <t>E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg, business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, Format, Headers and Content validated
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
+          <t>E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, IT DR test script completed by the business-line tester
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg, business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 25, 29, Format, Headers and Content validated
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
         </is>
       </c>
       <c r="M10" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 3301 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 31 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, view 'Applications In Scope for DR Test BSI'
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, BIA results &amp; applications list review
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, MQ Payment Monitor listed under 'Applications To Test' for Payments &amp; Cash Management (Franklin Puentes)
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 3301 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 31 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, view 'Applications In Scope for DR Test BSI'
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, BIA results &amp; applications list review
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, MQ Payment Monitor listed under 'Applications To Test' for Payments &amp; Cash Management (Franklin Puentes)
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
         </is>
       </c>
       <c r="N10" s="52" t="inlineStr">
         <is>
-          <t>BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, business line DIV results document, 11/15/2025, Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, Department Manager / Approval Date / Attestation fields
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Frank Puentes); scope confirmation only</t>
+          <t>BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, business line DIV results document, 11/15/2025, Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 25, 29, Department Manager / Approval Date / Attestation fields
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Frank Puentes); scope confirmation only</t>
         </is>
       </c>
       <c r="O10" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 25, 29
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 25, 29
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 25, 29
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, BCiC report screen (record on a later page of the 66-item report)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P10" s="52" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf
 [03 DIV Manager Attestation Email Approvals]
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E07: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="Q10" s="52" t="inlineStr">
@@ -26912,166 +26912,166 @@
       </c>
       <c r="B11" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 34, Exercise Date 11/15/25, 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 6, 26, 30, 34, 59, Business Data Validation Date 11/15/2025
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, script header DATE: 11/15/2025
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, script header DATE: 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 34, Exercise Date 11/15/25, 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 6, 26, 30, 34, 58, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 6, 26, 30, 34, 59, Business Data Validation Date 11/15/2025
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, script header DATE: 11/15/2025
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, script header DATE: 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
         </is>
       </c>
       <c r="C11" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 1903 selected; 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 34, Application ID 1903
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC view 'Applications In Scope for DR Test BSI'
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 6, 26, 30, 34, 59
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 1903 selected; 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 34, Application ID 1903
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC view 'Applications In Scope for DR Test BSI'
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 6, 26, 30, 34, 58
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 6, 26, 30, 34, 59
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen</t>
         </is>
       </c>
       <c r="D11" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, 'Business Tester(s)' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 6, 26, 30, 34, 59
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Tester(s) column
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, PRINT NAME OF OPERATOR: David Marquez
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, PRINT NAME OF OPERATOR: Frank Puentes / Gustavo Bucaro</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 6, 26, 30, 34, 58, 'Business Tester(s)' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 6, 26, 30, 34, 59
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Business Tester(s) column
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, PRINT NAME OF OPERATOR: David Marquez
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, PRINT NAME OF OPERATOR: Frank Puentes / Gustavo Bucaro</t>
         </is>
       </c>
       <c r="E11" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 6, 26, 30, 34, 59 to 11/15/2025; Format, Headers and Content validated
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and validation result columns
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, p.1 DIV procedure &amp; in-scope apps; pp.2-14 production-day 11/14 versus test-day 11/15 screenshots
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, pp.1-2 DIV section (Format / Headers / Content = yes; 11/14 Fed &amp; SWIFT data reconciled)
-E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg, pre-DR source reports 11/14/2025 (Payment Monitor, OFAC, SWIFT Interface Monitor)
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg, DR test-day 11/15/2025 comparison reports</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 6, 26, 30, 34, 58, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 6, 26, 30, 34, 59 to 11/15/2025; Format, Headers and Content validated
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Business Data Validation Date and validation result columns
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, p.1 DIV procedure &amp; in-scope apps; pp.2-14 production-day 11/14 versus test-day 11/15 screenshots
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, pp.1-2 DIV section (Format / Headers / Content = yes; 11/14 Fed &amp; SWIFT data reconciled)
+E07: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg, pre-DR source reports 11/14/2025 (Payment Monitor, OFAC, SWIFT Interface Monitor)
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg, DR test-day 11/15/2025 comparison reports</t>
         </is>
       </c>
       <c r="F11" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, 'Department Manager' column
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Department Manager column
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Jaime Verastegui (BSA/AML/OFAC); Marcel Garcia (Governance and Static Data); Franklin Puentes (Payments &amp; Cash Management)</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 6, 26, 30, 34, 58, 'Department Manager' column
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Department Manager column
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Jaime Verastegui (BSA/AML/OFAC); Marcel Garcia (Governance and Static Data); Franklin Puentes (Payments &amp; Cash Management)</t>
         </is>
       </c>
       <c r="G11" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, 'Department Manager Approval Date' and 'Attestation Date' columns
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Department Manager Approval Date column
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 6, 26, 30, 34, 58, 'Department Manager Approval Date' and 'Attestation Date' columns
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Department Manager Approval Date column
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg</t>
         </is>
       </c>
       <c r="H11" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, 'Data Integrity Validation Procedures' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 6, 26, 30, 34, 59, 'Data Integrity Validation Procedures' column
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 6, 26, 30, 34, 58, 'Data Integrity Validation Procedures' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 6, 26, 30, 34, 59, 'Data Integrity Validation Procedures' column
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
         </is>
       </c>
       <c r="I11" s="52" t="inlineStr">
         <is>
-          <t>DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg</t>
         </is>
       </c>
       <c r="J11" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, BCiC DIV export (tester, dates, manager, validation results, attestation)
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 6, 26, 30, 34, 59, BCiC DIV export 2025-26 reviewed with the attestation
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 34
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC DR-scope view
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, App ID 1903 selected in BCiC in-scope view</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 6, 26, 30, 34, 58, BCiC DIV export (tester, dates, manager, validation results, attestation)
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 6, 26, 30, 34, 59, BCiC DIV export 2025-26 reviewed with the attestation
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 34
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC DR-scope view
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, App ID 1903 selected in BCiC in-scope view</t>
         </is>
       </c>
       <c r="K11" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 34, Exercise Date 11/15/2025 / 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, dated 11/15/2025
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, dated 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 34, Exercise Date 11/15/2025 / 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 6, 26, 30, 34, 58, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, dated 11/15/2025
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, dated 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
         </is>
       </c>
       <c r="L11" s="52" t="inlineStr">
         <is>
-          <t>E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg, business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, Format, Headers and Content validated
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
+          <t>E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, IT DR test script completed by the business-line tester
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, IT DR test script completed by the business-line tester
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg, business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 6, 26, 30, 34, 58, Format, Headers and Content validated
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
         </is>
       </c>
       <c r="M11" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 1903 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 34 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, view 'Applications In Scope for DR Test BSI'
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, BIA results &amp; applications list review
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, OFAC - BSI listed under 'Applications To Test' for BSA/AML/OFAC (Jaime Verastegui); Governance and Static Data (Marcel Garcia); Payments &amp; Cash Management (Franklin Puentes)
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 1903 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 34 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, view 'Applications In Scope for DR Test BSI'
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, BIA results &amp; applications list review
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, OFAC - BSI listed under 'Applications To Test' for BSA/AML/OFAC (Jaime Verastegui); Governance and Static Data (Marcel Garcia); Payments &amp; Cash Management (Franklin Puentes)
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
         </is>
       </c>
       <c r="N11" s="52" t="inlineStr">
         <is>
-          <t>BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, business line DIV results document, 11/15/2025, BSA/AML/OFAC Compliance (operator David Marquez)
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, business line DIV results document, 11/15/2025, Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, Department Manager / Approval Date / Attestation fields
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Frank Puentes, Maria Teresa Del Cerro); scope confirmation only</t>
+          <t>BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, business line DIV results document, 11/15/2025, BSA/AML/OFAC Compliance (operator David Marquez)
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, business line DIV results document, 11/15/2025, Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 6, 26, 30, 34, 58, Department Manager / Approval Date / Attestation fields
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Frank Puentes, Maria Teresa Del Cerro); scope confirmation only</t>
         </is>
       </c>
       <c r="O11" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 6, 26, 30, 34, 59
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 6, 26, 30, 34, 58
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 6, 26, 30, 34, 59
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P11" s="52" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf
 [03 DIV Manager Attestation Email Approvals]
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E07: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="Q11" s="52" t="inlineStr">
@@ -27086,142 +27086,142 @@
       </c>
       <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 36, Exercise Date 11/15/25, 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 17, Business Data Validation Date 11/15/2025
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, script header DATE: 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 36, Exercise Date 11/15/25, 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 17, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 17, Business Data Validation Date 11/15/2025
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf, script header DATE: 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
         </is>
       </c>
       <c r="C12" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 1917 selected; 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 36, Application ID 1917
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC view 'Applications In Scope for DR Test BSI'
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 17
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 1917 selected; 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 36, Application ID 1917
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC view 'Applications In Scope for DR Test BSI'
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 17
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 17
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, BCiC report screen (record on a later page of the 66-item report)</t>
         </is>
       </c>
       <c r="D12" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, 'Business Tester(s)' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 17
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, PRINT NAME OF OPERATOR: Dunia Gonzalez Collado</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 17, 'Business Tester(s)' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 17
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf, PRINT NAME OF OPERATOR: Dunia Gonzalez Collado</t>
         </is>
       </c>
       <c r="E12" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 17 to 11/15/2025; Format, Headers and Content validated
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Yes / Yes / Yes, no discrepancies); pp.2-9 reconciliation reports 11/13 versus 11/15</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 17, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 17 to 11/15/2025; Format, Headers and Content validated
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf, p.1 DIV section (Yes / Yes / Yes, no discrepancies); pp.2-9 reconciliation reports 11/13 versus 11/15</t>
         </is>
       </c>
       <c r="F12" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, 'Department Manager' column
-BLA06: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Sadis Alvarenga Hernandez (Financial Analysis and Control)</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 17, 'Department Manager' column
+BLA06: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Sadis Alvarenga Hernandez (Financial Analysis and Control)</t>
         </is>
       </c>
       <c r="G12" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, 'Department Manager Approval Date' and 'Attestation Date' columns
-BLA06: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 17, 'Department Manager Approval Date' and 'Attestation Date' columns
+BLA06: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="H12" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, 'Data Integrity Validation Procedures' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 17, 'Data Integrity Validation Procedures' column
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 17, 'Data Integrity Validation Procedures' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 17, 'Data Integrity Validation Procedures' column
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
         </is>
       </c>
       <c r="I12" s="52" t="inlineStr">
         <is>
-          <t>• BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>• BLA06 – BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="J12" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, BCiC DIV export (tester, dates, manager, validation results, attestation)
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 17, BCiC DIV export 2025-26 reviewed with the attestation
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 36
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC DR-scope view
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, App ID 1917 selected in BCiC in-scope view</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 17, BCiC DIV export (tester, dates, manager, validation results, attestation)
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 17, BCiC DIV export 2025-26 reviewed with the attestation
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, BCiC report screen (record on a later page of the 66-item report)
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 36
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC DR-scope view
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, App ID 1917 selected in BCiC in-scope view</t>
         </is>
       </c>
       <c r="K12" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 36, Exercise Date 11/15/2025 / 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, dated 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 36, Exercise Date 11/15/2025 / 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 17, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf, dated 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
         </is>
       </c>
       <c r="L12" s="52" t="inlineStr">
         <is>
-          <t>E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
-E10: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg, IT DR (Elizabeth Noda) Finance DIV chart and approval request
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, Format, Headers and Content validated
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
+          <t>E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf, IT DR test script completed by the business-line tester
+E10: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg, IT DR (Elizabeth Noda) Finance DIV chart and approval request
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 17, Format, Headers and Content validated
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
         </is>
       </c>
       <c r="M12" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 1917 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 36 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, view 'Applications In Scope for DR Test BSI'
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, BIA results &amp; applications list review
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, ReconXpert listed under 'Applications To Test' for Financial Analysis and Control (Sadis Alvarenga Hernandez)
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 1917 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 36 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, view 'Applications In Scope for DR Test BSI'
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, BIA results &amp; applications list review
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, ReconXpert listed under 'Applications To Test' for Financial Analysis and Control (Sadis Alvarenga Hernandez)
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
         </is>
       </c>
       <c r="N12" s="52" t="inlineStr">
         <is>
-          <t>BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, business line DIV results document, 11/15/2025, Finance &amp; Accounting Reporting (operator Dunia Gonzalez Collado)
-BLA06: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, Department Manager / Approval Date / Attestation fields
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Sadis Alvarenga); scope confirmation only</t>
+          <t>BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf, business line DIV results document, 11/15/2025, Finance &amp; Accounting Reporting (operator Dunia Gonzalez Collado)
+BLA06: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 17, Department Manager / Approval Date / Attestation fields
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Sadis Alvarenga); scope confirmation only</t>
         </is>
       </c>
       <c r="O12" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 17
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, row 17
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, row 17
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, BCiC report screen (record on a later page of the 66-item report)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P12" s="52" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf
-BLA06: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf
+BLA06: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg
 [03 DIV Manager Attestation Email Approvals]
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E10: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E10: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="Q12" s="52" t="inlineStr">
@@ -27236,161 +27236,161 @@
       </c>
       <c r="B13" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 42, Exercise Date 11/15/25, 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 7, 61, Business Data Validation Date 11/15/2025
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, script header DATE: 11/15/2025
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, script header DATE: 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 42, Exercise Date 11/15/25, 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 7, 60, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 7, 61, Business Data Validation Date 11/15/2025
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, script header DATE: 11/15/2025
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, script header DATE: 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
         </is>
       </c>
       <c r="C13" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 1936 selected; 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 42, Application ID 1936
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC view 'Applications In Scope for DR Test BSI'
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 7, 61
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 1936 selected; 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 42, Application ID 1936
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC view 'Applications In Scope for DR Test BSI'
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 7, 60
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 7, 61
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen</t>
         </is>
       </c>
       <c r="D13" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, 'Business Tester(s)' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 7, 61
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Tester(s) column
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, PRINT NAME OF OPERATOR: Frank Puentes / Gustavo Bucaro
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, PRINT NAME OF OPERATOR: Michelle Oropesa</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 7, 60, 'Business Tester(s)' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 7, 61
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Business Tester(s) column
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, PRINT NAME OF OPERATOR: Frank Puentes / Gustavo Bucaro
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, PRINT NAME OF OPERATOR: Michelle Oropesa</t>
         </is>
       </c>
       <c r="E13" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 7, 61 to 11/15/2025; Format, Headers and Content validated
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and validation result columns
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, pp.1-2 DIV section (Format / Headers / Content = yes; 11/14 Fed &amp; SWIFT data reconciled)
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, DIV table (Format / Headers / Content = Yes; MT300 &amp; FX S reports matched 11/14 versus 11/15)
-E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg, pre-DR source reports 11/14/2025 (Payment Monitor, OFAC, SWIFT Interface Monitor)
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg, DR test-day 11/15/2025 comparison reports</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 7, 60, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 7, 61 to 11/15/2025; Format, Headers and Content validated
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Business Data Validation Date and validation result columns
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, pp.1-2 DIV section (Format / Headers / Content = yes; 11/14 Fed &amp; SWIFT data reconciled)
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, DIV table (Format / Headers / Content = Yes; MT300 &amp; FX S reports matched 11/14 versus 11/15)
+E07: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg, pre-DR source reports 11/14/2025 (Payment Monitor, OFAC, SWIFT Interface Monitor)
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg, DR test-day 11/15/2025 comparison reports</t>
         </is>
       </c>
       <c r="F13" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, 'Department Manager' column
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Department Manager column
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Jaime Verastegui (BSA/AML/OFAC); Michelle Oropesa (Investment Operations); Franklin Puentes (Payments &amp; Cash Management)</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 7, 60, 'Department Manager' column
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Department Manager column
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Jaime Verastegui (BSA/AML/OFAC); Michelle Oropesa (Investment Operations); Franklin Puentes (Payments &amp; Cash Management)</t>
         </is>
       </c>
       <c r="G13" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, 'Department Manager Approval Date' and 'Attestation Date' columns
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Department Manager Approval Date column
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 7, 60, 'Department Manager Approval Date' and 'Attestation Date' columns
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Department Manager Approval Date column
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="H13" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, 'Data Integrity Validation Procedures' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 7, 61, 'Data Integrity Validation Procedures' column
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 7, 60, 'Data Integrity Validation Procedures' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 7, 61, 'Data Integrity Validation Procedures' column
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
         </is>
       </c>
       <c r="I13" s="52" t="inlineStr">
         <is>
-          <t>DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="J13" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, BCiC DIV export (tester, dates, manager, validation results, attestation)
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 7, 61, BCiC DIV export 2025-26 reviewed with the attestation
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 42
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC DR-scope view
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, App ID 1936 selected in BCiC in-scope view</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 7, 60, BCiC DIV export (tester, dates, manager, validation results, attestation)
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 7, 61, BCiC DIV export 2025-26 reviewed with the attestation
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 42
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC DR-scope view
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, App ID 1936 selected in BCiC in-scope view</t>
         </is>
       </c>
       <c r="K13" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 42, Exercise Date 11/15/2025 / 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, dated 11/15/2025
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, dated 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 42, Exercise Date 11/15/2025 / 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 7, 60, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, dated 11/15/2025
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, dated 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
         </is>
       </c>
       <c r="L13" s="52" t="inlineStr">
         <is>
-          <t>E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, IT DR test script completed by the business-line tester
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg, business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, Format, Headers and Content validated
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
+          <t>E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, IT DR test script completed by the business-line tester
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, IT DR test script completed by the business-line tester
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg, business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 7, 60, Format, Headers and Content validated
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
         </is>
       </c>
       <c r="M13" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 1936 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 42 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, view 'Applications In Scope for DR Test BSI'
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, BIA results &amp; applications list review
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, Swift Interface - BSI listed under 'Applications To Test' for BSA/AML/OFAC (Jaime Verastegui); Investment Operations (Michelle Oropesa); Payments &amp; Cash Management (Franklin Puentes)
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 1936 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 42 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, view 'Applications In Scope for DR Test BSI'
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, BIA results &amp; applications list review
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, Swift Interface - BSI listed under 'Applications To Test' for BSA/AML/OFAC (Jaime Verastegui); Investment Operations (Michelle Oropesa); Payments &amp; Cash Management (Franklin Puentes)
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, Not on the DRS01 IT-application list (business-data application tested by the business lines).</t>
         </is>
       </c>
       <c r="N13" s="52" t="inlineStr">
         <is>
-          <t>BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, business line DIV results document, 11/15/2025, Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, business line DIV results document, 11/15/2025, Investment Operations (operator Michelle Oropesa)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, Department Manager / Approval Date / Attestation fields
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Michelle Oropesa, Frank Puentes); scope confirmation only</t>
+          <t>BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, business line DIV results document, 11/15/2025, Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, business line DIV results document, 11/15/2025, Investment Operations (operator Michelle Oropesa)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 7, 60, Department Manager / Approval Date / Attestation fields
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Michelle Oropesa, Frank Puentes); scope confirmation only</t>
         </is>
       </c>
       <c r="O13" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 7, 61
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 7, 60
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 7, 61
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P13" s="52" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx
 [03 DIV Manager Attestation Email Approvals]
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E07: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="Q13" s="52" t="inlineStr">
@@ -27405,247 +27405,247 @@
       </c>
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 43, Exercise Date 11/15/25, 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64, Business Data Validation Date 11/15/2025
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, script header DATE: 11/15/2025
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, script header DATE: 11/15/2025
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, script header DATE: 11/15/2025
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, script header DATE: 11/15/2025
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, script header DATE: 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 43, Exercise Date 11/15/25, 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64, Business Data Validation Date 11/15/2025
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover from Miami-Telefonica to the DR site)
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, script header DATE: 11/15/2025
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, script header DATE: 11/15/2025
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, script header DATE: 11/15/2025
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, script header DATE: 11/15/2025
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf, script header DATE: 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, same exercise name</t>
         </is>
       </c>
       <c r="C14" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 1937 selected; 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 43, Application ID 1937
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC view 'Applications In Scope for DR Test BSI'
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 1937 selected; 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 43, Application ID 1937
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC view 'Applications In Scope for DR Test BSI'
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen</t>
         </is>
       </c>
       <c r="D14" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, 'Business Tester(s)' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Tester(s) column
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, PRINT NAME OF OPERATOR: Raimy Ayala
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, PRINT NAME OF OPERATOR: David Marquez
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, PRINT NAME OF OPERATOR: Frank Puentes / Gustavo Bucaro
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, PRINT NAME OF OPERATOR: Michelle Oropesa
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, PRINT NAME OF OPERATOR: Dunia Gonzalez Collado</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, 'Business Tester(s)' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Business Tester(s) column
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, PRINT NAME OF OPERATOR: Raimy Ayala
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, PRINT NAME OF OPERATOR: David Marquez
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, PRINT NAME OF OPERATOR: Frank Puentes / Gustavo Bucaro
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, PRINT NAME OF OPERATOR: Michelle Oropesa
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf, PRINT NAME OF OPERATOR: Dunia Gonzalez Collado</t>
         </is>
       </c>
       <c r="E14" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64 to 11/15/2025; Format, Headers and Content validated
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and validation result columns
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, p.1 DIV procedure &amp; in-scope apps; pp.2-14 production-day 11/14 versus test-day 11/15 screenshots
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, pp.1-2 DIV section (Format / Headers / Content = yes; 11/14 Fed &amp; SWIFT data reconciled)
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, DIV table (Format / Headers / Content = Yes; MT300 &amp; FX S reports matched 11/14 versus 11/15)
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Yes / Yes / Yes, no discrepancies); pp.2-9 reconciliation reports 11/13 versus 11/15
-E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg, pre-DR source reports 11/14/2025 (Payment Monitor, OFAC, SWIFT Interface Monitor)
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg, DR test-day 11/15/2025 comparison reports</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64 to 11/15/2025; Format, Headers and Content validated
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Business Data Validation Date and validation result columns
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, p.1 DIV procedure &amp; in-scope apps; pp.2-14 production-day 11/14 versus test-day 11/15 screenshots
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, pp.1-2 DIV section (Format / Headers / Content = yes; 11/14 Fed &amp; SWIFT data reconciled)
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, DIV table (Format / Headers / Content = Yes; MT300 &amp; FX S reports matched 11/14 versus 11/15)
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf, p.1 DIV section (Yes / Yes / Yes, no discrepancies); pp.2-9 reconciliation reports 11/13 versus 11/15
+E07: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg, pre-DR source reports 11/14/2025 (Payment Monitor, OFAC, SWIFT Interface Monitor)
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg, DR test-day 11/15/2025 comparison reports</t>
         </is>
       </c>
       <c r="F14" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, 'Department Manager' column
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Department Manager column
-DMA06: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA11: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-BLA06: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA07: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-DMA12: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
-DMA10: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
-DMA08: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
-DMA09: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Lorena Otero; Miguel Orozco; Victoria Fernandez; Sadis Alvarenga Hernandez; Eduardo Fernandez / Ricardo Valdivia; Niccolo Gregoratti; Alfonso Camano; Clara De Castro; Ricardo Garcia / Christian Miranda; Jaime Verastegui; Xavier Caisapanta / Genevieve Barquin; Claudia Romero; Gabriela Hernandez Gonzalez; Marcel Garcia; Michelle Oropesa; Franklin Puentes</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, 'Department Manager' column
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Department Manager column
+DMA06: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA11: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml
+BLA06: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
+DMA07: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg
+DMA12: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA12_ClientServicing_Vizhnay_2026-09-09.eml
+DMA10: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA10_DigitalWealth_Fernandez_2026-08-21.eml
+DMA08: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA08_FinancialRisk_Caisapanta_2026-08-18.msg
+DMA09: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, Recovery Coordinator(s): Lorena Otero; Miguel Orozco; Victoria Fernandez; Sadis Alvarenga Hernandez; Eduardo Fernandez / Ricardo Valdivia; Niccolo Gregoratti; Alfonso Camano; Clara De Castro; Ricardo Garcia / Christian Miranda; Jaime Verastegui; Xavier Caisapanta / Genevieve Barquin; Claudia Romero; Gabriela Hernandez Gonzalez; Marcel Garcia; Michelle Oropesa; Franklin Puentes</t>
         </is>
       </c>
       <c r="G14" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, 'Department Manager Approval Date' and 'Attestation Date' columns
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Department Manager Approval Date column
-DMA06: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA11: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-BLA06: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA07: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-DMA12: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
-DMA10: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
-DMA08: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
-DMA09: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, 'Department Manager Approval Date' and 'Attestation Date' columns
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, Department Manager Approval Date column
+DMA06: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA11: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml
+BLA06: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
+DMA07: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg
+DMA12: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA12_ClientServicing_Vizhnay_2026-09-09.eml
+DMA10: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA10_DigitalWealth_Fernandez_2026-08-21.eml
+DMA08: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA08_FinancialRisk_Caisapanta_2026-08-18.msg
+DMA09: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg</t>
         </is>
       </c>
       <c r="H14" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, 'Data Integrity Validation Procedures' column
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64, 'Data Integrity Validation Procedures' column
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, 'Data Integrity Validation Procedures' column
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64, 'Data Integrity Validation Procedures' column
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf, 'Data Integrity Validation Testing' section, procedure instructions, application in-scope line and Format / Headers / Content questions</t>
         </is>
       </c>
       <c r="I14" s="52" t="inlineStr">
         <is>
-          <t>DMA06: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA11: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-BLA06: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA07: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-DMA12: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
-DMA10: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
-DMA08: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
-DMA09: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+          <t>DMA06: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA11: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml
+BLA06: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
+DMA07: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg
+DMA12: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA12_ClientServicing_Vizhnay_2026-09-09.eml
+DMA10: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA10_DigitalWealth_Fernandez_2026-08-21.eml
+DMA08: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA08_FinancialRisk_Caisapanta_2026-08-18.msg
+DMA09: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg</t>
         </is>
       </c>
       <c r="J14" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, BCiC DIV export (tester, dates, manager, validation results, attestation)
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64, BCiC DIV export 2025-26 reviewed with the attestation
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 43
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, BCiC DR-scope view
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, App ID 1937 selected in BCiC in-scope view</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, BCiC DIV export (tester, dates, manager, validation results, attestation)
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64, BCiC DIV export 2025-26 reviewed with the attestation
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 43
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, BCiC DR-scope view
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, App ID 1937 selected in BCiC in-scope view</t>
         </is>
       </c>
       <c r="K14" s="52" t="inlineStr">
         <is>
-          <t>E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 43, Exercise Date 11/15/2025 / 2025 DR Test Scope = True
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, Business Data Validation Date 11/15/2025 / Last App DR Test Date
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, dated 11/15/2025
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, dated 11/15/2025
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, dated 11/15/2025
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, dated 11/15/2025
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, dated 11/15/2025
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
+          <t>E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 43, Exercise Date 11/15/2025 / 2025 DR Test Scope = True
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, Business Data Validation Date 11/15/2025 / Last App DR Test Date
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation section 1, DIV facilitated on an annual basis
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, dated 11/15/2025
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, dated 11/15/2025
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, dated 11/15/2025
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, dated 11/15/2025
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf, dated 11/15/2025
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, 'yearly Disaster Recovery (DR) Test'
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, 'yearly Disaster Recovery (DR) Test'</t>
         </is>
       </c>
       <c r="L14" s="52" t="inlineStr">
         <is>
-          <t>E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, IT DR test script completed by the business-line tester
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg, business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
-E10: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg, IT DR (Elizabeth Noda) Finance DIV chart and approval request
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, Format, Headers and Content validated
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
+          <t>E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, IT DR test script completed by the business-line tester
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, IT DR test script completed by the business-line tester
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, IT DR test script completed by the business-line tester
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, IT DR test script completed by the business-line tester
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf, IT DR test script completed by the business-line tester
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg, business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
+E10: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg, IT DR (Elizabeth Noda) Finance DIV chart and approval request
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, Format, Headers and Content validated
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, IT DR team requests IT application testers
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, IT DR team sends applications to test / recovery coordinators to the business lines</t>
         </is>
       </c>
       <c r="M14" s="52" t="inlineStr">
         <is>
-          <t>MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png, BSI In-Scope Applications-2026, App ID 1937 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 43 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg, view 'Applications In Scope for DR Test BSI'
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, BIA results &amp; applications list review
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, T24 listed under 'Applications To Test' for 16 of 18 departments (see DRS02); also in the IT Scope as 'T24 - Job Scheduling' (DRS01)
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml, IT Scope email 10/08/2025, DRS01 (IT Scope, 10/08/2025) also lists T24 under 'Application In scope' for the Job Scheduling process.</t>
+          <t>MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png, BSI In-Scope Applications-2026, App ID 1937 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx, row 43 to 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg, view 'Applications In Scope for DR Test BSI'
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg, BIA results &amp; applications list review
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 2, application listed among the 13 in-scope applications that store business data
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, T24 listed under 'Applications To Test' for 16 of 18 departments (see DRS02); also in the IT Scope as 'T24 - Job Scheduling' (DRS01)
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml, IT Scope email 10/08/2025, DRS01 (IT Scope, 10/08/2025) also lists T24 under 'Application In scope' for the Job Scheduling process.</t>
         </is>
       </c>
       <c r="N14" s="52" t="inlineStr">
         <is>
-          <t>BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, business line DIV results document, 11/15/2025, Client Back Office (operator Raimy Ayala)
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, business line DIV results document, 11/15/2025, BSA/AML/OFAC Compliance (operator David Marquez)
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, business line DIV results document, 11/15/2025, Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, business line DIV results document, 11/15/2025, Investment Operations (operator Michelle Oropesa)
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, business line DIV results document, 11/15/2025, Finance &amp; Accounting Reporting (operator Dunia Gonzalez Collado)
-DMA06: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA11: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-BLA06: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA07: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-DMA12: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
-DMA10: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
-DMA08: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
-DMA09: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, Department Manager / Approval Date / Attestation fields
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Ricardo Garcia-Marques, Claudia Romero, Miguel Orozco, Sadis Alvarenga, Michelle Oropesa, Frank Puentes, Victoria Fernandez, Ivan (Xavier) Caisapanta, Clara De Castro, Martha Sullivan, Liliana Vizhnay, Maria Teresa Del Cerro); scope confirmation only</t>
+          <t>BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf, business line DIV results document, 11/15/2025, Client Back Office (operator Raimy Ayala)
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf, business line DIV results document, 11/15/2025, BSA/AML/OFAC Compliance (operator David Marquez)
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf, business line DIV results document, 11/15/2025, Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx, business line DIV results document, 11/15/2025, Investment Operations (operator Michelle Oropesa)
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf, business line DIV results document, 11/15/2025, Finance &amp; Accounting Reporting (operator Dunia Gonzalez Collado)
+DMA06: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA11: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml
+BLA06: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
+DMA07: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg
+DMA12: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA12_ClientServicing_Vizhnay_2026-09-09.eml
+DMA10: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA10_DigitalWealth_Fernandez_2026-08-21.eml
+DMA08: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA08_FinancialRisk_Caisapanta_2026-08-18.msg
+DMA09: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, Department Manager / Approval Date / Attestation fields
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml, Business Scope email 10/06/2025 / 10/08/2025, application scope communicated to the business line managers (Ricardo Garcia-Marques, Claudia Romero, Miguel Orozco, Sadis Alvarenga, Michelle Oropesa, Frank Puentes, Victoria Fernandez, Ivan (Xavier) Caisapanta, Clara De Castro, Martha Sullivan, Liliana Vizhnay, Maria Teresa Del Cerro); scope confirmation only</t>
         </is>
       </c>
       <c r="O14" s="52" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg, records visible on screen
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg, attached signed attestation section 3.5, attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P14" s="52" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
-MA01: BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA01: BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA01_InScope_Apps_2026.png
 [02 Business Line Approval Results: Email]
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
-BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
-BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
-BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
-BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf
-BLA06: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
+BLA01: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf
+BLA02: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf
+BLA03: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA03_Payments_DIV_Results_2025-11-15.pdf
+BLA04: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA04_InvestmentOps_DIV_Results_2025-11-15.docx
+BLA05: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf
+BLA06: BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg
 [03 DIV Manager Attestation Email Approvals]
-DMA01: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA03: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA04: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-DMA05: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DMA06: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-DMA07: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-DMA08: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
-DMA09: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg
-DMA10: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
-DMA11: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-DMA12: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
+DMA01: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg
+DMA02: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg
+DMA03: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg
+DMA04: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg
+DMA05: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg
+DMA06: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg
+DMA07: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg
+DMA08: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA08_FinancialRisk_Caisapanta_2026-08-18.msg
+DMA09: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg
+DMA10: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA10_DigitalWealth_Fernandez_2026-08-21.eml
+DMA11: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA11_CommMiddleOffice_Orozco_2026-09-09.eml
+DMA12: BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA12_ClientServicing_Vizhnay_2026-09-09.eml
 [04 Data Integrity &amp; Email Testing Evidence]
-E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
-E02: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
-E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
-E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E10: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+E01: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E01_BCiC_Apps_InScope_DR.xlsx
+E02: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E02_BCiC_Apps_InScope_Screenshot.jpg
+E03: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E03_BCiC_DIV_Testing_Export.xls
+E04: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E04_BCiC_DIV_Report_Screenshot.jpg
+E05: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg
+E07: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg
+E08: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg
+E09: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E09_ClientBackOffice_BackupRestore_Signoff.msg
+E10: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg
+E16b: BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx
 [05 Annual DR Exercise Scope Emails: IT Scope &amp; Business Scope]
-DRS01: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml
-DRS02: BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+DRS01: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml
+DRS02: BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="Q14" s="52" t="inlineStr">
@@ -27858,12 +27858,12 @@
       </c>
       <c r="B3" s="84" t="inlineStr">
         <is>
-          <t>MA01_BSI In-Scope Applications-2026.png</t>
+          <t>MA01_InScope_Apps_2026.png</t>
         </is>
       </c>
       <c r="C3" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_InScope_Apps</t>
         </is>
       </c>
       <c r="D3" s="57" t="inlineStr">
@@ -27912,12 +27912,12 @@
       </c>
       <c r="B4" s="84" t="inlineStr">
         <is>
-          <t>BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
+          <t>BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C4" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results</t>
         </is>
       </c>
       <c r="D4" s="57" t="inlineStr">
@@ -27966,12 +27966,12 @@
       </c>
       <c r="B5" s="84" t="inlineStr">
         <is>
-          <t>BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
+          <t>BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C5" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results</t>
         </is>
       </c>
       <c r="D5" s="57" t="inlineStr">
@@ -28020,12 +28020,12 @@
       </c>
       <c r="B6" s="84" t="inlineStr">
         <is>
-          <t>BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
+          <t>BLA03_Payments_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C6" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results</t>
         </is>
       </c>
       <c r="D6" s="57" t="inlineStr">
@@ -28074,12 +28074,12 @@
       </c>
       <c r="B7" s="84" t="inlineStr">
         <is>
-          <t>BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
+          <t>BLA04_InvestmentOps_DIV_Results_2025-11-15.docx</t>
         </is>
       </c>
       <c r="C7" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results</t>
         </is>
       </c>
       <c r="D7" s="57" t="inlineStr">
@@ -28128,12 +28128,12 @@
       </c>
       <c r="B8" s="84" t="inlineStr">
         <is>
-          <t>BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
+          <t>BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf</t>
         </is>
       </c>
       <c r="C8" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results</t>
         </is>
       </c>
       <c r="D8" s="57" t="inlineStr">
@@ -28182,12 +28182,12 @@
       </c>
       <c r="B9" s="84" t="inlineStr">
         <is>
-          <t>BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="C9" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results</t>
         </is>
       </c>
       <c r="D9" s="57" t="inlineStr">
@@ -28236,12 +28236,12 @@
       </c>
       <c r="B10" s="84" t="inlineStr">
         <is>
-          <t>DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C10" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals</t>
         </is>
       </c>
       <c r="D10" s="57" t="inlineStr">
@@ -28290,12 +28290,12 @@
       </c>
       <c r="B11" s="84" t="inlineStr">
         <is>
-          <t>DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="C11" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals</t>
         </is>
       </c>
       <c r="D11" s="57" t="inlineStr">
@@ -28344,12 +28344,12 @@
       </c>
       <c r="B12" s="84" t="inlineStr">
         <is>
-          <t>DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C12" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals</t>
         </is>
       </c>
       <c r="D12" s="57" t="inlineStr">
@@ -28398,12 +28398,12 @@
       </c>
       <c r="B13" s="84" t="inlineStr">
         <is>
-          <t>DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="C13" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals</t>
         </is>
       </c>
       <c r="D13" s="57" t="inlineStr">
@@ -28452,12 +28452,12 @@
       </c>
       <c r="B14" s="84" t="inlineStr">
         <is>
-          <t>DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>DMA05_Operations_DelCerro_2026-08-19.msg</t>
         </is>
       </c>
       <c r="C14" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals</t>
         </is>
       </c>
       <c r="D14" s="57" t="inlineStr">
@@ -28506,12 +28506,12 @@
       </c>
       <c r="B15" s="84" t="inlineStr">
         <is>
-          <t>DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+          <t>DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C15" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals</t>
         </is>
       </c>
       <c r="D15" s="57" t="inlineStr">
@@ -28560,12 +28560,12 @@
       </c>
       <c r="B16" s="84" t="inlineStr">
         <is>
-          <t>DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+          <t>DMA07_Treasury_Sullivan_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C16" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals</t>
         </is>
       </c>
       <c r="D16" s="57" t="inlineStr">
@@ -28614,12 +28614,12 @@
       </c>
       <c r="B17" s="84" t="inlineStr">
         <is>
-          <t>DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
+          <t>DMA08_FinancialRisk_Caisapanta_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C17" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals</t>
         </is>
       </c>
       <c r="D17" s="57" t="inlineStr">
@@ -28668,12 +28668,12 @@
       </c>
       <c r="B18" s="84" t="inlineStr">
         <is>
-          <t>DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+          <t>DMA09_GeneralServices_DeCastro_2026-08-18.msg</t>
         </is>
       </c>
       <c r="C18" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals</t>
         </is>
       </c>
       <c r="D18" s="57" t="inlineStr">
@@ -28722,12 +28722,12 @@
       </c>
       <c r="B19" s="84" t="inlineStr">
         <is>
-          <t>DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+          <t>DMA10_DigitalWealth_Fernandez_2026-08-21.eml</t>
         </is>
       </c>
       <c r="C19" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals</t>
         </is>
       </c>
       <c r="D19" s="57" t="inlineStr">
@@ -28776,12 +28776,12 @@
       </c>
       <c r="B20" s="84" t="inlineStr">
         <is>
-          <t>DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+          <t>DMA11_CommMiddleOffice_Orozco_2026-09-09.eml</t>
         </is>
       </c>
       <c r="C20" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals</t>
         </is>
       </c>
       <c r="D20" s="57" t="inlineStr">
@@ -28830,12 +28830,12 @@
       </c>
       <c r="B21" s="84" t="inlineStr">
         <is>
-          <t>DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+          <t>DMA12_ClientServicing_Vizhnay_2026-09-09.eml</t>
         </is>
       </c>
       <c r="C21" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals</t>
         </is>
       </c>
       <c r="D21" s="57" t="inlineStr">
@@ -28884,12 +28884,12 @@
       </c>
       <c r="B22" s="84" t="inlineStr">
         <is>
-          <t>DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
+          <t>DMA13_CiscoCallMgr_Noda_2026-09-09_OutOfScope.eml</t>
         </is>
       </c>
       <c r="C22" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals</t>
         </is>
       </c>
       <c r="D22" s="57" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="B23" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>E01_BCiC_Apps_InScope_DR.xlsx</t>
         </is>
       </c>
       <c r="C23" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing</t>
         </is>
       </c>
       <c r="D23" s="57" t="inlineStr">
@@ -28988,12 +28988,12 @@
       </c>
       <c r="B24" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>E02_BCiC_Apps_InScope_Screenshot.jpg</t>
         </is>
       </c>
       <c r="C24" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing</t>
         </is>
       </c>
       <c r="D24" s="57" t="inlineStr">
@@ -29042,12 +29042,12 @@
       </c>
       <c r="B25" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>E03_BCiC_DIV_Testing_Export.xls</t>
         </is>
       </c>
       <c r="C25" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing</t>
         </is>
       </c>
       <c r="D25" s="57" t="inlineStr">
@@ -29096,12 +29096,12 @@
       </c>
       <c r="B26" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+          <t>E04_BCiC_DIV_Report_Screenshot.jpg</t>
         </is>
       </c>
       <c r="C26" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing</t>
         </is>
       </c>
       <c r="D26" s="57" t="inlineStr">
@@ -29150,12 +29150,12 @@
       </c>
       <c r="B27" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+          <t>E05_IT_BIA_Review_DR_Prep.msg</t>
         </is>
       </c>
       <c r="C27" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing</t>
         </is>
       </c>
       <c r="D27" s="57" t="inlineStr">
@@ -29204,12 +29204,12 @@
       </c>
       <c r="B28" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+          <t>E07_DIV_Source_Files_2025-11-14.msg</t>
         </is>
       </c>
       <c r="C28" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing</t>
         </is>
       </c>
       <c r="D28" s="57" t="inlineStr">
@@ -29258,12 +29258,12 @@
       </c>
       <c r="B29" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>E08_DR_Test_Files_2025-11-15.msg</t>
         </is>
       </c>
       <c r="C29" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing</t>
         </is>
       </c>
       <c r="D29" s="57" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="B30" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+          <t>E09_ClientBackOffice_BackupRestore_Signoff.msg</t>
         </is>
       </c>
       <c r="C30" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing</t>
         </is>
       </c>
       <c r="D30" s="57" t="inlineStr">
@@ -29366,12 +29366,12 @@
       </c>
       <c r="B31" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+          <t>E10_Finance_BackupRestore_Approval.msg</t>
         </is>
       </c>
       <c r="C31" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing</t>
         </is>
       </c>
       <c r="D31" s="57" t="inlineStr">
@@ -29420,12 +29420,12 @@
       </c>
       <c r="B32" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
+          <t>E13_T24_Env_Refresh_2024-11-13.msg</t>
         </is>
       </c>
       <c r="C32" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing</t>
         </is>
       </c>
       <c r="D32" s="57" t="inlineStr">
@@ -29470,12 +29470,12 @@
       </c>
       <c r="B33" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>E16b_BCiC_DIV_Testing_2025-26.xlsx</t>
         </is>
       </c>
       <c r="C33" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing</t>
         </is>
       </c>
       <c r="D33" s="57" t="inlineStr">
@@ -29524,12 +29524,12 @@
       </c>
       <c r="B34" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C34" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails</t>
         </is>
       </c>
       <c r="D34" s="57" t="inlineStr">
@@ -29581,12 +29581,12 @@
       </c>
       <c r="B35" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml</t>
         </is>
       </c>
       <c r="C35" s="84" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails</t>
+          <t>BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails</t>
         </is>
       </c>
       <c r="D35" s="57" t="inlineStr">
@@ -29704,7 +29704,7 @@
       </c>
       <c r="B39" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_InScope_Apps\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C39" s="57" t="inlineStr">
@@ -29714,7 +29714,7 @@
       </c>
       <c r="D39" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="E39" s="57" t="inlineStr">
@@ -29738,7 +29738,7 @@
       </c>
       <c r="B40" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05b_Operations (Governance &amp; Static Data, Multi-Family Office) - All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\Signed_Attestations_extracted\DMA05b_Operations (Governance &amp; Static Data, Multi-Family Office) - All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="C40" s="57" t="inlineStr">
@@ -29748,7 +29748,7 @@
       </c>
       <c r="D40" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E16b_BCiC_DIV_Testing_2025-26.xlsx</t>
         </is>
       </c>
       <c r="E40" s="57" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="B41" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg</t>
         </is>
       </c>
       <c r="C41" s="57" t="inlineStr">
@@ -29782,7 +29782,7 @@
       </c>
       <c r="D41" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E10_Finance_BackupRestore_Approval.msg</t>
         </is>
       </c>
       <c r="E41" s="57" t="inlineStr">
@@ -29806,7 +29806,7 @@
       </c>
       <c r="B42" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg</t>
         </is>
       </c>
       <c r="C42" s="57" t="inlineStr">
@@ -29816,7 +29816,7 @@
       </c>
       <c r="D42" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_BL_Results\BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg</t>
         </is>
       </c>
       <c r="E42" s="57" t="inlineStr">
@@ -29840,7 +29840,7 @@
       </c>
       <c r="B43" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml</t>
         </is>
       </c>
       <c r="C43" s="57" t="inlineStr">
@@ -29850,7 +29850,7 @@
       </c>
       <c r="D43" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="E43" s="57" t="inlineStr">
@@ -29874,7 +29874,7 @@
       </c>
       <c r="B44" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
         </is>
       </c>
       <c r="C44" s="57" t="inlineStr">
@@ -29884,7 +29884,7 @@
       </c>
       <c r="D44" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="E44" s="57" t="inlineStr">
@@ -29908,7 +29908,7 @@
       </c>
       <c r="B45" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml</t>
         </is>
       </c>
       <c r="C45" s="57" t="inlineStr">
@@ -29918,7 +29918,7 @@
       </c>
       <c r="D45" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="E45" s="57" t="inlineStr">
@@ -29942,7 +29942,7 @@
       </c>
       <c r="B46" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C46" s="57" t="inlineStr">
@@ -29952,7 +29952,7 @@
       </c>
       <c r="D46" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="E46" s="57" t="inlineStr">
@@ -29976,7 +29976,7 @@
       </c>
       <c r="B47" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml</t>
         </is>
       </c>
       <c r="C47" s="57" t="inlineStr">
@@ -29986,7 +29986,7 @@
       </c>
       <c r="D47" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg</t>
         </is>
       </c>
       <c r="E47" s="57" t="inlineStr">
@@ -30010,7 +30010,7 @@
       </c>
       <c r="B48" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C48" s="57" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="D48" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg</t>
         </is>
       </c>
       <c r="E48" s="57" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="B49" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml</t>
         </is>
       </c>
       <c r="C49" s="57" t="inlineStr">
@@ -30054,7 +30054,7 @@
       </c>
       <c r="D49" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="E49" s="57" t="inlineStr">
@@ -30078,7 +30078,7 @@
       </c>
       <c r="B50" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\BSI.IT.6.C7.3_E17a_4069_001.pdf</t>
         </is>
       </c>
       <c r="C50" s="57" t="inlineStr">
@@ -30088,7 +30088,7 @@
       </c>
       <c r="D50" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="E50" s="57" t="inlineStr">
@@ -30112,7 +30112,7 @@
       </c>
       <c r="B51" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
         </is>
       </c>
       <c r="C51" s="57" t="inlineStr">
@@ -30122,7 +30122,7 @@
       </c>
       <c r="D51" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA01_ClientBackOffice_Romero_2026-08-18.msg</t>
         </is>
       </c>
       <c r="E51" s="57" t="inlineStr">
@@ -30146,7 +30146,7 @@
       </c>
       <c r="B52" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
         </is>
       </c>
       <c r="C52" s="57" t="inlineStr">
@@ -30156,7 +30156,7 @@
       </c>
       <c r="D52" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg</t>
         </is>
       </c>
       <c r="E52" s="57" t="inlineStr">
@@ -30180,7 +30180,7 @@
       </c>
       <c r="B53" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
         </is>
       </c>
       <c r="C53" s="57" t="inlineStr">
@@ -30190,7 +30190,7 @@
       </c>
       <c r="D53" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA03_Payments_Puentes_2026-08-18.msg</t>
         </is>
       </c>
       <c r="E53" s="57" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="B54" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C54" s="57" t="inlineStr">
@@ -30224,7 +30224,7 @@
       </c>
       <c r="D54" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA04_InvestmentOps_Oropesa_2026-08-17.msg</t>
         </is>
       </c>
       <c r="E54" s="57" t="inlineStr">
@@ -30248,7 +30248,7 @@
       </c>
       <c r="B55" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C55" s="57" t="inlineStr">
@@ -30258,7 +30258,7 @@
       </c>
       <c r="D55" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA05_Operations_DelCerro_2026-08-19.msg</t>
         </is>
       </c>
       <c r="E55" s="57" t="inlineStr">
@@ -30282,7 +30282,7 @@
       </c>
       <c r="B56" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf</t>
         </is>
       </c>
       <c r="C56" s="57" t="inlineStr">
@@ -30292,7 +30292,7 @@
       </c>
       <c r="D56" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg</t>
         </is>
       </c>
       <c r="E56" s="57" t="inlineStr">
@@ -30316,7 +30316,7 @@
       </c>
       <c r="B57" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C57" s="57" t="inlineStr">
@@ -30326,7 +30326,7 @@
       </c>
       <c r="D57" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA07_Treasury_Sullivan_2026-08-18.msg</t>
         </is>
       </c>
       <c r="E57" s="57" t="inlineStr">
@@ -30350,7 +30350,7 @@
       </c>
       <c r="B58" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C58" s="57" t="inlineStr">
@@ -30360,7 +30360,7 @@
       </c>
       <c r="D58" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals\DMA09_GeneralServices_DeCastro_2026-08-18.msg</t>
         </is>
       </c>
       <c r="E58" s="57" t="inlineStr">
@@ -30384,7 +30384,7 @@
       </c>
       <c r="B59" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\E07_Attachments_extracted (13 files)</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_Attachments_extracted (13 files)</t>
         </is>
       </c>
       <c r="C59" s="57" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="D59" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E07_DIV_Source_Files_2025-11-14.msg</t>
         </is>
       </c>
       <c r="E59" s="57" t="inlineStr">
@@ -30418,7 +30418,7 @@
       </c>
       <c r="B60" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\E08_Attachments_extracted (13 files)</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_Attachments_extracted (13 files)</t>
         </is>
       </c>
       <c r="C60" s="57" t="inlineStr">
@@ -30428,7 +30428,7 @@
       </c>
       <c r="D60" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E08_DR_Test_Files_2025-11-15.msg</t>
         </is>
       </c>
       <c r="E60" s="57" t="inlineStr">
@@ -30452,7 +30452,7 @@
       </c>
       <c r="B61" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml</t>
         </is>
       </c>
       <c r="C61" s="57" t="inlineStr">
@@ -30462,7 +30462,7 @@
       </c>
       <c r="D61" s="57" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_DIV_Testing\E05_IT_BIA_Review_DR_Prep.msg</t>
         </is>
       </c>
       <c r="E61" s="57" t="inlineStr">
@@ -31336,104 +31336,104 @@
   <autoFilter ref="A2:K35"/>
   <hyperlinks>
     <hyperlink ref="A3" location="'Application Attribute Testing'!A98" display="MA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" display="MA01_BSI In-Scope Applications-2026.png" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" display="BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" display="MA01_InScope_Apps_2026.png" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" display="BSI.IT.6.C7.3-Evidences\01_InScope_Apps" r:id="rId2"/>
     <hyperlink ref="A4" location="'Application Attribute Testing'!A73" display="BLA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" display="BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" display="BLA01_ClientBackOffice_DIV_Results_2025-11-15.pdf" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" display="BSI.IT.6.C7.3-Evidences\02_BL_Results" r:id="rId4"/>
     <hyperlink ref="A5" location="'Application Attribute Testing'!A74" display="BLA02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" display="BLA02_BSA_AML_OFAC_DIV_Results_2025-11-15.pdf" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" display="BSI.IT.6.C7.3-Evidences\02_BL_Results" r:id="rId6"/>
     <hyperlink ref="A6" location="'Application Attribute Testing'!A75" display="BLA03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" display="BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" display="BLA03_Payments_DIV_Results_2025-11-15.pdf" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" display="BSI.IT.6.C7.3-Evidences\02_BL_Results" r:id="rId8"/>
     <hyperlink ref="A7" location="'Application Attribute Testing'!A76" display="BLA04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" display="BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" display="BLA04_InvestmentOps_DIV_Results_2025-11-15.docx" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" display="BSI.IT.6.C7.3-Evidences\02_BL_Results" r:id="rId10"/>
     <hyperlink ref="A8" location="'Application Attribute Testing'!A77" display="BLA05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" display="BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" display="BLA05_FinAnalysis_ReconXpert_DIV_Results_2025-11-15.pdf" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" display="BSI.IT.6.C7.3-Evidences\02_BL_Results" r:id="rId12"/>
     <hyperlink ref="A9" location="'Application Attribute Testing'!A78" display="BLA06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" display="BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" display="BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" display="BLA06_FinAnalysis_Approval_Alvarenga_2026-01-26.msg" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" display="BSI.IT.6.C7.3-Evidences\02_BL_Results" r:id="rId14"/>
     <hyperlink ref="A10" location="'Application Attribute Testing'!A82" display="DMA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" display="DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" display="DMA01_ClientBackOffice_Romero_2026-08-18.msg" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals" r:id="rId16"/>
     <hyperlink ref="A11" location="'Application Attribute Testing'!A83" display="DMA02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" display="DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" display="DMA02_BSA_AML_OFAC_Marquez_2026-08-19.msg" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals" r:id="rId18"/>
     <hyperlink ref="A12" location="'Application Attribute Testing'!A84" display="DMA03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" display="DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" display="DMA03_Payments_Puentes_2026-08-18.msg" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals" r:id="rId20"/>
     <hyperlink ref="A13" location="'Application Attribute Testing'!A85" display="DMA04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" display="DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" display="DMA04_InvestmentOps_Oropesa_2026-08-17.msg" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals" r:id="rId22"/>
     <hyperlink ref="A14" location="'Application Attribute Testing'!A86" display="DMA05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" display="DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" display="DMA05_Operations_DelCerro_2026-08-19.msg" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals" r:id="rId24"/>
     <hyperlink ref="A15" location="'Application Attribute Testing'!A87" display="DMA06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" display="DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" display="DMA06_TradingCapMkts_GarciaMarques_2026-08-18.msg" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals" r:id="rId26"/>
     <hyperlink ref="A16" location="'Application Attribute Testing'!A88" display="DMA07"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" display="DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" display="DMA07_Treasury_Sullivan_2026-08-18.msg" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals" r:id="rId28"/>
     <hyperlink ref="A17" location="'Application Attribute Testing'!A89" display="DMA08"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" display="DMA08_FinancialRisk_Caisapanta_2026-08-18.msg" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals" r:id="rId30"/>
     <hyperlink ref="A18" location="'Application Attribute Testing'!A90" display="DMA09"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" display="DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" display="DMA09_GeneralServices_DeCastro_2026-08-18.msg" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals" r:id="rId32"/>
     <hyperlink ref="A19" location="'Application Attribute Testing'!A91" display="DMA10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" display="DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" display="DMA10_DigitalWealth_Fernandez_2026-08-21.eml" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals" r:id="rId34"/>
     <hyperlink ref="A20" location="'Application Attribute Testing'!A92" display="DMA11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" display="DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" display="DMA11_CommMiddleOffice_Orozco_2026-09-09.eml" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals" r:id="rId36"/>
     <hyperlink ref="A21" location="'Application Attribute Testing'!A93" display="DMA12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" display="DMA12_ClientServicing_Vizhnay_2026-09-09.eml" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals" r:id="rId38"/>
     <hyperlink ref="A22" location="'Application Attribute Testing'!A94" display="DMA13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" display="DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" display="BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" display="DMA13_CiscoCallMgr_Noda_2026-09-09_OutOfScope.eml" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" display="BSI.IT.6.C7.3-Evidences\03_Mgr_Approvals" r:id="rId40"/>
     <hyperlink ref="A23" location="'Application Attribute Testing'!A99" display="E01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" display="BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" display="E01_BCiC_Apps_InScope_DR.xlsx" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing" r:id="rId42"/>
     <hyperlink ref="A24" location="'Application Attribute Testing'!A100" display="E02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" display="BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" display="E02_BCiC_Apps_InScope_Screenshot.jpg" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing" r:id="rId44"/>
     <hyperlink ref="A25" location="'Application Attribute Testing'!A101" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" display="BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" display="E03_BCiC_DIV_Testing_Export.xls" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing" r:id="rId46"/>
     <hyperlink ref="A26" location="'Application Attribute Testing'!A102" display="E04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" display="BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" display="E04_BCiC_DIV_Report_Screenshot.jpg" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing" r:id="rId48"/>
     <hyperlink ref="A27" location="'Application Attribute Testing'!A103" display="E05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" display="BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" display="E05_IT_BIA_Review_DR_Prep.msg" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing" r:id="rId50"/>
     <hyperlink ref="A28" location="'Application Attribute Testing'!A104" display="E07"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" display="BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" display="E07_DIV_Source_Files_2025-11-14.msg" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing" r:id="rId52"/>
     <hyperlink ref="A29" location="'Application Attribute Testing'!A105" display="E08"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" display="BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" display="E08_DR_Test_Files_2025-11-15.msg" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing" r:id="rId54"/>
     <hyperlink ref="A30" location="'Application Attribute Testing'!A106" display="E09"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" display="BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" display="E09_ClientBackOffice_BackupRestore_Signoff.msg" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing" r:id="rId56"/>
     <hyperlink ref="A31" location="'Application Attribute Testing'!A107" display="E10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" display="BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" display="E10_Finance_BackupRestore_Approval.msg" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing" r:id="rId58"/>
     <hyperlink ref="A32" location="'Application Attribute Testing'!A108" display="E13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" display="BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" display="E13_T24_Env_Refresh_2024-11-13.msg" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing" r:id="rId60"/>
     <hyperlink ref="A33" location="'Application Attribute Testing'!A109" display="E16b"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" display="BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" display="BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" display="E16b_BCiC_DIV_Testing_2025-26.xlsx" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" display="BSI.IT.6.C7.3-Evidences\04_DIV_Testing" r:id="rId62"/>
     <hyperlink ref="A34" location="'Testing Attributes Testing -2'!A125" display="DRS01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS01_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - IT Scope 10-08-2025.eml" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS01_DR_Exercise_IT_Scope_2025-10-08.eml" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails" r:id="rId64"/>
     <hyperlink ref="A35" location="'Testing Attributes Testing -2'!A126" display="DRS02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails\DRS02_Fw_ Annual DR (Disaster Recovery) Exercise - Saturday, Nov 15 - confirm participants - Business Scope 10-08-2025.eml" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" display="BSI.IT.6.C7.3-Evidences\05_Annual_DR_Exercise_IT_and_Business_Scope_Emails" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails\DRS02_DR_Exercise_Business_Scope_2025-10-08.eml" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" display="BSI.IT.6.C7.3-Evidences\05_DR_Scope_Emails" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
